--- a/n8n-only/template/instagram-posts-template.xlsx
+++ b/n8n-only/template/instagram-posts-template.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1000"/>
+  <dimension ref="A1:T1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -458,6 +458,7 @@
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="40" customWidth="1" min="18" max="18"/>
     <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,6 +557,11 @@
           <t>Last Updated</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Approval Code</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -587,6 +593,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="3" t="n"/>
+      <c r="T2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -612,6 +619,7 @@
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
       <c r="R3" s="3" t="n"/>
+      <c r="T3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -633,6 +641,7 @@
       <c r="P4" s="2" t="n"/>
       <c r="Q4" s="2" t="n"/>
       <c r="R4" s="3" t="n"/>
+      <c r="T4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -644,6 +653,7 @@
       <c r="P5" s="2" t="n"/>
       <c r="Q5" s="2" t="n"/>
       <c r="R5" s="3" t="n"/>
+      <c r="T5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -655,6 +665,7 @@
       <c r="P6" s="2" t="n"/>
       <c r="Q6" s="2" t="n"/>
       <c r="R6" s="3" t="n"/>
+      <c r="T6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -666,6 +677,7 @@
       <c r="P7" s="2" t="n"/>
       <c r="Q7" s="2" t="n"/>
       <c r="R7" s="3" t="n"/>
+      <c r="T7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -677,6 +689,7 @@
       <c r="P8" s="2" t="n"/>
       <c r="Q8" s="2" t="n"/>
       <c r="R8" s="3" t="n"/>
+      <c r="T8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -688,6 +701,7 @@
       <c r="P9" s="2" t="n"/>
       <c r="Q9" s="2" t="n"/>
       <c r="R9" s="3" t="n"/>
+      <c r="T9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -699,6 +713,7 @@
       <c r="P10" s="2" t="n"/>
       <c r="Q10" s="2" t="n"/>
       <c r="R10" s="3" t="n"/>
+      <c r="T10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -710,6 +725,7 @@
       <c r="P11" s="2" t="n"/>
       <c r="Q11" s="2" t="n"/>
       <c r="R11" s="3" t="n"/>
+      <c r="T11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -721,6 +737,7 @@
       <c r="P12" s="2" t="n"/>
       <c r="Q12" s="2" t="n"/>
       <c r="R12" s="3" t="n"/>
+      <c r="T12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -732,6 +749,7 @@
       <c r="P13" s="2" t="n"/>
       <c r="Q13" s="2" t="n"/>
       <c r="R13" s="3" t="n"/>
+      <c r="T13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -743,6 +761,7 @@
       <c r="P14" s="2" t="n"/>
       <c r="Q14" s="2" t="n"/>
       <c r="R14" s="3" t="n"/>
+      <c r="T14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -754,6 +773,7 @@
       <c r="P15" s="2" t="n"/>
       <c r="Q15" s="2" t="n"/>
       <c r="R15" s="3" t="n"/>
+      <c r="T15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -765,6 +785,7 @@
       <c r="P16" s="2" t="n"/>
       <c r="Q16" s="2" t="n"/>
       <c r="R16" s="3" t="n"/>
+      <c r="T16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -776,6 +797,7 @@
       <c r="P17" s="2" t="n"/>
       <c r="Q17" s="2" t="n"/>
       <c r="R17" s="3" t="n"/>
+      <c r="T17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -787,6 +809,7 @@
       <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="n"/>
       <c r="R18" s="3" t="n"/>
+      <c r="T18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -798,6 +821,7 @@
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="n"/>
       <c r="R19" s="3" t="n"/>
+      <c r="T19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -809,6 +833,7 @@
       <c r="P20" s="2" t="n"/>
       <c r="Q20" s="2" t="n"/>
       <c r="R20" s="3" t="n"/>
+      <c r="T20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -820,6 +845,7 @@
       <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="n"/>
       <c r="R21" s="3" t="n"/>
+      <c r="T21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -831,6 +857,7 @@
       <c r="P22" s="2" t="n"/>
       <c r="Q22" s="2" t="n"/>
       <c r="R22" s="3" t="n"/>
+      <c r="T22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -842,6 +869,7 @@
       <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="n"/>
       <c r="R23" s="3" t="n"/>
+      <c r="T23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -853,6 +881,7 @@
       <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="n"/>
       <c r="R24" s="3" t="n"/>
+      <c r="T24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -864,6 +893,7 @@
       <c r="P25" s="2" t="n"/>
       <c r="Q25" s="2" t="n"/>
       <c r="R25" s="3" t="n"/>
+      <c r="T25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -875,6 +905,7 @@
       <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="n"/>
       <c r="R26" s="3" t="n"/>
+      <c r="T26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -886,6 +917,7 @@
       <c r="P27" s="2" t="n"/>
       <c r="Q27" s="2" t="n"/>
       <c r="R27" s="3" t="n"/>
+      <c r="T27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -897,6 +929,7 @@
       <c r="P28" s="2" t="n"/>
       <c r="Q28" s="2" t="n"/>
       <c r="R28" s="3" t="n"/>
+      <c r="T28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -908,6 +941,7 @@
       <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="n"/>
       <c r="R29" s="3" t="n"/>
+      <c r="T29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -919,6 +953,7 @@
       <c r="P30" s="2" t="n"/>
       <c r="Q30" s="2" t="n"/>
       <c r="R30" s="3" t="n"/>
+      <c r="T30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -930,6 +965,7 @@
       <c r="P31" s="2" t="n"/>
       <c r="Q31" s="2" t="n"/>
       <c r="R31" s="3" t="n"/>
+      <c r="T31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -941,6 +977,7 @@
       <c r="P32" s="2" t="n"/>
       <c r="Q32" s="2" t="n"/>
       <c r="R32" s="3" t="n"/>
+      <c r="T32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -952,6 +989,7 @@
       <c r="P33" s="2" t="n"/>
       <c r="Q33" s="2" t="n"/>
       <c r="R33" s="3" t="n"/>
+      <c r="T33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -963,6 +1001,7 @@
       <c r="P34" s="2" t="n"/>
       <c r="Q34" s="2" t="n"/>
       <c r="R34" s="3" t="n"/>
+      <c r="T34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -974,6 +1013,7 @@
       <c r="P35" s="2" t="n"/>
       <c r="Q35" s="2" t="n"/>
       <c r="R35" s="3" t="n"/>
+      <c r="T35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -985,6 +1025,7 @@
       <c r="P36" s="2" t="n"/>
       <c r="Q36" s="2" t="n"/>
       <c r="R36" s="3" t="n"/>
+      <c r="T36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -996,6 +1037,7 @@
       <c r="P37" s="2" t="n"/>
       <c r="Q37" s="2" t="n"/>
       <c r="R37" s="3" t="n"/>
+      <c r="T37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -1007,6 +1049,7 @@
       <c r="P38" s="2" t="n"/>
       <c r="Q38" s="2" t="n"/>
       <c r="R38" s="3" t="n"/>
+      <c r="T38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -1018,6 +1061,7 @@
       <c r="P39" s="2" t="n"/>
       <c r="Q39" s="2" t="n"/>
       <c r="R39" s="3" t="n"/>
+      <c r="T39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -1029,6 +1073,7 @@
       <c r="P40" s="2" t="n"/>
       <c r="Q40" s="2" t="n"/>
       <c r="R40" s="3" t="n"/>
+      <c r="T40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -1040,6 +1085,7 @@
       <c r="P41" s="2" t="n"/>
       <c r="Q41" s="2" t="n"/>
       <c r="R41" s="3" t="n"/>
+      <c r="T41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -1051,6 +1097,7 @@
       <c r="P42" s="2" t="n"/>
       <c r="Q42" s="2" t="n"/>
       <c r="R42" s="3" t="n"/>
+      <c r="T42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -1062,6 +1109,7 @@
       <c r="P43" s="2" t="n"/>
       <c r="Q43" s="2" t="n"/>
       <c r="R43" s="3" t="n"/>
+      <c r="T43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -1073,6 +1121,7 @@
       <c r="P44" s="2" t="n"/>
       <c r="Q44" s="2" t="n"/>
       <c r="R44" s="3" t="n"/>
+      <c r="T44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -1084,6 +1133,7 @@
       <c r="P45" s="2" t="n"/>
       <c r="Q45" s="2" t="n"/>
       <c r="R45" s="3" t="n"/>
+      <c r="T45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -1095,6 +1145,7 @@
       <c r="P46" s="2" t="n"/>
       <c r="Q46" s="2" t="n"/>
       <c r="R46" s="3" t="n"/>
+      <c r="T46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
@@ -1106,6 +1157,7 @@
       <c r="P47" s="2" t="n"/>
       <c r="Q47" s="2" t="n"/>
       <c r="R47" s="3" t="n"/>
+      <c r="T47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -1117,6 +1169,7 @@
       <c r="P48" s="2" t="n"/>
       <c r="Q48" s="2" t="n"/>
       <c r="R48" s="3" t="n"/>
+      <c r="T48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
@@ -1128,6 +1181,7 @@
       <c r="P49" s="2" t="n"/>
       <c r="Q49" s="2" t="n"/>
       <c r="R49" s="3" t="n"/>
+      <c r="T49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -1139,6 +1193,7 @@
       <c r="P50" s="2" t="n"/>
       <c r="Q50" s="2" t="n"/>
       <c r="R50" s="3" t="n"/>
+      <c r="T50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
@@ -1150,6 +1205,7 @@
       <c r="P51" s="2" t="n"/>
       <c r="Q51" s="2" t="n"/>
       <c r="R51" s="3" t="n"/>
+      <c r="T51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -1161,6 +1217,7 @@
       <c r="P52" s="2" t="n"/>
       <c r="Q52" s="2" t="n"/>
       <c r="R52" s="3" t="n"/>
+      <c r="T52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -1172,6 +1229,7 @@
       <c r="P53" s="2" t="n"/>
       <c r="Q53" s="2" t="n"/>
       <c r="R53" s="3" t="n"/>
+      <c r="T53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -1183,6 +1241,7 @@
       <c r="P54" s="2" t="n"/>
       <c r="Q54" s="2" t="n"/>
       <c r="R54" s="3" t="n"/>
+      <c r="T54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>
@@ -1194,6 +1253,7 @@
       <c r="P55" s="2" t="n"/>
       <c r="Q55" s="2" t="n"/>
       <c r="R55" s="3" t="n"/>
+      <c r="T55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -1205,6 +1265,7 @@
       <c r="P56" s="2" t="n"/>
       <c r="Q56" s="2" t="n"/>
       <c r="R56" s="3" t="n"/>
+      <c r="T56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>
@@ -1216,6 +1277,7 @@
       <c r="P57" s="2" t="n"/>
       <c r="Q57" s="2" t="n"/>
       <c r="R57" s="3" t="n"/>
+      <c r="T57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -1227,6 +1289,7 @@
       <c r="P58" s="2" t="n"/>
       <c r="Q58" s="2" t="n"/>
       <c r="R58" s="3" t="n"/>
+      <c r="T58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
@@ -1238,6 +1301,7 @@
       <c r="P59" s="2" t="n"/>
       <c r="Q59" s="2" t="n"/>
       <c r="R59" s="3" t="n"/>
+      <c r="T59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -1249,6 +1313,7 @@
       <c r="P60" s="2" t="n"/>
       <c r="Q60" s="2" t="n"/>
       <c r="R60" s="3" t="n"/>
+      <c r="T60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n"/>
@@ -1260,6 +1325,7 @@
       <c r="P61" s="2" t="n"/>
       <c r="Q61" s="2" t="n"/>
       <c r="R61" s="3" t="n"/>
+      <c r="T61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n"/>
@@ -1271,6 +1337,7 @@
       <c r="P62" s="2" t="n"/>
       <c r="Q62" s="2" t="n"/>
       <c r="R62" s="3" t="n"/>
+      <c r="T62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n"/>
@@ -1282,6 +1349,7 @@
       <c r="P63" s="2" t="n"/>
       <c r="Q63" s="2" t="n"/>
       <c r="R63" s="3" t="n"/>
+      <c r="T63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>
@@ -1293,6 +1361,7 @@
       <c r="P64" s="2" t="n"/>
       <c r="Q64" s="2" t="n"/>
       <c r="R64" s="3" t="n"/>
+      <c r="T64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n"/>
@@ -1304,6 +1373,7 @@
       <c r="P65" s="2" t="n"/>
       <c r="Q65" s="2" t="n"/>
       <c r="R65" s="3" t="n"/>
+      <c r="T65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n"/>
@@ -1315,6 +1385,7 @@
       <c r="P66" s="2" t="n"/>
       <c r="Q66" s="2" t="n"/>
       <c r="R66" s="3" t="n"/>
+      <c r="T66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n"/>
@@ -1326,6 +1397,7 @@
       <c r="P67" s="2" t="n"/>
       <c r="Q67" s="2" t="n"/>
       <c r="R67" s="3" t="n"/>
+      <c r="T67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>
@@ -1337,6 +1409,7 @@
       <c r="P68" s="2" t="n"/>
       <c r="Q68" s="2" t="n"/>
       <c r="R68" s="3" t="n"/>
+      <c r="T68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n"/>
@@ -1348,6 +1421,7 @@
       <c r="P69" s="2" t="n"/>
       <c r="Q69" s="2" t="n"/>
       <c r="R69" s="3" t="n"/>
+      <c r="T69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n"/>
@@ -1359,6 +1433,7 @@
       <c r="P70" s="2" t="n"/>
       <c r="Q70" s="2" t="n"/>
       <c r="R70" s="3" t="n"/>
+      <c r="T70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n"/>
@@ -1370,6 +1445,7 @@
       <c r="P71" s="2" t="n"/>
       <c r="Q71" s="2" t="n"/>
       <c r="R71" s="3" t="n"/>
+      <c r="T71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n"/>
@@ -1381,6 +1457,7 @@
       <c r="P72" s="2" t="n"/>
       <c r="Q72" s="2" t="n"/>
       <c r="R72" s="3" t="n"/>
+      <c r="T72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n"/>
@@ -1392,6 +1469,7 @@
       <c r="P73" s="2" t="n"/>
       <c r="Q73" s="2" t="n"/>
       <c r="R73" s="3" t="n"/>
+      <c r="T73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>
@@ -1403,6 +1481,7 @@
       <c r="P74" s="2" t="n"/>
       <c r="Q74" s="2" t="n"/>
       <c r="R74" s="3" t="n"/>
+      <c r="T74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n"/>
@@ -1414,6 +1493,7 @@
       <c r="P75" s="2" t="n"/>
       <c r="Q75" s="2" t="n"/>
       <c r="R75" s="3" t="n"/>
+      <c r="T75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n"/>
@@ -1425,6 +1505,7 @@
       <c r="P76" s="2" t="n"/>
       <c r="Q76" s="2" t="n"/>
       <c r="R76" s="3" t="n"/>
+      <c r="T76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n"/>
@@ -1436,6 +1517,7 @@
       <c r="P77" s="2" t="n"/>
       <c r="Q77" s="2" t="n"/>
       <c r="R77" s="3" t="n"/>
+      <c r="T77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n"/>
@@ -1447,6 +1529,7 @@
       <c r="P78" s="2" t="n"/>
       <c r="Q78" s="2" t="n"/>
       <c r="R78" s="3" t="n"/>
+      <c r="T78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n"/>
@@ -1458,6 +1541,7 @@
       <c r="P79" s="2" t="n"/>
       <c r="Q79" s="2" t="n"/>
       <c r="R79" s="3" t="n"/>
+      <c r="T79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>
@@ -1469,6 +1553,7 @@
       <c r="P80" s="2" t="n"/>
       <c r="Q80" s="2" t="n"/>
       <c r="R80" s="3" t="n"/>
+      <c r="T80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n"/>
@@ -1480,6 +1565,7 @@
       <c r="P81" s="2" t="n"/>
       <c r="Q81" s="2" t="n"/>
       <c r="R81" s="3" t="n"/>
+      <c r="T81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n"/>
@@ -1491,6 +1577,7 @@
       <c r="P82" s="2" t="n"/>
       <c r="Q82" s="2" t="n"/>
       <c r="R82" s="3" t="n"/>
+      <c r="T82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n"/>
@@ -1502,6 +1589,7 @@
       <c r="P83" s="2" t="n"/>
       <c r="Q83" s="2" t="n"/>
       <c r="R83" s="3" t="n"/>
+      <c r="T83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n"/>
@@ -1513,6 +1601,7 @@
       <c r="P84" s="2" t="n"/>
       <c r="Q84" s="2" t="n"/>
       <c r="R84" s="3" t="n"/>
+      <c r="T84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n"/>
@@ -1524,6 +1613,7 @@
       <c r="P85" s="2" t="n"/>
       <c r="Q85" s="2" t="n"/>
       <c r="R85" s="3" t="n"/>
+      <c r="T85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n"/>
@@ -1535,6 +1625,7 @@
       <c r="P86" s="2" t="n"/>
       <c r="Q86" s="2" t="n"/>
       <c r="R86" s="3" t="n"/>
+      <c r="T86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n"/>
@@ -1546,6 +1637,7 @@
       <c r="P87" s="2" t="n"/>
       <c r="Q87" s="2" t="n"/>
       <c r="R87" s="3" t="n"/>
+      <c r="T87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n"/>
@@ -1557,6 +1649,7 @@
       <c r="P88" s="2" t="n"/>
       <c r="Q88" s="2" t="n"/>
       <c r="R88" s="3" t="n"/>
+      <c r="T88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n"/>
@@ -1568,6 +1661,7 @@
       <c r="P89" s="2" t="n"/>
       <c r="Q89" s="2" t="n"/>
       <c r="R89" s="3" t="n"/>
+      <c r="T89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n"/>
@@ -1579,6 +1673,7 @@
       <c r="P90" s="2" t="n"/>
       <c r="Q90" s="2" t="n"/>
       <c r="R90" s="3" t="n"/>
+      <c r="T90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n"/>
@@ -1590,6 +1685,7 @@
       <c r="P91" s="2" t="n"/>
       <c r="Q91" s="2" t="n"/>
       <c r="R91" s="3" t="n"/>
+      <c r="T91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n"/>
@@ -1601,6 +1697,7 @@
       <c r="P92" s="2" t="n"/>
       <c r="Q92" s="2" t="n"/>
       <c r="R92" s="3" t="n"/>
+      <c r="T92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n"/>
@@ -1612,6 +1709,7 @@
       <c r="P93" s="2" t="n"/>
       <c r="Q93" s="2" t="n"/>
       <c r="R93" s="3" t="n"/>
+      <c r="T93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n"/>
@@ -1623,6 +1721,7 @@
       <c r="P94" s="2" t="n"/>
       <c r="Q94" s="2" t="n"/>
       <c r="R94" s="3" t="n"/>
+      <c r="T94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n"/>
@@ -1634,6 +1733,7 @@
       <c r="P95" s="2" t="n"/>
       <c r="Q95" s="2" t="n"/>
       <c r="R95" s="3" t="n"/>
+      <c r="T95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n"/>
@@ -1645,6 +1745,7 @@
       <c r="P96" s="2" t="n"/>
       <c r="Q96" s="2" t="n"/>
       <c r="R96" s="3" t="n"/>
+      <c r="T96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n"/>
@@ -1656,6 +1757,7 @@
       <c r="P97" s="2" t="n"/>
       <c r="Q97" s="2" t="n"/>
       <c r="R97" s="3" t="n"/>
+      <c r="T97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n"/>
@@ -1667,6 +1769,7 @@
       <c r="P98" s="2" t="n"/>
       <c r="Q98" s="2" t="n"/>
       <c r="R98" s="3" t="n"/>
+      <c r="T98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n"/>
@@ -1678,6 +1781,7 @@
       <c r="P99" s="2" t="n"/>
       <c r="Q99" s="2" t="n"/>
       <c r="R99" s="3" t="n"/>
+      <c r="T99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n"/>
@@ -1689,6 +1793,7 @@
       <c r="P100" s="2" t="n"/>
       <c r="Q100" s="2" t="n"/>
       <c r="R100" s="3" t="n"/>
+      <c r="T100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n"/>
@@ -1700,6 +1805,7 @@
       <c r="P101" s="2" t="n"/>
       <c r="Q101" s="2" t="n"/>
       <c r="R101" s="3" t="n"/>
+      <c r="T101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n"/>
@@ -1711,6 +1817,7 @@
       <c r="P102" s="2" t="n"/>
       <c r="Q102" s="2" t="n"/>
       <c r="R102" s="3" t="n"/>
+      <c r="T102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n"/>
@@ -1722,6 +1829,7 @@
       <c r="P103" s="2" t="n"/>
       <c r="Q103" s="2" t="n"/>
       <c r="R103" s="3" t="n"/>
+      <c r="T103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n"/>
@@ -1733,6 +1841,7 @@
       <c r="P104" s="2" t="n"/>
       <c r="Q104" s="2" t="n"/>
       <c r="R104" s="3" t="n"/>
+      <c r="T104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n"/>
@@ -1744,6 +1853,7 @@
       <c r="P105" s="2" t="n"/>
       <c r="Q105" s="2" t="n"/>
       <c r="R105" s="3" t="n"/>
+      <c r="T105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n"/>
@@ -1755,6 +1865,7 @@
       <c r="P106" s="2" t="n"/>
       <c r="Q106" s="2" t="n"/>
       <c r="R106" s="3" t="n"/>
+      <c r="T106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n"/>
@@ -1766,6 +1877,7 @@
       <c r="P107" s="2" t="n"/>
       <c r="Q107" s="2" t="n"/>
       <c r="R107" s="3" t="n"/>
+      <c r="T107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n"/>
@@ -1777,6 +1889,7 @@
       <c r="P108" s="2" t="n"/>
       <c r="Q108" s="2" t="n"/>
       <c r="R108" s="3" t="n"/>
+      <c r="T108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n"/>
@@ -1788,6 +1901,7 @@
       <c r="P109" s="2" t="n"/>
       <c r="Q109" s="2" t="n"/>
       <c r="R109" s="3" t="n"/>
+      <c r="T109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n"/>
@@ -1799,6 +1913,7 @@
       <c r="P110" s="2" t="n"/>
       <c r="Q110" s="2" t="n"/>
       <c r="R110" s="3" t="n"/>
+      <c r="T110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n"/>
@@ -1810,6 +1925,7 @@
       <c r="P111" s="2" t="n"/>
       <c r="Q111" s="2" t="n"/>
       <c r="R111" s="3" t="n"/>
+      <c r="T111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n"/>
@@ -1821,6 +1937,7 @@
       <c r="P112" s="2" t="n"/>
       <c r="Q112" s="2" t="n"/>
       <c r="R112" s="3" t="n"/>
+      <c r="T112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n"/>
@@ -1832,6 +1949,7 @@
       <c r="P113" s="2" t="n"/>
       <c r="Q113" s="2" t="n"/>
       <c r="R113" s="3" t="n"/>
+      <c r="T113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n"/>
@@ -1843,6 +1961,7 @@
       <c r="P114" s="2" t="n"/>
       <c r="Q114" s="2" t="n"/>
       <c r="R114" s="3" t="n"/>
+      <c r="T114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n"/>
@@ -1854,6 +1973,7 @@
       <c r="P115" s="2" t="n"/>
       <c r="Q115" s="2" t="n"/>
       <c r="R115" s="3" t="n"/>
+      <c r="T115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n"/>
@@ -1865,6 +1985,7 @@
       <c r="P116" s="2" t="n"/>
       <c r="Q116" s="2" t="n"/>
       <c r="R116" s="3" t="n"/>
+      <c r="T116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n"/>
@@ -1876,6 +1997,7 @@
       <c r="P117" s="2" t="n"/>
       <c r="Q117" s="2" t="n"/>
       <c r="R117" s="3" t="n"/>
+      <c r="T117" s="2" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n"/>
@@ -1887,6 +2009,7 @@
       <c r="P118" s="2" t="n"/>
       <c r="Q118" s="2" t="n"/>
       <c r="R118" s="3" t="n"/>
+      <c r="T118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n"/>
@@ -1898,6 +2021,7 @@
       <c r="P119" s="2" t="n"/>
       <c r="Q119" s="2" t="n"/>
       <c r="R119" s="3" t="n"/>
+      <c r="T119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n"/>
@@ -1909,6 +2033,7 @@
       <c r="P120" s="2" t="n"/>
       <c r="Q120" s="2" t="n"/>
       <c r="R120" s="3" t="n"/>
+      <c r="T120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n"/>
@@ -1920,6 +2045,7 @@
       <c r="P121" s="2" t="n"/>
       <c r="Q121" s="2" t="n"/>
       <c r="R121" s="3" t="n"/>
+      <c r="T121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n"/>
@@ -1931,6 +2057,7 @@
       <c r="P122" s="2" t="n"/>
       <c r="Q122" s="2" t="n"/>
       <c r="R122" s="3" t="n"/>
+      <c r="T122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n"/>
@@ -1942,6 +2069,7 @@
       <c r="P123" s="2" t="n"/>
       <c r="Q123" s="2" t="n"/>
       <c r="R123" s="3" t="n"/>
+      <c r="T123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n"/>
@@ -1953,6 +2081,7 @@
       <c r="P124" s="2" t="n"/>
       <c r="Q124" s="2" t="n"/>
       <c r="R124" s="3" t="n"/>
+      <c r="T124" s="2" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n"/>
@@ -1964,6 +2093,7 @@
       <c r="P125" s="2" t="n"/>
       <c r="Q125" s="2" t="n"/>
       <c r="R125" s="3" t="n"/>
+      <c r="T125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n"/>
@@ -1975,6 +2105,7 @@
       <c r="P126" s="2" t="n"/>
       <c r="Q126" s="2" t="n"/>
       <c r="R126" s="3" t="n"/>
+      <c r="T126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n"/>
@@ -1986,6 +2117,7 @@
       <c r="P127" s="2" t="n"/>
       <c r="Q127" s="2" t="n"/>
       <c r="R127" s="3" t="n"/>
+      <c r="T127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n"/>
@@ -1997,6 +2129,7 @@
       <c r="P128" s="2" t="n"/>
       <c r="Q128" s="2" t="n"/>
       <c r="R128" s="3" t="n"/>
+      <c r="T128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n"/>
@@ -2008,6 +2141,7 @@
       <c r="P129" s="2" t="n"/>
       <c r="Q129" s="2" t="n"/>
       <c r="R129" s="3" t="n"/>
+      <c r="T129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n"/>
@@ -2019,6 +2153,7 @@
       <c r="P130" s="2" t="n"/>
       <c r="Q130" s="2" t="n"/>
       <c r="R130" s="3" t="n"/>
+      <c r="T130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n"/>
@@ -2030,6 +2165,7 @@
       <c r="P131" s="2" t="n"/>
       <c r="Q131" s="2" t="n"/>
       <c r="R131" s="3" t="n"/>
+      <c r="T131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n"/>
@@ -2041,6 +2177,7 @@
       <c r="P132" s="2" t="n"/>
       <c r="Q132" s="2" t="n"/>
       <c r="R132" s="3" t="n"/>
+      <c r="T132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n"/>
@@ -2052,6 +2189,7 @@
       <c r="P133" s="2" t="n"/>
       <c r="Q133" s="2" t="n"/>
       <c r="R133" s="3" t="n"/>
+      <c r="T133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n"/>
@@ -2063,6 +2201,7 @@
       <c r="P134" s="2" t="n"/>
       <c r="Q134" s="2" t="n"/>
       <c r="R134" s="3" t="n"/>
+      <c r="T134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n"/>
@@ -2074,6 +2213,7 @@
       <c r="P135" s="2" t="n"/>
       <c r="Q135" s="2" t="n"/>
       <c r="R135" s="3" t="n"/>
+      <c r="T135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n"/>
@@ -2085,6 +2225,7 @@
       <c r="P136" s="2" t="n"/>
       <c r="Q136" s="2" t="n"/>
       <c r="R136" s="3" t="n"/>
+      <c r="T136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n"/>
@@ -2096,6 +2237,7 @@
       <c r="P137" s="2" t="n"/>
       <c r="Q137" s="2" t="n"/>
       <c r="R137" s="3" t="n"/>
+      <c r="T137" s="2" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n"/>
@@ -2107,6 +2249,7 @@
       <c r="P138" s="2" t="n"/>
       <c r="Q138" s="2" t="n"/>
       <c r="R138" s="3" t="n"/>
+      <c r="T138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n"/>
@@ -2118,6 +2261,7 @@
       <c r="P139" s="2" t="n"/>
       <c r="Q139" s="2" t="n"/>
       <c r="R139" s="3" t="n"/>
+      <c r="T139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n"/>
@@ -2129,6 +2273,7 @@
       <c r="P140" s="2" t="n"/>
       <c r="Q140" s="2" t="n"/>
       <c r="R140" s="3" t="n"/>
+      <c r="T140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n"/>
@@ -2140,6 +2285,7 @@
       <c r="P141" s="2" t="n"/>
       <c r="Q141" s="2" t="n"/>
       <c r="R141" s="3" t="n"/>
+      <c r="T141" s="2" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n"/>
@@ -2151,6 +2297,7 @@
       <c r="P142" s="2" t="n"/>
       <c r="Q142" s="2" t="n"/>
       <c r="R142" s="3" t="n"/>
+      <c r="T142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n"/>
@@ -2162,6 +2309,7 @@
       <c r="P143" s="2" t="n"/>
       <c r="Q143" s="2" t="n"/>
       <c r="R143" s="3" t="n"/>
+      <c r="T143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n"/>
@@ -2173,6 +2321,7 @@
       <c r="P144" s="2" t="n"/>
       <c r="Q144" s="2" t="n"/>
       <c r="R144" s="3" t="n"/>
+      <c r="T144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n"/>
@@ -2184,6 +2333,7 @@
       <c r="P145" s="2" t="n"/>
       <c r="Q145" s="2" t="n"/>
       <c r="R145" s="3" t="n"/>
+      <c r="T145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n"/>
@@ -2195,6 +2345,7 @@
       <c r="P146" s="2" t="n"/>
       <c r="Q146" s="2" t="n"/>
       <c r="R146" s="3" t="n"/>
+      <c r="T146" s="2" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n"/>
@@ -2206,6 +2357,7 @@
       <c r="P147" s="2" t="n"/>
       <c r="Q147" s="2" t="n"/>
       <c r="R147" s="3" t="n"/>
+      <c r="T147" s="2" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n"/>
@@ -2217,6 +2369,7 @@
       <c r="P148" s="2" t="n"/>
       <c r="Q148" s="2" t="n"/>
       <c r="R148" s="3" t="n"/>
+      <c r="T148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n"/>
@@ -2228,6 +2381,7 @@
       <c r="P149" s="2" t="n"/>
       <c r="Q149" s="2" t="n"/>
       <c r="R149" s="3" t="n"/>
+      <c r="T149" s="2" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n"/>
@@ -2239,6 +2393,7 @@
       <c r="P150" s="2" t="n"/>
       <c r="Q150" s="2" t="n"/>
       <c r="R150" s="3" t="n"/>
+      <c r="T150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n"/>
@@ -2250,6 +2405,7 @@
       <c r="P151" s="2" t="n"/>
       <c r="Q151" s="2" t="n"/>
       <c r="R151" s="3" t="n"/>
+      <c r="T151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n"/>
@@ -2261,6 +2417,7 @@
       <c r="P152" s="2" t="n"/>
       <c r="Q152" s="2" t="n"/>
       <c r="R152" s="3" t="n"/>
+      <c r="T152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n"/>
@@ -2272,6 +2429,7 @@
       <c r="P153" s="2" t="n"/>
       <c r="Q153" s="2" t="n"/>
       <c r="R153" s="3" t="n"/>
+      <c r="T153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n"/>
@@ -2283,6 +2441,7 @@
       <c r="P154" s="2" t="n"/>
       <c r="Q154" s="2" t="n"/>
       <c r="R154" s="3" t="n"/>
+      <c r="T154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n"/>
@@ -2294,6 +2453,7 @@
       <c r="P155" s="2" t="n"/>
       <c r="Q155" s="2" t="n"/>
       <c r="R155" s="3" t="n"/>
+      <c r="T155" s="2" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n"/>
@@ -2305,6 +2465,7 @@
       <c r="P156" s="2" t="n"/>
       <c r="Q156" s="2" t="n"/>
       <c r="R156" s="3" t="n"/>
+      <c r="T156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n"/>
@@ -2316,6 +2477,7 @@
       <c r="P157" s="2" t="n"/>
       <c r="Q157" s="2" t="n"/>
       <c r="R157" s="3" t="n"/>
+      <c r="T157" s="2" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n"/>
@@ -2327,6 +2489,7 @@
       <c r="P158" s="2" t="n"/>
       <c r="Q158" s="2" t="n"/>
       <c r="R158" s="3" t="n"/>
+      <c r="T158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n"/>
@@ -2338,6 +2501,7 @@
       <c r="P159" s="2" t="n"/>
       <c r="Q159" s="2" t="n"/>
       <c r="R159" s="3" t="n"/>
+      <c r="T159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n"/>
@@ -2349,6 +2513,7 @@
       <c r="P160" s="2" t="n"/>
       <c r="Q160" s="2" t="n"/>
       <c r="R160" s="3" t="n"/>
+      <c r="T160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n"/>
@@ -2360,6 +2525,7 @@
       <c r="P161" s="2" t="n"/>
       <c r="Q161" s="2" t="n"/>
       <c r="R161" s="3" t="n"/>
+      <c r="T161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n"/>
@@ -2371,6 +2537,7 @@
       <c r="P162" s="2" t="n"/>
       <c r="Q162" s="2" t="n"/>
       <c r="R162" s="3" t="n"/>
+      <c r="T162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n"/>
@@ -2382,6 +2549,7 @@
       <c r="P163" s="2" t="n"/>
       <c r="Q163" s="2" t="n"/>
       <c r="R163" s="3" t="n"/>
+      <c r="T163" s="2" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n"/>
@@ -2393,6 +2561,7 @@
       <c r="P164" s="2" t="n"/>
       <c r="Q164" s="2" t="n"/>
       <c r="R164" s="3" t="n"/>
+      <c r="T164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n"/>
@@ -2404,6 +2573,7 @@
       <c r="P165" s="2" t="n"/>
       <c r="Q165" s="2" t="n"/>
       <c r="R165" s="3" t="n"/>
+      <c r="T165" s="2" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n"/>
@@ -2415,6 +2585,7 @@
       <c r="P166" s="2" t="n"/>
       <c r="Q166" s="2" t="n"/>
       <c r="R166" s="3" t="n"/>
+      <c r="T166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n"/>
@@ -2426,6 +2597,7 @@
       <c r="P167" s="2" t="n"/>
       <c r="Q167" s="2" t="n"/>
       <c r="R167" s="3" t="n"/>
+      <c r="T167" s="2" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n"/>
@@ -2437,6 +2609,7 @@
       <c r="P168" s="2" t="n"/>
       <c r="Q168" s="2" t="n"/>
       <c r="R168" s="3" t="n"/>
+      <c r="T168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n"/>
@@ -2448,6 +2621,7 @@
       <c r="P169" s="2" t="n"/>
       <c r="Q169" s="2" t="n"/>
       <c r="R169" s="3" t="n"/>
+      <c r="T169" s="2" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n"/>
@@ -2459,6 +2633,7 @@
       <c r="P170" s="2" t="n"/>
       <c r="Q170" s="2" t="n"/>
       <c r="R170" s="3" t="n"/>
+      <c r="T170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n"/>
@@ -2470,6 +2645,7 @@
       <c r="P171" s="2" t="n"/>
       <c r="Q171" s="2" t="n"/>
       <c r="R171" s="3" t="n"/>
+      <c r="T171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n"/>
@@ -2481,6 +2657,7 @@
       <c r="P172" s="2" t="n"/>
       <c r="Q172" s="2" t="n"/>
       <c r="R172" s="3" t="n"/>
+      <c r="T172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n"/>
@@ -2492,6 +2669,7 @@
       <c r="P173" s="2" t="n"/>
       <c r="Q173" s="2" t="n"/>
       <c r="R173" s="3" t="n"/>
+      <c r="T173" s="2" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n"/>
@@ -2503,6 +2681,7 @@
       <c r="P174" s="2" t="n"/>
       <c r="Q174" s="2" t="n"/>
       <c r="R174" s="3" t="n"/>
+      <c r="T174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n"/>
@@ -2514,6 +2693,7 @@
       <c r="P175" s="2" t="n"/>
       <c r="Q175" s="2" t="n"/>
       <c r="R175" s="3" t="n"/>
+      <c r="T175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n"/>
@@ -2525,6 +2705,7 @@
       <c r="P176" s="2" t="n"/>
       <c r="Q176" s="2" t="n"/>
       <c r="R176" s="3" t="n"/>
+      <c r="T176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n"/>
@@ -2536,6 +2717,7 @@
       <c r="P177" s="2" t="n"/>
       <c r="Q177" s="2" t="n"/>
       <c r="R177" s="3" t="n"/>
+      <c r="T177" s="2" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n"/>
@@ -2547,6 +2729,7 @@
       <c r="P178" s="2" t="n"/>
       <c r="Q178" s="2" t="n"/>
       <c r="R178" s="3" t="n"/>
+      <c r="T178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n"/>
@@ -2558,6 +2741,7 @@
       <c r="P179" s="2" t="n"/>
       <c r="Q179" s="2" t="n"/>
       <c r="R179" s="3" t="n"/>
+      <c r="T179" s="2" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n"/>
@@ -2569,6 +2753,7 @@
       <c r="P180" s="2" t="n"/>
       <c r="Q180" s="2" t="n"/>
       <c r="R180" s="3" t="n"/>
+      <c r="T180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n"/>
@@ -2580,6 +2765,7 @@
       <c r="P181" s="2" t="n"/>
       <c r="Q181" s="2" t="n"/>
       <c r="R181" s="3" t="n"/>
+      <c r="T181" s="2" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n"/>
@@ -2591,6 +2777,7 @@
       <c r="P182" s="2" t="n"/>
       <c r="Q182" s="2" t="n"/>
       <c r="R182" s="3" t="n"/>
+      <c r="T182" s="2" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n"/>
@@ -2602,6 +2789,7 @@
       <c r="P183" s="2" t="n"/>
       <c r="Q183" s="2" t="n"/>
       <c r="R183" s="3" t="n"/>
+      <c r="T183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n"/>
@@ -2613,6 +2801,7 @@
       <c r="P184" s="2" t="n"/>
       <c r="Q184" s="2" t="n"/>
       <c r="R184" s="3" t="n"/>
+      <c r="T184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n"/>
@@ -2624,6 +2813,7 @@
       <c r="P185" s="2" t="n"/>
       <c r="Q185" s="2" t="n"/>
       <c r="R185" s="3" t="n"/>
+      <c r="T185" s="2" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n"/>
@@ -2635,6 +2825,7 @@
       <c r="P186" s="2" t="n"/>
       <c r="Q186" s="2" t="n"/>
       <c r="R186" s="3" t="n"/>
+      <c r="T186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n"/>
@@ -2646,6 +2837,7 @@
       <c r="P187" s="2" t="n"/>
       <c r="Q187" s="2" t="n"/>
       <c r="R187" s="3" t="n"/>
+      <c r="T187" s="2" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n"/>
@@ -2657,6 +2849,7 @@
       <c r="P188" s="2" t="n"/>
       <c r="Q188" s="2" t="n"/>
       <c r="R188" s="3" t="n"/>
+      <c r="T188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n"/>
@@ -2668,6 +2861,7 @@
       <c r="P189" s="2" t="n"/>
       <c r="Q189" s="2" t="n"/>
       <c r="R189" s="3" t="n"/>
+      <c r="T189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n"/>
@@ -2679,6 +2873,7 @@
       <c r="P190" s="2" t="n"/>
       <c r="Q190" s="2" t="n"/>
       <c r="R190" s="3" t="n"/>
+      <c r="T190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n"/>
@@ -2690,6 +2885,7 @@
       <c r="P191" s="2" t="n"/>
       <c r="Q191" s="2" t="n"/>
       <c r="R191" s="3" t="n"/>
+      <c r="T191" s="2" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n"/>
@@ -2701,6 +2897,7 @@
       <c r="P192" s="2" t="n"/>
       <c r="Q192" s="2" t="n"/>
       <c r="R192" s="3" t="n"/>
+      <c r="T192" s="2" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n"/>
@@ -2712,6 +2909,7 @@
       <c r="P193" s="2" t="n"/>
       <c r="Q193" s="2" t="n"/>
       <c r="R193" s="3" t="n"/>
+      <c r="T193" s="2" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n"/>
@@ -2723,6 +2921,7 @@
       <c r="P194" s="2" t="n"/>
       <c r="Q194" s="2" t="n"/>
       <c r="R194" s="3" t="n"/>
+      <c r="T194" s="2" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n"/>
@@ -2734,6 +2933,7 @@
       <c r="P195" s="2" t="n"/>
       <c r="Q195" s="2" t="n"/>
       <c r="R195" s="3" t="n"/>
+      <c r="T195" s="2" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n"/>
@@ -2745,6 +2945,7 @@
       <c r="P196" s="2" t="n"/>
       <c r="Q196" s="2" t="n"/>
       <c r="R196" s="3" t="n"/>
+      <c r="T196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n"/>
@@ -2756,6 +2957,7 @@
       <c r="P197" s="2" t="n"/>
       <c r="Q197" s="2" t="n"/>
       <c r="R197" s="3" t="n"/>
+      <c r="T197" s="2" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n"/>
@@ -2767,6 +2969,7 @@
       <c r="P198" s="2" t="n"/>
       <c r="Q198" s="2" t="n"/>
       <c r="R198" s="3" t="n"/>
+      <c r="T198" s="2" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n"/>
@@ -2778,6 +2981,7 @@
       <c r="P199" s="2" t="n"/>
       <c r="Q199" s="2" t="n"/>
       <c r="R199" s="3" t="n"/>
+      <c r="T199" s="2" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n"/>
@@ -2789,6 +2993,7 @@
       <c r="P200" s="2" t="n"/>
       <c r="Q200" s="2" t="n"/>
       <c r="R200" s="3" t="n"/>
+      <c r="T200" s="2" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n"/>
@@ -2800,6 +3005,7 @@
       <c r="P201" s="2" t="n"/>
       <c r="Q201" s="2" t="n"/>
       <c r="R201" s="3" t="n"/>
+      <c r="T201" s="2" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n"/>
@@ -2811,6 +3017,7 @@
       <c r="P202" s="2" t="n"/>
       <c r="Q202" s="2" t="n"/>
       <c r="R202" s="3" t="n"/>
+      <c r="T202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n"/>
@@ -2822,6 +3029,7 @@
       <c r="P203" s="2" t="n"/>
       <c r="Q203" s="2" t="n"/>
       <c r="R203" s="3" t="n"/>
+      <c r="T203" s="2" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n"/>
@@ -2833,6 +3041,7 @@
       <c r="P204" s="2" t="n"/>
       <c r="Q204" s="2" t="n"/>
       <c r="R204" s="3" t="n"/>
+      <c r="T204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n"/>
@@ -2844,6 +3053,7 @@
       <c r="P205" s="2" t="n"/>
       <c r="Q205" s="2" t="n"/>
       <c r="R205" s="3" t="n"/>
+      <c r="T205" s="2" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n"/>
@@ -2855,6 +3065,7 @@
       <c r="P206" s="2" t="n"/>
       <c r="Q206" s="2" t="n"/>
       <c r="R206" s="3" t="n"/>
+      <c r="T206" s="2" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n"/>
@@ -2866,6 +3077,7 @@
       <c r="P207" s="2" t="n"/>
       <c r="Q207" s="2" t="n"/>
       <c r="R207" s="3" t="n"/>
+      <c r="T207" s="2" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n"/>
@@ -2877,6 +3089,7 @@
       <c r="P208" s="2" t="n"/>
       <c r="Q208" s="2" t="n"/>
       <c r="R208" s="3" t="n"/>
+      <c r="T208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n"/>
@@ -2888,6 +3101,7 @@
       <c r="P209" s="2" t="n"/>
       <c r="Q209" s="2" t="n"/>
       <c r="R209" s="3" t="n"/>
+      <c r="T209" s="2" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n"/>
@@ -2899,6 +3113,7 @@
       <c r="P210" s="2" t="n"/>
       <c r="Q210" s="2" t="n"/>
       <c r="R210" s="3" t="n"/>
+      <c r="T210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n"/>
@@ -2910,6 +3125,7 @@
       <c r="P211" s="2" t="n"/>
       <c r="Q211" s="2" t="n"/>
       <c r="R211" s="3" t="n"/>
+      <c r="T211" s="2" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n"/>
@@ -2921,6 +3137,7 @@
       <c r="P212" s="2" t="n"/>
       <c r="Q212" s="2" t="n"/>
       <c r="R212" s="3" t="n"/>
+      <c r="T212" s="2" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n"/>
@@ -2932,6 +3149,7 @@
       <c r="P213" s="2" t="n"/>
       <c r="Q213" s="2" t="n"/>
       <c r="R213" s="3" t="n"/>
+      <c r="T213" s="2" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n"/>
@@ -2943,6 +3161,7 @@
       <c r="P214" s="2" t="n"/>
       <c r="Q214" s="2" t="n"/>
       <c r="R214" s="3" t="n"/>
+      <c r="T214" s="2" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n"/>
@@ -2954,6 +3173,7 @@
       <c r="P215" s="2" t="n"/>
       <c r="Q215" s="2" t="n"/>
       <c r="R215" s="3" t="n"/>
+      <c r="T215" s="2" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n"/>
@@ -2965,6 +3185,7 @@
       <c r="P216" s="2" t="n"/>
       <c r="Q216" s="2" t="n"/>
       <c r="R216" s="3" t="n"/>
+      <c r="T216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n"/>
@@ -2976,6 +3197,7 @@
       <c r="P217" s="2" t="n"/>
       <c r="Q217" s="2" t="n"/>
       <c r="R217" s="3" t="n"/>
+      <c r="T217" s="2" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n"/>
@@ -2987,6 +3209,7 @@
       <c r="P218" s="2" t="n"/>
       <c r="Q218" s="2" t="n"/>
       <c r="R218" s="3" t="n"/>
+      <c r="T218" s="2" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n"/>
@@ -2998,6 +3221,7 @@
       <c r="P219" s="2" t="n"/>
       <c r="Q219" s="2" t="n"/>
       <c r="R219" s="3" t="n"/>
+      <c r="T219" s="2" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n"/>
@@ -3009,6 +3233,7 @@
       <c r="P220" s="2" t="n"/>
       <c r="Q220" s="2" t="n"/>
       <c r="R220" s="3" t="n"/>
+      <c r="T220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n"/>
@@ -3020,6 +3245,7 @@
       <c r="P221" s="2" t="n"/>
       <c r="Q221" s="2" t="n"/>
       <c r="R221" s="3" t="n"/>
+      <c r="T221" s="2" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n"/>
@@ -3031,6 +3257,7 @@
       <c r="P222" s="2" t="n"/>
       <c r="Q222" s="2" t="n"/>
       <c r="R222" s="3" t="n"/>
+      <c r="T222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n"/>
@@ -3042,6 +3269,7 @@
       <c r="P223" s="2" t="n"/>
       <c r="Q223" s="2" t="n"/>
       <c r="R223" s="3" t="n"/>
+      <c r="T223" s="2" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n"/>
@@ -3053,6 +3281,7 @@
       <c r="P224" s="2" t="n"/>
       <c r="Q224" s="2" t="n"/>
       <c r="R224" s="3" t="n"/>
+      <c r="T224" s="2" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n"/>
@@ -3064,6 +3293,7 @@
       <c r="P225" s="2" t="n"/>
       <c r="Q225" s="2" t="n"/>
       <c r="R225" s="3" t="n"/>
+      <c r="T225" s="2" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n"/>
@@ -3075,6 +3305,7 @@
       <c r="P226" s="2" t="n"/>
       <c r="Q226" s="2" t="n"/>
       <c r="R226" s="3" t="n"/>
+      <c r="T226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n"/>
@@ -3086,6 +3317,7 @@
       <c r="P227" s="2" t="n"/>
       <c r="Q227" s="2" t="n"/>
       <c r="R227" s="3" t="n"/>
+      <c r="T227" s="2" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n"/>
@@ -3097,6 +3329,7 @@
       <c r="P228" s="2" t="n"/>
       <c r="Q228" s="2" t="n"/>
       <c r="R228" s="3" t="n"/>
+      <c r="T228" s="2" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n"/>
@@ -3108,6 +3341,7 @@
       <c r="P229" s="2" t="n"/>
       <c r="Q229" s="2" t="n"/>
       <c r="R229" s="3" t="n"/>
+      <c r="T229" s="2" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n"/>
@@ -3119,6 +3353,7 @@
       <c r="P230" s="2" t="n"/>
       <c r="Q230" s="2" t="n"/>
       <c r="R230" s="3" t="n"/>
+      <c r="T230" s="2" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n"/>
@@ -3130,6 +3365,7 @@
       <c r="P231" s="2" t="n"/>
       <c r="Q231" s="2" t="n"/>
       <c r="R231" s="3" t="n"/>
+      <c r="T231" s="2" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n"/>
@@ -3141,6 +3377,7 @@
       <c r="P232" s="2" t="n"/>
       <c r="Q232" s="2" t="n"/>
       <c r="R232" s="3" t="n"/>
+      <c r="T232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n"/>
@@ -3152,6 +3389,7 @@
       <c r="P233" s="2" t="n"/>
       <c r="Q233" s="2" t="n"/>
       <c r="R233" s="3" t="n"/>
+      <c r="T233" s="2" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n"/>
@@ -3163,6 +3401,7 @@
       <c r="P234" s="2" t="n"/>
       <c r="Q234" s="2" t="n"/>
       <c r="R234" s="3" t="n"/>
+      <c r="T234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n"/>
@@ -3174,6 +3413,7 @@
       <c r="P235" s="2" t="n"/>
       <c r="Q235" s="2" t="n"/>
       <c r="R235" s="3" t="n"/>
+      <c r="T235" s="2" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n"/>
@@ -3185,6 +3425,7 @@
       <c r="P236" s="2" t="n"/>
       <c r="Q236" s="2" t="n"/>
       <c r="R236" s="3" t="n"/>
+      <c r="T236" s="2" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n"/>
@@ -3196,6 +3437,7 @@
       <c r="P237" s="2" t="n"/>
       <c r="Q237" s="2" t="n"/>
       <c r="R237" s="3" t="n"/>
+      <c r="T237" s="2" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n"/>
@@ -3207,6 +3449,7 @@
       <c r="P238" s="2" t="n"/>
       <c r="Q238" s="2" t="n"/>
       <c r="R238" s="3" t="n"/>
+      <c r="T238" s="2" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n"/>
@@ -3218,6 +3461,7 @@
       <c r="P239" s="2" t="n"/>
       <c r="Q239" s="2" t="n"/>
       <c r="R239" s="3" t="n"/>
+      <c r="T239" s="2" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n"/>
@@ -3229,6 +3473,7 @@
       <c r="P240" s="2" t="n"/>
       <c r="Q240" s="2" t="n"/>
       <c r="R240" s="3" t="n"/>
+      <c r="T240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n"/>
@@ -3240,6 +3485,7 @@
       <c r="P241" s="2" t="n"/>
       <c r="Q241" s="2" t="n"/>
       <c r="R241" s="3" t="n"/>
+      <c r="T241" s="2" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n"/>
@@ -3251,6 +3497,7 @@
       <c r="P242" s="2" t="n"/>
       <c r="Q242" s="2" t="n"/>
       <c r="R242" s="3" t="n"/>
+      <c r="T242" s="2" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n"/>
@@ -3262,6 +3509,7 @@
       <c r="P243" s="2" t="n"/>
       <c r="Q243" s="2" t="n"/>
       <c r="R243" s="3" t="n"/>
+      <c r="T243" s="2" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n"/>
@@ -3273,6 +3521,7 @@
       <c r="P244" s="2" t="n"/>
       <c r="Q244" s="2" t="n"/>
       <c r="R244" s="3" t="n"/>
+      <c r="T244" s="2" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n"/>
@@ -3284,6 +3533,7 @@
       <c r="P245" s="2" t="n"/>
       <c r="Q245" s="2" t="n"/>
       <c r="R245" s="3" t="n"/>
+      <c r="T245" s="2" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n"/>
@@ -3295,6 +3545,7 @@
       <c r="P246" s="2" t="n"/>
       <c r="Q246" s="2" t="n"/>
       <c r="R246" s="3" t="n"/>
+      <c r="T246" s="2" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n"/>
@@ -3306,6 +3557,7 @@
       <c r="P247" s="2" t="n"/>
       <c r="Q247" s="2" t="n"/>
       <c r="R247" s="3" t="n"/>
+      <c r="T247" s="2" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n"/>
@@ -3317,6 +3569,7 @@
       <c r="P248" s="2" t="n"/>
       <c r="Q248" s="2" t="n"/>
       <c r="R248" s="3" t="n"/>
+      <c r="T248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n"/>
@@ -3328,6 +3581,7 @@
       <c r="P249" s="2" t="n"/>
       <c r="Q249" s="2" t="n"/>
       <c r="R249" s="3" t="n"/>
+      <c r="T249" s="2" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n"/>
@@ -3339,6 +3593,7 @@
       <c r="P250" s="2" t="n"/>
       <c r="Q250" s="2" t="n"/>
       <c r="R250" s="3" t="n"/>
+      <c r="T250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n"/>
@@ -3350,6 +3605,7 @@
       <c r="P251" s="2" t="n"/>
       <c r="Q251" s="2" t="n"/>
       <c r="R251" s="3" t="n"/>
+      <c r="T251" s="2" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n"/>
@@ -3361,6 +3617,7 @@
       <c r="P252" s="2" t="n"/>
       <c r="Q252" s="2" t="n"/>
       <c r="R252" s="3" t="n"/>
+      <c r="T252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n"/>
@@ -3372,6 +3629,7 @@
       <c r="P253" s="2" t="n"/>
       <c r="Q253" s="2" t="n"/>
       <c r="R253" s="3" t="n"/>
+      <c r="T253" s="2" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n"/>
@@ -3383,6 +3641,7 @@
       <c r="P254" s="2" t="n"/>
       <c r="Q254" s="2" t="n"/>
       <c r="R254" s="3" t="n"/>
+      <c r="T254" s="2" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n"/>
@@ -3394,6 +3653,7 @@
       <c r="P255" s="2" t="n"/>
       <c r="Q255" s="2" t="n"/>
       <c r="R255" s="3" t="n"/>
+      <c r="T255" s="2" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n"/>
@@ -3405,6 +3665,7 @@
       <c r="P256" s="2" t="n"/>
       <c r="Q256" s="2" t="n"/>
       <c r="R256" s="3" t="n"/>
+      <c r="T256" s="2" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n"/>
@@ -3416,6 +3677,7 @@
       <c r="P257" s="2" t="n"/>
       <c r="Q257" s="2" t="n"/>
       <c r="R257" s="3" t="n"/>
+      <c r="T257" s="2" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n"/>
@@ -3427,6 +3689,7 @@
       <c r="P258" s="2" t="n"/>
       <c r="Q258" s="2" t="n"/>
       <c r="R258" s="3" t="n"/>
+      <c r="T258" s="2" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n"/>
@@ -3438,6 +3701,7 @@
       <c r="P259" s="2" t="n"/>
       <c r="Q259" s="2" t="n"/>
       <c r="R259" s="3" t="n"/>
+      <c r="T259" s="2" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n"/>
@@ -3449,6 +3713,7 @@
       <c r="P260" s="2" t="n"/>
       <c r="Q260" s="2" t="n"/>
       <c r="R260" s="3" t="n"/>
+      <c r="T260" s="2" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n"/>
@@ -3460,6 +3725,7 @@
       <c r="P261" s="2" t="n"/>
       <c r="Q261" s="2" t="n"/>
       <c r="R261" s="3" t="n"/>
+      <c r="T261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n"/>
@@ -3471,6 +3737,7 @@
       <c r="P262" s="2" t="n"/>
       <c r="Q262" s="2" t="n"/>
       <c r="R262" s="3" t="n"/>
+      <c r="T262" s="2" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n"/>
@@ -3482,6 +3749,7 @@
       <c r="P263" s="2" t="n"/>
       <c r="Q263" s="2" t="n"/>
       <c r="R263" s="3" t="n"/>
+      <c r="T263" s="2" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n"/>
@@ -3493,6 +3761,7 @@
       <c r="P264" s="2" t="n"/>
       <c r="Q264" s="2" t="n"/>
       <c r="R264" s="3" t="n"/>
+      <c r="T264" s="2" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n"/>
@@ -3504,6 +3773,7 @@
       <c r="P265" s="2" t="n"/>
       <c r="Q265" s="2" t="n"/>
       <c r="R265" s="3" t="n"/>
+      <c r="T265" s="2" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n"/>
@@ -3515,6 +3785,7 @@
       <c r="P266" s="2" t="n"/>
       <c r="Q266" s="2" t="n"/>
       <c r="R266" s="3" t="n"/>
+      <c r="T266" s="2" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n"/>
@@ -3526,6 +3797,7 @@
       <c r="P267" s="2" t="n"/>
       <c r="Q267" s="2" t="n"/>
       <c r="R267" s="3" t="n"/>
+      <c r="T267" s="2" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n"/>
@@ -3537,6 +3809,7 @@
       <c r="P268" s="2" t="n"/>
       <c r="Q268" s="2" t="n"/>
       <c r="R268" s="3" t="n"/>
+      <c r="T268" s="2" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n"/>
@@ -3548,6 +3821,7 @@
       <c r="P269" s="2" t="n"/>
       <c r="Q269" s="2" t="n"/>
       <c r="R269" s="3" t="n"/>
+      <c r="T269" s="2" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n"/>
@@ -3559,6 +3833,7 @@
       <c r="P270" s="2" t="n"/>
       <c r="Q270" s="2" t="n"/>
       <c r="R270" s="3" t="n"/>
+      <c r="T270" s="2" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n"/>
@@ -3570,6 +3845,7 @@
       <c r="P271" s="2" t="n"/>
       <c r="Q271" s="2" t="n"/>
       <c r="R271" s="3" t="n"/>
+      <c r="T271" s="2" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n"/>
@@ -3581,6 +3857,7 @@
       <c r="P272" s="2" t="n"/>
       <c r="Q272" s="2" t="n"/>
       <c r="R272" s="3" t="n"/>
+      <c r="T272" s="2" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n"/>
@@ -3592,6 +3869,7 @@
       <c r="P273" s="2" t="n"/>
       <c r="Q273" s="2" t="n"/>
       <c r="R273" s="3" t="n"/>
+      <c r="T273" s="2" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n"/>
@@ -3603,6 +3881,7 @@
       <c r="P274" s="2" t="n"/>
       <c r="Q274" s="2" t="n"/>
       <c r="R274" s="3" t="n"/>
+      <c r="T274" s="2" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n"/>
@@ -3614,6 +3893,7 @@
       <c r="P275" s="2" t="n"/>
       <c r="Q275" s="2" t="n"/>
       <c r="R275" s="3" t="n"/>
+      <c r="T275" s="2" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n"/>
@@ -3625,6 +3905,7 @@
       <c r="P276" s="2" t="n"/>
       <c r="Q276" s="2" t="n"/>
       <c r="R276" s="3" t="n"/>
+      <c r="T276" s="2" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n"/>
@@ -3636,6 +3917,7 @@
       <c r="P277" s="2" t="n"/>
       <c r="Q277" s="2" t="n"/>
       <c r="R277" s="3" t="n"/>
+      <c r="T277" s="2" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n"/>
@@ -3647,6 +3929,7 @@
       <c r="P278" s="2" t="n"/>
       <c r="Q278" s="2" t="n"/>
       <c r="R278" s="3" t="n"/>
+      <c r="T278" s="2" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n"/>
@@ -3658,6 +3941,7 @@
       <c r="P279" s="2" t="n"/>
       <c r="Q279" s="2" t="n"/>
       <c r="R279" s="3" t="n"/>
+      <c r="T279" s="2" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n"/>
@@ -3669,6 +3953,7 @@
       <c r="P280" s="2" t="n"/>
       <c r="Q280" s="2" t="n"/>
       <c r="R280" s="3" t="n"/>
+      <c r="T280" s="2" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n"/>
@@ -3680,6 +3965,7 @@
       <c r="P281" s="2" t="n"/>
       <c r="Q281" s="2" t="n"/>
       <c r="R281" s="3" t="n"/>
+      <c r="T281" s="2" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n"/>
@@ -3691,6 +3977,7 @@
       <c r="P282" s="2" t="n"/>
       <c r="Q282" s="2" t="n"/>
       <c r="R282" s="3" t="n"/>
+      <c r="T282" s="2" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n"/>
@@ -3702,6 +3989,7 @@
       <c r="P283" s="2" t="n"/>
       <c r="Q283" s="2" t="n"/>
       <c r="R283" s="3" t="n"/>
+      <c r="T283" s="2" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n"/>
@@ -3713,6 +4001,7 @@
       <c r="P284" s="2" t="n"/>
       <c r="Q284" s="2" t="n"/>
       <c r="R284" s="3" t="n"/>
+      <c r="T284" s="2" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n"/>
@@ -3724,6 +4013,7 @@
       <c r="P285" s="2" t="n"/>
       <c r="Q285" s="2" t="n"/>
       <c r="R285" s="3" t="n"/>
+      <c r="T285" s="2" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n"/>
@@ -3735,6 +4025,7 @@
       <c r="P286" s="2" t="n"/>
       <c r="Q286" s="2" t="n"/>
       <c r="R286" s="3" t="n"/>
+      <c r="T286" s="2" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n"/>
@@ -3746,6 +4037,7 @@
       <c r="P287" s="2" t="n"/>
       <c r="Q287" s="2" t="n"/>
       <c r="R287" s="3" t="n"/>
+      <c r="T287" s="2" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n"/>
@@ -3757,6 +4049,7 @@
       <c r="P288" s="2" t="n"/>
       <c r="Q288" s="2" t="n"/>
       <c r="R288" s="3" t="n"/>
+      <c r="T288" s="2" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n"/>
@@ -3768,6 +4061,7 @@
       <c r="P289" s="2" t="n"/>
       <c r="Q289" s="2" t="n"/>
       <c r="R289" s="3" t="n"/>
+      <c r="T289" s="2" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n"/>
@@ -3779,6 +4073,7 @@
       <c r="P290" s="2" t="n"/>
       <c r="Q290" s="2" t="n"/>
       <c r="R290" s="3" t="n"/>
+      <c r="T290" s="2" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n"/>
@@ -3790,6 +4085,7 @@
       <c r="P291" s="2" t="n"/>
       <c r="Q291" s="2" t="n"/>
       <c r="R291" s="3" t="n"/>
+      <c r="T291" s="2" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n"/>
@@ -3801,6 +4097,7 @@
       <c r="P292" s="2" t="n"/>
       <c r="Q292" s="2" t="n"/>
       <c r="R292" s="3" t="n"/>
+      <c r="T292" s="2" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n"/>
@@ -3812,6 +4109,7 @@
       <c r="P293" s="2" t="n"/>
       <c r="Q293" s="2" t="n"/>
       <c r="R293" s="3" t="n"/>
+      <c r="T293" s="2" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n"/>
@@ -3823,6 +4121,7 @@
       <c r="P294" s="2" t="n"/>
       <c r="Q294" s="2" t="n"/>
       <c r="R294" s="3" t="n"/>
+      <c r="T294" s="2" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n"/>
@@ -3834,6 +4133,7 @@
       <c r="P295" s="2" t="n"/>
       <c r="Q295" s="2" t="n"/>
       <c r="R295" s="3" t="n"/>
+      <c r="T295" s="2" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n"/>
@@ -3845,6 +4145,7 @@
       <c r="P296" s="2" t="n"/>
       <c r="Q296" s="2" t="n"/>
       <c r="R296" s="3" t="n"/>
+      <c r="T296" s="2" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n"/>
@@ -3856,6 +4157,7 @@
       <c r="P297" s="2" t="n"/>
       <c r="Q297" s="2" t="n"/>
       <c r="R297" s="3" t="n"/>
+      <c r="T297" s="2" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n"/>
@@ -3867,6 +4169,7 @@
       <c r="P298" s="2" t="n"/>
       <c r="Q298" s="2" t="n"/>
       <c r="R298" s="3" t="n"/>
+      <c r="T298" s="2" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n"/>
@@ -3878,6 +4181,7 @@
       <c r="P299" s="2" t="n"/>
       <c r="Q299" s="2" t="n"/>
       <c r="R299" s="3" t="n"/>
+      <c r="T299" s="2" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n"/>
@@ -3889,6 +4193,7 @@
       <c r="P300" s="2" t="n"/>
       <c r="Q300" s="2" t="n"/>
       <c r="R300" s="3" t="n"/>
+      <c r="T300" s="2" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n"/>
@@ -3900,6 +4205,7 @@
       <c r="P301" s="2" t="n"/>
       <c r="Q301" s="2" t="n"/>
       <c r="R301" s="3" t="n"/>
+      <c r="T301" s="2" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n"/>
@@ -3911,6 +4217,7 @@
       <c r="P302" s="2" t="n"/>
       <c r="Q302" s="2" t="n"/>
       <c r="R302" s="3" t="n"/>
+      <c r="T302" s="2" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n"/>
@@ -3922,6 +4229,7 @@
       <c r="P303" s="2" t="n"/>
       <c r="Q303" s="2" t="n"/>
       <c r="R303" s="3" t="n"/>
+      <c r="T303" s="2" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n"/>
@@ -3933,6 +4241,7 @@
       <c r="P304" s="2" t="n"/>
       <c r="Q304" s="2" t="n"/>
       <c r="R304" s="3" t="n"/>
+      <c r="T304" s="2" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n"/>
@@ -3944,6 +4253,7 @@
       <c r="P305" s="2" t="n"/>
       <c r="Q305" s="2" t="n"/>
       <c r="R305" s="3" t="n"/>
+      <c r="T305" s="2" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n"/>
@@ -3955,6 +4265,7 @@
       <c r="P306" s="2" t="n"/>
       <c r="Q306" s="2" t="n"/>
       <c r="R306" s="3" t="n"/>
+      <c r="T306" s="2" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n"/>
@@ -3966,6 +4277,7 @@
       <c r="P307" s="2" t="n"/>
       <c r="Q307" s="2" t="n"/>
       <c r="R307" s="3" t="n"/>
+      <c r="T307" s="2" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n"/>
@@ -3977,6 +4289,7 @@
       <c r="P308" s="2" t="n"/>
       <c r="Q308" s="2" t="n"/>
       <c r="R308" s="3" t="n"/>
+      <c r="T308" s="2" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n"/>
@@ -3988,6 +4301,7 @@
       <c r="P309" s="2" t="n"/>
       <c r="Q309" s="2" t="n"/>
       <c r="R309" s="3" t="n"/>
+      <c r="T309" s="2" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n"/>
@@ -3999,6 +4313,7 @@
       <c r="P310" s="2" t="n"/>
       <c r="Q310" s="2" t="n"/>
       <c r="R310" s="3" t="n"/>
+      <c r="T310" s="2" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n"/>
@@ -4010,6 +4325,7 @@
       <c r="P311" s="2" t="n"/>
       <c r="Q311" s="2" t="n"/>
       <c r="R311" s="3" t="n"/>
+      <c r="T311" s="2" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n"/>
@@ -4021,6 +4337,7 @@
       <c r="P312" s="2" t="n"/>
       <c r="Q312" s="2" t="n"/>
       <c r="R312" s="3" t="n"/>
+      <c r="T312" s="2" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n"/>
@@ -4032,6 +4349,7 @@
       <c r="P313" s="2" t="n"/>
       <c r="Q313" s="2" t="n"/>
       <c r="R313" s="3" t="n"/>
+      <c r="T313" s="2" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n"/>
@@ -4043,6 +4361,7 @@
       <c r="P314" s="2" t="n"/>
       <c r="Q314" s="2" t="n"/>
       <c r="R314" s="3" t="n"/>
+      <c r="T314" s="2" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n"/>
@@ -4054,6 +4373,7 @@
       <c r="P315" s="2" t="n"/>
       <c r="Q315" s="2" t="n"/>
       <c r="R315" s="3" t="n"/>
+      <c r="T315" s="2" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n"/>
@@ -4065,6 +4385,7 @@
       <c r="P316" s="2" t="n"/>
       <c r="Q316" s="2" t="n"/>
       <c r="R316" s="3" t="n"/>
+      <c r="T316" s="2" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n"/>
@@ -4076,6 +4397,7 @@
       <c r="P317" s="2" t="n"/>
       <c r="Q317" s="2" t="n"/>
       <c r="R317" s="3" t="n"/>
+      <c r="T317" s="2" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n"/>
@@ -4087,6 +4409,7 @@
       <c r="P318" s="2" t="n"/>
       <c r="Q318" s="2" t="n"/>
       <c r="R318" s="3" t="n"/>
+      <c r="T318" s="2" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n"/>
@@ -4098,6 +4421,7 @@
       <c r="P319" s="2" t="n"/>
       <c r="Q319" s="2" t="n"/>
       <c r="R319" s="3" t="n"/>
+      <c r="T319" s="2" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n"/>
@@ -4109,6 +4433,7 @@
       <c r="P320" s="2" t="n"/>
       <c r="Q320" s="2" t="n"/>
       <c r="R320" s="3" t="n"/>
+      <c r="T320" s="2" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n"/>
@@ -4120,6 +4445,7 @@
       <c r="P321" s="2" t="n"/>
       <c r="Q321" s="2" t="n"/>
       <c r="R321" s="3" t="n"/>
+      <c r="T321" s="2" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n"/>
@@ -4131,6 +4457,7 @@
       <c r="P322" s="2" t="n"/>
       <c r="Q322" s="2" t="n"/>
       <c r="R322" s="3" t="n"/>
+      <c r="T322" s="2" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n"/>
@@ -4142,6 +4469,7 @@
       <c r="P323" s="2" t="n"/>
       <c r="Q323" s="2" t="n"/>
       <c r="R323" s="3" t="n"/>
+      <c r="T323" s="2" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n"/>
@@ -4153,6 +4481,7 @@
       <c r="P324" s="2" t="n"/>
       <c r="Q324" s="2" t="n"/>
       <c r="R324" s="3" t="n"/>
+      <c r="T324" s="2" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n"/>
@@ -4164,6 +4493,7 @@
       <c r="P325" s="2" t="n"/>
       <c r="Q325" s="2" t="n"/>
       <c r="R325" s="3" t="n"/>
+      <c r="T325" s="2" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n"/>
@@ -4175,6 +4505,7 @@
       <c r="P326" s="2" t="n"/>
       <c r="Q326" s="2" t="n"/>
       <c r="R326" s="3" t="n"/>
+      <c r="T326" s="2" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n"/>
@@ -4186,6 +4517,7 @@
       <c r="P327" s="2" t="n"/>
       <c r="Q327" s="2" t="n"/>
       <c r="R327" s="3" t="n"/>
+      <c r="T327" s="2" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n"/>
@@ -4197,6 +4529,7 @@
       <c r="P328" s="2" t="n"/>
       <c r="Q328" s="2" t="n"/>
       <c r="R328" s="3" t="n"/>
+      <c r="T328" s="2" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n"/>
@@ -4208,6 +4541,7 @@
       <c r="P329" s="2" t="n"/>
       <c r="Q329" s="2" t="n"/>
       <c r="R329" s="3" t="n"/>
+      <c r="T329" s="2" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n"/>
@@ -4219,6 +4553,7 @@
       <c r="P330" s="2" t="n"/>
       <c r="Q330" s="2" t="n"/>
       <c r="R330" s="3" t="n"/>
+      <c r="T330" s="2" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n"/>
@@ -4230,6 +4565,7 @@
       <c r="P331" s="2" t="n"/>
       <c r="Q331" s="2" t="n"/>
       <c r="R331" s="3" t="n"/>
+      <c r="T331" s="2" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n"/>
@@ -4241,6 +4577,7 @@
       <c r="P332" s="2" t="n"/>
       <c r="Q332" s="2" t="n"/>
       <c r="R332" s="3" t="n"/>
+      <c r="T332" s="2" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n"/>
@@ -4252,6 +4589,7 @@
       <c r="P333" s="2" t="n"/>
       <c r="Q333" s="2" t="n"/>
       <c r="R333" s="3" t="n"/>
+      <c r="T333" s="2" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n"/>
@@ -4263,6 +4601,7 @@
       <c r="P334" s="2" t="n"/>
       <c r="Q334" s="2" t="n"/>
       <c r="R334" s="3" t="n"/>
+      <c r="T334" s="2" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n"/>
@@ -4274,6 +4613,7 @@
       <c r="P335" s="2" t="n"/>
       <c r="Q335" s="2" t="n"/>
       <c r="R335" s="3" t="n"/>
+      <c r="T335" s="2" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n"/>
@@ -4285,6 +4625,7 @@
       <c r="P336" s="2" t="n"/>
       <c r="Q336" s="2" t="n"/>
       <c r="R336" s="3" t="n"/>
+      <c r="T336" s="2" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n"/>
@@ -4296,6 +4637,7 @@
       <c r="P337" s="2" t="n"/>
       <c r="Q337" s="2" t="n"/>
       <c r="R337" s="3" t="n"/>
+      <c r="T337" s="2" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n"/>
@@ -4307,6 +4649,7 @@
       <c r="P338" s="2" t="n"/>
       <c r="Q338" s="2" t="n"/>
       <c r="R338" s="3" t="n"/>
+      <c r="T338" s="2" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n"/>
@@ -4318,6 +4661,7 @@
       <c r="P339" s="2" t="n"/>
       <c r="Q339" s="2" t="n"/>
       <c r="R339" s="3" t="n"/>
+      <c r="T339" s="2" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n"/>
@@ -4329,6 +4673,7 @@
       <c r="P340" s="2" t="n"/>
       <c r="Q340" s="2" t="n"/>
       <c r="R340" s="3" t="n"/>
+      <c r="T340" s="2" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n"/>
@@ -4340,6 +4685,7 @@
       <c r="P341" s="2" t="n"/>
       <c r="Q341" s="2" t="n"/>
       <c r="R341" s="3" t="n"/>
+      <c r="T341" s="2" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n"/>
@@ -4351,6 +4697,7 @@
       <c r="P342" s="2" t="n"/>
       <c r="Q342" s="2" t="n"/>
       <c r="R342" s="3" t="n"/>
+      <c r="T342" s="2" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n"/>
@@ -4362,6 +4709,7 @@
       <c r="P343" s="2" t="n"/>
       <c r="Q343" s="2" t="n"/>
       <c r="R343" s="3" t="n"/>
+      <c r="T343" s="2" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n"/>
@@ -4373,6 +4721,7 @@
       <c r="P344" s="2" t="n"/>
       <c r="Q344" s="2" t="n"/>
       <c r="R344" s="3" t="n"/>
+      <c r="T344" s="2" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n"/>
@@ -4384,6 +4733,7 @@
       <c r="P345" s="2" t="n"/>
       <c r="Q345" s="2" t="n"/>
       <c r="R345" s="3" t="n"/>
+      <c r="T345" s="2" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n"/>
@@ -4395,6 +4745,7 @@
       <c r="P346" s="2" t="n"/>
       <c r="Q346" s="2" t="n"/>
       <c r="R346" s="3" t="n"/>
+      <c r="T346" s="2" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n"/>
@@ -4406,6 +4757,7 @@
       <c r="P347" s="2" t="n"/>
       <c r="Q347" s="2" t="n"/>
       <c r="R347" s="3" t="n"/>
+      <c r="T347" s="2" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n"/>
@@ -4417,6 +4769,7 @@
       <c r="P348" s="2" t="n"/>
       <c r="Q348" s="2" t="n"/>
       <c r="R348" s="3" t="n"/>
+      <c r="T348" s="2" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n"/>
@@ -4428,6 +4781,7 @@
       <c r="P349" s="2" t="n"/>
       <c r="Q349" s="2" t="n"/>
       <c r="R349" s="3" t="n"/>
+      <c r="T349" s="2" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n"/>
@@ -4439,6 +4793,7 @@
       <c r="P350" s="2" t="n"/>
       <c r="Q350" s="2" t="n"/>
       <c r="R350" s="3" t="n"/>
+      <c r="T350" s="2" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n"/>
@@ -4450,6 +4805,7 @@
       <c r="P351" s="2" t="n"/>
       <c r="Q351" s="2" t="n"/>
       <c r="R351" s="3" t="n"/>
+      <c r="T351" s="2" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n"/>
@@ -4461,6 +4817,7 @@
       <c r="P352" s="2" t="n"/>
       <c r="Q352" s="2" t="n"/>
       <c r="R352" s="3" t="n"/>
+      <c r="T352" s="2" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n"/>
@@ -4472,6 +4829,7 @@
       <c r="P353" s="2" t="n"/>
       <c r="Q353" s="2" t="n"/>
       <c r="R353" s="3" t="n"/>
+      <c r="T353" s="2" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n"/>
@@ -4483,6 +4841,7 @@
       <c r="P354" s="2" t="n"/>
       <c r="Q354" s="2" t="n"/>
       <c r="R354" s="3" t="n"/>
+      <c r="T354" s="2" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n"/>
@@ -4494,6 +4853,7 @@
       <c r="P355" s="2" t="n"/>
       <c r="Q355" s="2" t="n"/>
       <c r="R355" s="3" t="n"/>
+      <c r="T355" s="2" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n"/>
@@ -4505,6 +4865,7 @@
       <c r="P356" s="2" t="n"/>
       <c r="Q356" s="2" t="n"/>
       <c r="R356" s="3" t="n"/>
+      <c r="T356" s="2" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n"/>
@@ -4516,6 +4877,7 @@
       <c r="P357" s="2" t="n"/>
       <c r="Q357" s="2" t="n"/>
       <c r="R357" s="3" t="n"/>
+      <c r="T357" s="2" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n"/>
@@ -4527,6 +4889,7 @@
       <c r="P358" s="2" t="n"/>
       <c r="Q358" s="2" t="n"/>
       <c r="R358" s="3" t="n"/>
+      <c r="T358" s="2" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n"/>
@@ -4538,6 +4901,7 @@
       <c r="P359" s="2" t="n"/>
       <c r="Q359" s="2" t="n"/>
       <c r="R359" s="3" t="n"/>
+      <c r="T359" s="2" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n"/>
@@ -4549,6 +4913,7 @@
       <c r="P360" s="2" t="n"/>
       <c r="Q360" s="2" t="n"/>
       <c r="R360" s="3" t="n"/>
+      <c r="T360" s="2" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n"/>
@@ -4560,6 +4925,7 @@
       <c r="P361" s="2" t="n"/>
       <c r="Q361" s="2" t="n"/>
       <c r="R361" s="3" t="n"/>
+      <c r="T361" s="2" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n"/>
@@ -4571,6 +4937,7 @@
       <c r="P362" s="2" t="n"/>
       <c r="Q362" s="2" t="n"/>
       <c r="R362" s="3" t="n"/>
+      <c r="T362" s="2" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n"/>
@@ -4582,6 +4949,7 @@
       <c r="P363" s="2" t="n"/>
       <c r="Q363" s="2" t="n"/>
       <c r="R363" s="3" t="n"/>
+      <c r="T363" s="2" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n"/>
@@ -4593,6 +4961,7 @@
       <c r="P364" s="2" t="n"/>
       <c r="Q364" s="2" t="n"/>
       <c r="R364" s="3" t="n"/>
+      <c r="T364" s="2" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n"/>
@@ -4604,6 +4973,7 @@
       <c r="P365" s="2" t="n"/>
       <c r="Q365" s="2" t="n"/>
       <c r="R365" s="3" t="n"/>
+      <c r="T365" s="2" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n"/>
@@ -4615,6 +4985,7 @@
       <c r="P366" s="2" t="n"/>
       <c r="Q366" s="2" t="n"/>
       <c r="R366" s="3" t="n"/>
+      <c r="T366" s="2" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n"/>
@@ -4626,6 +4997,7 @@
       <c r="P367" s="2" t="n"/>
       <c r="Q367" s="2" t="n"/>
       <c r="R367" s="3" t="n"/>
+      <c r="T367" s="2" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n"/>
@@ -4637,6 +5009,7 @@
       <c r="P368" s="2" t="n"/>
       <c r="Q368" s="2" t="n"/>
       <c r="R368" s="3" t="n"/>
+      <c r="T368" s="2" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n"/>
@@ -4648,6 +5021,7 @@
       <c r="P369" s="2" t="n"/>
       <c r="Q369" s="2" t="n"/>
       <c r="R369" s="3" t="n"/>
+      <c r="T369" s="2" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n"/>
@@ -4659,6 +5033,7 @@
       <c r="P370" s="2" t="n"/>
       <c r="Q370" s="2" t="n"/>
       <c r="R370" s="3" t="n"/>
+      <c r="T370" s="2" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n"/>
@@ -4670,6 +5045,7 @@
       <c r="P371" s="2" t="n"/>
       <c r="Q371" s="2" t="n"/>
       <c r="R371" s="3" t="n"/>
+      <c r="T371" s="2" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n"/>
@@ -4681,6 +5057,7 @@
       <c r="P372" s="2" t="n"/>
       <c r="Q372" s="2" t="n"/>
       <c r="R372" s="3" t="n"/>
+      <c r="T372" s="2" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n"/>
@@ -4692,6 +5069,7 @@
       <c r="P373" s="2" t="n"/>
       <c r="Q373" s="2" t="n"/>
       <c r="R373" s="3" t="n"/>
+      <c r="T373" s="2" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n"/>
@@ -4703,6 +5081,7 @@
       <c r="P374" s="2" t="n"/>
       <c r="Q374" s="2" t="n"/>
       <c r="R374" s="3" t="n"/>
+      <c r="T374" s="2" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n"/>
@@ -4714,6 +5093,7 @@
       <c r="P375" s="2" t="n"/>
       <c r="Q375" s="2" t="n"/>
       <c r="R375" s="3" t="n"/>
+      <c r="T375" s="2" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n"/>
@@ -4725,6 +5105,7 @@
       <c r="P376" s="2" t="n"/>
       <c r="Q376" s="2" t="n"/>
       <c r="R376" s="3" t="n"/>
+      <c r="T376" s="2" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n"/>
@@ -4736,6 +5117,7 @@
       <c r="P377" s="2" t="n"/>
       <c r="Q377" s="2" t="n"/>
       <c r="R377" s="3" t="n"/>
+      <c r="T377" s="2" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n"/>
@@ -4747,6 +5129,7 @@
       <c r="P378" s="2" t="n"/>
       <c r="Q378" s="2" t="n"/>
       <c r="R378" s="3" t="n"/>
+      <c r="T378" s="2" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n"/>
@@ -4758,6 +5141,7 @@
       <c r="P379" s="2" t="n"/>
       <c r="Q379" s="2" t="n"/>
       <c r="R379" s="3" t="n"/>
+      <c r="T379" s="2" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n"/>
@@ -4769,6 +5153,7 @@
       <c r="P380" s="2" t="n"/>
       <c r="Q380" s="2" t="n"/>
       <c r="R380" s="3" t="n"/>
+      <c r="T380" s="2" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n"/>
@@ -4780,6 +5165,7 @@
       <c r="P381" s="2" t="n"/>
       <c r="Q381" s="2" t="n"/>
       <c r="R381" s="3" t="n"/>
+      <c r="T381" s="2" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n"/>
@@ -4791,6 +5177,7 @@
       <c r="P382" s="2" t="n"/>
       <c r="Q382" s="2" t="n"/>
       <c r="R382" s="3" t="n"/>
+      <c r="T382" s="2" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n"/>
@@ -4802,6 +5189,7 @@
       <c r="P383" s="2" t="n"/>
       <c r="Q383" s="2" t="n"/>
       <c r="R383" s="3" t="n"/>
+      <c r="T383" s="2" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n"/>
@@ -4813,6 +5201,7 @@
       <c r="P384" s="2" t="n"/>
       <c r="Q384" s="2" t="n"/>
       <c r="R384" s="3" t="n"/>
+      <c r="T384" s="2" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n"/>
@@ -4824,6 +5213,7 @@
       <c r="P385" s="2" t="n"/>
       <c r="Q385" s="2" t="n"/>
       <c r="R385" s="3" t="n"/>
+      <c r="T385" s="2" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n"/>
@@ -4835,6 +5225,7 @@
       <c r="P386" s="2" t="n"/>
       <c r="Q386" s="2" t="n"/>
       <c r="R386" s="3" t="n"/>
+      <c r="T386" s="2" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n"/>
@@ -4846,6 +5237,7 @@
       <c r="P387" s="2" t="n"/>
       <c r="Q387" s="2" t="n"/>
       <c r="R387" s="3" t="n"/>
+      <c r="T387" s="2" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n"/>
@@ -4857,6 +5249,7 @@
       <c r="P388" s="2" t="n"/>
       <c r="Q388" s="2" t="n"/>
       <c r="R388" s="3" t="n"/>
+      <c r="T388" s="2" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n"/>
@@ -4868,6 +5261,7 @@
       <c r="P389" s="2" t="n"/>
       <c r="Q389" s="2" t="n"/>
       <c r="R389" s="3" t="n"/>
+      <c r="T389" s="2" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n"/>
@@ -4879,6 +5273,7 @@
       <c r="P390" s="2" t="n"/>
       <c r="Q390" s="2" t="n"/>
       <c r="R390" s="3" t="n"/>
+      <c r="T390" s="2" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n"/>
@@ -4890,6 +5285,7 @@
       <c r="P391" s="2" t="n"/>
       <c r="Q391" s="2" t="n"/>
       <c r="R391" s="3" t="n"/>
+      <c r="T391" s="2" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n"/>
@@ -4901,6 +5297,7 @@
       <c r="P392" s="2" t="n"/>
       <c r="Q392" s="2" t="n"/>
       <c r="R392" s="3" t="n"/>
+      <c r="T392" s="2" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n"/>
@@ -4912,6 +5309,7 @@
       <c r="P393" s="2" t="n"/>
       <c r="Q393" s="2" t="n"/>
       <c r="R393" s="3" t="n"/>
+      <c r="T393" s="2" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n"/>
@@ -4923,6 +5321,7 @@
       <c r="P394" s="2" t="n"/>
       <c r="Q394" s="2" t="n"/>
       <c r="R394" s="3" t="n"/>
+      <c r="T394" s="2" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n"/>
@@ -4934,6 +5333,7 @@
       <c r="P395" s="2" t="n"/>
       <c r="Q395" s="2" t="n"/>
       <c r="R395" s="3" t="n"/>
+      <c r="T395" s="2" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n"/>
@@ -4945,6 +5345,7 @@
       <c r="P396" s="2" t="n"/>
       <c r="Q396" s="2" t="n"/>
       <c r="R396" s="3" t="n"/>
+      <c r="T396" s="2" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n"/>
@@ -4956,6 +5357,7 @@
       <c r="P397" s="2" t="n"/>
       <c r="Q397" s="2" t="n"/>
       <c r="R397" s="3" t="n"/>
+      <c r="T397" s="2" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n"/>
@@ -4967,6 +5369,7 @@
       <c r="P398" s="2" t="n"/>
       <c r="Q398" s="2" t="n"/>
       <c r="R398" s="3" t="n"/>
+      <c r="T398" s="2" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n"/>
@@ -4978,6 +5381,7 @@
       <c r="P399" s="2" t="n"/>
       <c r="Q399" s="2" t="n"/>
       <c r="R399" s="3" t="n"/>
+      <c r="T399" s="2" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n"/>
@@ -4989,6 +5393,7 @@
       <c r="P400" s="2" t="n"/>
       <c r="Q400" s="2" t="n"/>
       <c r="R400" s="3" t="n"/>
+      <c r="T400" s="2" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n"/>
@@ -5000,6 +5405,7 @@
       <c r="P401" s="2" t="n"/>
       <c r="Q401" s="2" t="n"/>
       <c r="R401" s="3" t="n"/>
+      <c r="T401" s="2" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n"/>
@@ -5011,6 +5417,7 @@
       <c r="P402" s="2" t="n"/>
       <c r="Q402" s="2" t="n"/>
       <c r="R402" s="3" t="n"/>
+      <c r="T402" s="2" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n"/>
@@ -5022,6 +5429,7 @@
       <c r="P403" s="2" t="n"/>
       <c r="Q403" s="2" t="n"/>
       <c r="R403" s="3" t="n"/>
+      <c r="T403" s="2" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n"/>
@@ -5033,6 +5441,7 @@
       <c r="P404" s="2" t="n"/>
       <c r="Q404" s="2" t="n"/>
       <c r="R404" s="3" t="n"/>
+      <c r="T404" s="2" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n"/>
@@ -5044,6 +5453,7 @@
       <c r="P405" s="2" t="n"/>
       <c r="Q405" s="2" t="n"/>
       <c r="R405" s="3" t="n"/>
+      <c r="T405" s="2" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n"/>
@@ -5055,6 +5465,7 @@
       <c r="P406" s="2" t="n"/>
       <c r="Q406" s="2" t="n"/>
       <c r="R406" s="3" t="n"/>
+      <c r="T406" s="2" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n"/>
@@ -5066,6 +5477,7 @@
       <c r="P407" s="2" t="n"/>
       <c r="Q407" s="2" t="n"/>
       <c r="R407" s="3" t="n"/>
+      <c r="T407" s="2" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n"/>
@@ -5077,6 +5489,7 @@
       <c r="P408" s="2" t="n"/>
       <c r="Q408" s="2" t="n"/>
       <c r="R408" s="3" t="n"/>
+      <c r="T408" s="2" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n"/>
@@ -5088,6 +5501,7 @@
       <c r="P409" s="2" t="n"/>
       <c r="Q409" s="2" t="n"/>
       <c r="R409" s="3" t="n"/>
+      <c r="T409" s="2" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n"/>
@@ -5099,6 +5513,7 @@
       <c r="P410" s="2" t="n"/>
       <c r="Q410" s="2" t="n"/>
       <c r="R410" s="3" t="n"/>
+      <c r="T410" s="2" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n"/>
@@ -5110,6 +5525,7 @@
       <c r="P411" s="2" t="n"/>
       <c r="Q411" s="2" t="n"/>
       <c r="R411" s="3" t="n"/>
+      <c r="T411" s="2" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n"/>
@@ -5121,6 +5537,7 @@
       <c r="P412" s="2" t="n"/>
       <c r="Q412" s="2" t="n"/>
       <c r="R412" s="3" t="n"/>
+      <c r="T412" s="2" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n"/>
@@ -5132,6 +5549,7 @@
       <c r="P413" s="2" t="n"/>
       <c r="Q413" s="2" t="n"/>
       <c r="R413" s="3" t="n"/>
+      <c r="T413" s="2" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n"/>
@@ -5143,6 +5561,7 @@
       <c r="P414" s="2" t="n"/>
       <c r="Q414" s="2" t="n"/>
       <c r="R414" s="3" t="n"/>
+      <c r="T414" s="2" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n"/>
@@ -5154,6 +5573,7 @@
       <c r="P415" s="2" t="n"/>
       <c r="Q415" s="2" t="n"/>
       <c r="R415" s="3" t="n"/>
+      <c r="T415" s="2" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n"/>
@@ -5165,6 +5585,7 @@
       <c r="P416" s="2" t="n"/>
       <c r="Q416" s="2" t="n"/>
       <c r="R416" s="3" t="n"/>
+      <c r="T416" s="2" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n"/>
@@ -5176,6 +5597,7 @@
       <c r="P417" s="2" t="n"/>
       <c r="Q417" s="2" t="n"/>
       <c r="R417" s="3" t="n"/>
+      <c r="T417" s="2" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n"/>
@@ -5187,6 +5609,7 @@
       <c r="P418" s="2" t="n"/>
       <c r="Q418" s="2" t="n"/>
       <c r="R418" s="3" t="n"/>
+      <c r="T418" s="2" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n"/>
@@ -5198,6 +5621,7 @@
       <c r="P419" s="2" t="n"/>
       <c r="Q419" s="2" t="n"/>
       <c r="R419" s="3" t="n"/>
+      <c r="T419" s="2" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n"/>
@@ -5209,6 +5633,7 @@
       <c r="P420" s="2" t="n"/>
       <c r="Q420" s="2" t="n"/>
       <c r="R420" s="3" t="n"/>
+      <c r="T420" s="2" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n"/>
@@ -5220,6 +5645,7 @@
       <c r="P421" s="2" t="n"/>
       <c r="Q421" s="2" t="n"/>
       <c r="R421" s="3" t="n"/>
+      <c r="T421" s="2" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n"/>
@@ -5231,6 +5657,7 @@
       <c r="P422" s="2" t="n"/>
       <c r="Q422" s="2" t="n"/>
       <c r="R422" s="3" t="n"/>
+      <c r="T422" s="2" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n"/>
@@ -5242,6 +5669,7 @@
       <c r="P423" s="2" t="n"/>
       <c r="Q423" s="2" t="n"/>
       <c r="R423" s="3" t="n"/>
+      <c r="T423" s="2" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n"/>
@@ -5253,6 +5681,7 @@
       <c r="P424" s="2" t="n"/>
       <c r="Q424" s="2" t="n"/>
       <c r="R424" s="3" t="n"/>
+      <c r="T424" s="2" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n"/>
@@ -5264,6 +5693,7 @@
       <c r="P425" s="2" t="n"/>
       <c r="Q425" s="2" t="n"/>
       <c r="R425" s="3" t="n"/>
+      <c r="T425" s="2" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n"/>
@@ -5275,6 +5705,7 @@
       <c r="P426" s="2" t="n"/>
       <c r="Q426" s="2" t="n"/>
       <c r="R426" s="3" t="n"/>
+      <c r="T426" s="2" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n"/>
@@ -5286,6 +5717,7 @@
       <c r="P427" s="2" t="n"/>
       <c r="Q427" s="2" t="n"/>
       <c r="R427" s="3" t="n"/>
+      <c r="T427" s="2" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n"/>
@@ -5297,6 +5729,7 @@
       <c r="P428" s="2" t="n"/>
       <c r="Q428" s="2" t="n"/>
       <c r="R428" s="3" t="n"/>
+      <c r="T428" s="2" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n"/>
@@ -5308,6 +5741,7 @@
       <c r="P429" s="2" t="n"/>
       <c r="Q429" s="2" t="n"/>
       <c r="R429" s="3" t="n"/>
+      <c r="T429" s="2" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n"/>
@@ -5319,6 +5753,7 @@
       <c r="P430" s="2" t="n"/>
       <c r="Q430" s="2" t="n"/>
       <c r="R430" s="3" t="n"/>
+      <c r="T430" s="2" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n"/>
@@ -5330,6 +5765,7 @@
       <c r="P431" s="2" t="n"/>
       <c r="Q431" s="2" t="n"/>
       <c r="R431" s="3" t="n"/>
+      <c r="T431" s="2" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n"/>
@@ -5341,6 +5777,7 @@
       <c r="P432" s="2" t="n"/>
       <c r="Q432" s="2" t="n"/>
       <c r="R432" s="3" t="n"/>
+      <c r="T432" s="2" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n"/>
@@ -5352,6 +5789,7 @@
       <c r="P433" s="2" t="n"/>
       <c r="Q433" s="2" t="n"/>
       <c r="R433" s="3" t="n"/>
+      <c r="T433" s="2" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n"/>
@@ -5363,6 +5801,7 @@
       <c r="P434" s="2" t="n"/>
       <c r="Q434" s="2" t="n"/>
       <c r="R434" s="3" t="n"/>
+      <c r="T434" s="2" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n"/>
@@ -5374,6 +5813,7 @@
       <c r="P435" s="2" t="n"/>
       <c r="Q435" s="2" t="n"/>
       <c r="R435" s="3" t="n"/>
+      <c r="T435" s="2" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n"/>
@@ -5385,6 +5825,7 @@
       <c r="P436" s="2" t="n"/>
       <c r="Q436" s="2" t="n"/>
       <c r="R436" s="3" t="n"/>
+      <c r="T436" s="2" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n"/>
@@ -5396,6 +5837,7 @@
       <c r="P437" s="2" t="n"/>
       <c r="Q437" s="2" t="n"/>
       <c r="R437" s="3" t="n"/>
+      <c r="T437" s="2" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n"/>
@@ -5407,6 +5849,7 @@
       <c r="P438" s="2" t="n"/>
       <c r="Q438" s="2" t="n"/>
       <c r="R438" s="3" t="n"/>
+      <c r="T438" s="2" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n"/>
@@ -5418,6 +5861,7 @@
       <c r="P439" s="2" t="n"/>
       <c r="Q439" s="2" t="n"/>
       <c r="R439" s="3" t="n"/>
+      <c r="T439" s="2" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n"/>
@@ -5429,6 +5873,7 @@
       <c r="P440" s="2" t="n"/>
       <c r="Q440" s="2" t="n"/>
       <c r="R440" s="3" t="n"/>
+      <c r="T440" s="2" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n"/>
@@ -5440,6 +5885,7 @@
       <c r="P441" s="2" t="n"/>
       <c r="Q441" s="2" t="n"/>
       <c r="R441" s="3" t="n"/>
+      <c r="T441" s="2" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n"/>
@@ -5451,6 +5897,7 @@
       <c r="P442" s="2" t="n"/>
       <c r="Q442" s="2" t="n"/>
       <c r="R442" s="3" t="n"/>
+      <c r="T442" s="2" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n"/>
@@ -5462,6 +5909,7 @@
       <c r="P443" s="2" t="n"/>
       <c r="Q443" s="2" t="n"/>
       <c r="R443" s="3" t="n"/>
+      <c r="T443" s="2" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n"/>
@@ -5473,6 +5921,7 @@
       <c r="P444" s="2" t="n"/>
       <c r="Q444" s="2" t="n"/>
       <c r="R444" s="3" t="n"/>
+      <c r="T444" s="2" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n"/>
@@ -5484,6 +5933,7 @@
       <c r="P445" s="2" t="n"/>
       <c r="Q445" s="2" t="n"/>
       <c r="R445" s="3" t="n"/>
+      <c r="T445" s="2" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n"/>
@@ -5495,6 +5945,7 @@
       <c r="P446" s="2" t="n"/>
       <c r="Q446" s="2" t="n"/>
       <c r="R446" s="3" t="n"/>
+      <c r="T446" s="2" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n"/>
@@ -5506,6 +5957,7 @@
       <c r="P447" s="2" t="n"/>
       <c r="Q447" s="2" t="n"/>
       <c r="R447" s="3" t="n"/>
+      <c r="T447" s="2" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n"/>
@@ -5517,6 +5969,7 @@
       <c r="P448" s="2" t="n"/>
       <c r="Q448" s="2" t="n"/>
       <c r="R448" s="3" t="n"/>
+      <c r="T448" s="2" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n"/>
@@ -5528,6 +5981,7 @@
       <c r="P449" s="2" t="n"/>
       <c r="Q449" s="2" t="n"/>
       <c r="R449" s="3" t="n"/>
+      <c r="T449" s="2" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n"/>
@@ -5539,6 +5993,7 @@
       <c r="P450" s="2" t="n"/>
       <c r="Q450" s="2" t="n"/>
       <c r="R450" s="3" t="n"/>
+      <c r="T450" s="2" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n"/>
@@ -5550,6 +6005,7 @@
       <c r="P451" s="2" t="n"/>
       <c r="Q451" s="2" t="n"/>
       <c r="R451" s="3" t="n"/>
+      <c r="T451" s="2" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n"/>
@@ -5561,6 +6017,7 @@
       <c r="P452" s="2" t="n"/>
       <c r="Q452" s="2" t="n"/>
       <c r="R452" s="3" t="n"/>
+      <c r="T452" s="2" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n"/>
@@ -5572,6 +6029,7 @@
       <c r="P453" s="2" t="n"/>
       <c r="Q453" s="2" t="n"/>
       <c r="R453" s="3" t="n"/>
+      <c r="T453" s="2" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n"/>
@@ -5583,6 +6041,7 @@
       <c r="P454" s="2" t="n"/>
       <c r="Q454" s="2" t="n"/>
       <c r="R454" s="3" t="n"/>
+      <c r="T454" s="2" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n"/>
@@ -5594,6 +6053,7 @@
       <c r="P455" s="2" t="n"/>
       <c r="Q455" s="2" t="n"/>
       <c r="R455" s="3" t="n"/>
+      <c r="T455" s="2" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n"/>
@@ -5605,6 +6065,7 @@
       <c r="P456" s="2" t="n"/>
       <c r="Q456" s="2" t="n"/>
       <c r="R456" s="3" t="n"/>
+      <c r="T456" s="2" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n"/>
@@ -5616,6 +6077,7 @@
       <c r="P457" s="2" t="n"/>
       <c r="Q457" s="2" t="n"/>
       <c r="R457" s="3" t="n"/>
+      <c r="T457" s="2" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n"/>
@@ -5627,6 +6089,7 @@
       <c r="P458" s="2" t="n"/>
       <c r="Q458" s="2" t="n"/>
       <c r="R458" s="3" t="n"/>
+      <c r="T458" s="2" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n"/>
@@ -5638,6 +6101,7 @@
       <c r="P459" s="2" t="n"/>
       <c r="Q459" s="2" t="n"/>
       <c r="R459" s="3" t="n"/>
+      <c r="T459" s="2" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n"/>
@@ -5649,6 +6113,7 @@
       <c r="P460" s="2" t="n"/>
       <c r="Q460" s="2" t="n"/>
       <c r="R460" s="3" t="n"/>
+      <c r="T460" s="2" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n"/>
@@ -5660,6 +6125,7 @@
       <c r="P461" s="2" t="n"/>
       <c r="Q461" s="2" t="n"/>
       <c r="R461" s="3" t="n"/>
+      <c r="T461" s="2" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n"/>
@@ -5671,6 +6137,7 @@
       <c r="P462" s="2" t="n"/>
       <c r="Q462" s="2" t="n"/>
       <c r="R462" s="3" t="n"/>
+      <c r="T462" s="2" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n"/>
@@ -5682,6 +6149,7 @@
       <c r="P463" s="2" t="n"/>
       <c r="Q463" s="2" t="n"/>
       <c r="R463" s="3" t="n"/>
+      <c r="T463" s="2" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n"/>
@@ -5693,6 +6161,7 @@
       <c r="P464" s="2" t="n"/>
       <c r="Q464" s="2" t="n"/>
       <c r="R464" s="3" t="n"/>
+      <c r="T464" s="2" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n"/>
@@ -5704,6 +6173,7 @@
       <c r="P465" s="2" t="n"/>
       <c r="Q465" s="2" t="n"/>
       <c r="R465" s="3" t="n"/>
+      <c r="T465" s="2" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n"/>
@@ -5715,6 +6185,7 @@
       <c r="P466" s="2" t="n"/>
       <c r="Q466" s="2" t="n"/>
       <c r="R466" s="3" t="n"/>
+      <c r="T466" s="2" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n"/>
@@ -5726,6 +6197,7 @@
       <c r="P467" s="2" t="n"/>
       <c r="Q467" s="2" t="n"/>
       <c r="R467" s="3" t="n"/>
+      <c r="T467" s="2" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n"/>
@@ -5737,6 +6209,7 @@
       <c r="P468" s="2" t="n"/>
       <c r="Q468" s="2" t="n"/>
       <c r="R468" s="3" t="n"/>
+      <c r="T468" s="2" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n"/>
@@ -5748,6 +6221,7 @@
       <c r="P469" s="2" t="n"/>
       <c r="Q469" s="2" t="n"/>
       <c r="R469" s="3" t="n"/>
+      <c r="T469" s="2" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n"/>
@@ -5759,6 +6233,7 @@
       <c r="P470" s="2" t="n"/>
       <c r="Q470" s="2" t="n"/>
       <c r="R470" s="3" t="n"/>
+      <c r="T470" s="2" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n"/>
@@ -5770,6 +6245,7 @@
       <c r="P471" s="2" t="n"/>
       <c r="Q471" s="2" t="n"/>
       <c r="R471" s="3" t="n"/>
+      <c r="T471" s="2" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n"/>
@@ -5781,6 +6257,7 @@
       <c r="P472" s="2" t="n"/>
       <c r="Q472" s="2" t="n"/>
       <c r="R472" s="3" t="n"/>
+      <c r="T472" s="2" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n"/>
@@ -5792,6 +6269,7 @@
       <c r="P473" s="2" t="n"/>
       <c r="Q473" s="2" t="n"/>
       <c r="R473" s="3" t="n"/>
+      <c r="T473" s="2" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n"/>
@@ -5803,6 +6281,7 @@
       <c r="P474" s="2" t="n"/>
       <c r="Q474" s="2" t="n"/>
       <c r="R474" s="3" t="n"/>
+      <c r="T474" s="2" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n"/>
@@ -5814,6 +6293,7 @@
       <c r="P475" s="2" t="n"/>
       <c r="Q475" s="2" t="n"/>
       <c r="R475" s="3" t="n"/>
+      <c r="T475" s="2" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n"/>
@@ -5825,6 +6305,7 @@
       <c r="P476" s="2" t="n"/>
       <c r="Q476" s="2" t="n"/>
       <c r="R476" s="3" t="n"/>
+      <c r="T476" s="2" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n"/>
@@ -5836,6 +6317,7 @@
       <c r="P477" s="2" t="n"/>
       <c r="Q477" s="2" t="n"/>
       <c r="R477" s="3" t="n"/>
+      <c r="T477" s="2" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n"/>
@@ -5847,6 +6329,7 @@
       <c r="P478" s="2" t="n"/>
       <c r="Q478" s="2" t="n"/>
       <c r="R478" s="3" t="n"/>
+      <c r="T478" s="2" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n"/>
@@ -5858,6 +6341,7 @@
       <c r="P479" s="2" t="n"/>
       <c r="Q479" s="2" t="n"/>
       <c r="R479" s="3" t="n"/>
+      <c r="T479" s="2" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n"/>
@@ -5869,6 +6353,7 @@
       <c r="P480" s="2" t="n"/>
       <c r="Q480" s="2" t="n"/>
       <c r="R480" s="3" t="n"/>
+      <c r="T480" s="2" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n"/>
@@ -5880,6 +6365,7 @@
       <c r="P481" s="2" t="n"/>
       <c r="Q481" s="2" t="n"/>
       <c r="R481" s="3" t="n"/>
+      <c r="T481" s="2" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n"/>
@@ -5891,6 +6377,7 @@
       <c r="P482" s="2" t="n"/>
       <c r="Q482" s="2" t="n"/>
       <c r="R482" s="3" t="n"/>
+      <c r="T482" s="2" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n"/>
@@ -5902,6 +6389,7 @@
       <c r="P483" s="2" t="n"/>
       <c r="Q483" s="2" t="n"/>
       <c r="R483" s="3" t="n"/>
+      <c r="T483" s="2" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n"/>
@@ -5913,6 +6401,7 @@
       <c r="P484" s="2" t="n"/>
       <c r="Q484" s="2" t="n"/>
       <c r="R484" s="3" t="n"/>
+      <c r="T484" s="2" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n"/>
@@ -5924,6 +6413,7 @@
       <c r="P485" s="2" t="n"/>
       <c r="Q485" s="2" t="n"/>
       <c r="R485" s="3" t="n"/>
+      <c r="T485" s="2" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n"/>
@@ -5935,6 +6425,7 @@
       <c r="P486" s="2" t="n"/>
       <c r="Q486" s="2" t="n"/>
       <c r="R486" s="3" t="n"/>
+      <c r="T486" s="2" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n"/>
@@ -5946,6 +6437,7 @@
       <c r="P487" s="2" t="n"/>
       <c r="Q487" s="2" t="n"/>
       <c r="R487" s="3" t="n"/>
+      <c r="T487" s="2" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n"/>
@@ -5957,6 +6449,7 @@
       <c r="P488" s="2" t="n"/>
       <c r="Q488" s="2" t="n"/>
       <c r="R488" s="3" t="n"/>
+      <c r="T488" s="2" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n"/>
@@ -5968,6 +6461,7 @@
       <c r="P489" s="2" t="n"/>
       <c r="Q489" s="2" t="n"/>
       <c r="R489" s="3" t="n"/>
+      <c r="T489" s="2" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n"/>
@@ -5979,6 +6473,7 @@
       <c r="P490" s="2" t="n"/>
       <c r="Q490" s="2" t="n"/>
       <c r="R490" s="3" t="n"/>
+      <c r="T490" s="2" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n"/>
@@ -5990,6 +6485,7 @@
       <c r="P491" s="2" t="n"/>
       <c r="Q491" s="2" t="n"/>
       <c r="R491" s="3" t="n"/>
+      <c r="T491" s="2" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n"/>
@@ -6001,6 +6497,7 @@
       <c r="P492" s="2" t="n"/>
       <c r="Q492" s="2" t="n"/>
       <c r="R492" s="3" t="n"/>
+      <c r="T492" s="2" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n"/>
@@ -6012,6 +6509,7 @@
       <c r="P493" s="2" t="n"/>
       <c r="Q493" s="2" t="n"/>
       <c r="R493" s="3" t="n"/>
+      <c r="T493" s="2" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n"/>
@@ -6023,6 +6521,7 @@
       <c r="P494" s="2" t="n"/>
       <c r="Q494" s="2" t="n"/>
       <c r="R494" s="3" t="n"/>
+      <c r="T494" s="2" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n"/>
@@ -6034,6 +6533,7 @@
       <c r="P495" s="2" t="n"/>
       <c r="Q495" s="2" t="n"/>
       <c r="R495" s="3" t="n"/>
+      <c r="T495" s="2" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n"/>
@@ -6045,6 +6545,7 @@
       <c r="P496" s="2" t="n"/>
       <c r="Q496" s="2" t="n"/>
       <c r="R496" s="3" t="n"/>
+      <c r="T496" s="2" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n"/>
@@ -6056,6 +6557,7 @@
       <c r="P497" s="2" t="n"/>
       <c r="Q497" s="2" t="n"/>
       <c r="R497" s="3" t="n"/>
+      <c r="T497" s="2" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n"/>
@@ -6067,6 +6569,7 @@
       <c r="P498" s="2" t="n"/>
       <c r="Q498" s="2" t="n"/>
       <c r="R498" s="3" t="n"/>
+      <c r="T498" s="2" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n"/>
@@ -6078,6 +6581,7 @@
       <c r="P499" s="2" t="n"/>
       <c r="Q499" s="2" t="n"/>
       <c r="R499" s="3" t="n"/>
+      <c r="T499" s="2" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n"/>
@@ -6089,6 +6593,7 @@
       <c r="P500" s="2" t="n"/>
       <c r="Q500" s="2" t="n"/>
       <c r="R500" s="3" t="n"/>
+      <c r="T500" s="2" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n"/>
@@ -6100,6 +6605,7 @@
       <c r="P501" s="2" t="n"/>
       <c r="Q501" s="2" t="n"/>
       <c r="R501" s="3" t="n"/>
+      <c r="T501" s="2" t="n"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="n"/>
@@ -6111,6 +6617,7 @@
       <c r="P502" s="2" t="n"/>
       <c r="Q502" s="2" t="n"/>
       <c r="R502" s="3" t="n"/>
+      <c r="T502" s="2" t="n"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="n"/>
@@ -6122,6 +6629,7 @@
       <c r="P503" s="2" t="n"/>
       <c r="Q503" s="2" t="n"/>
       <c r="R503" s="3" t="n"/>
+      <c r="T503" s="2" t="n"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="n"/>
@@ -6133,6 +6641,7 @@
       <c r="P504" s="2" t="n"/>
       <c r="Q504" s="2" t="n"/>
       <c r="R504" s="3" t="n"/>
+      <c r="T504" s="2" t="n"/>
     </row>
     <row r="505">
       <c r="A505" s="2" t="n"/>
@@ -6144,6 +6653,7 @@
       <c r="P505" s="2" t="n"/>
       <c r="Q505" s="2" t="n"/>
       <c r="R505" s="3" t="n"/>
+      <c r="T505" s="2" t="n"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n"/>
@@ -6155,6 +6665,7 @@
       <c r="P506" s="2" t="n"/>
       <c r="Q506" s="2" t="n"/>
       <c r="R506" s="3" t="n"/>
+      <c r="T506" s="2" t="n"/>
     </row>
     <row r="507">
       <c r="A507" s="2" t="n"/>
@@ -6166,6 +6677,7 @@
       <c r="P507" s="2" t="n"/>
       <c r="Q507" s="2" t="n"/>
       <c r="R507" s="3" t="n"/>
+      <c r="T507" s="2" t="n"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="n"/>
@@ -6177,6 +6689,7 @@
       <c r="P508" s="2" t="n"/>
       <c r="Q508" s="2" t="n"/>
       <c r="R508" s="3" t="n"/>
+      <c r="T508" s="2" t="n"/>
     </row>
     <row r="509">
       <c r="A509" s="2" t="n"/>
@@ -6188,6 +6701,7 @@
       <c r="P509" s="2" t="n"/>
       <c r="Q509" s="2" t="n"/>
       <c r="R509" s="3" t="n"/>
+      <c r="T509" s="2" t="n"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="n"/>
@@ -6199,6 +6713,7 @@
       <c r="P510" s="2" t="n"/>
       <c r="Q510" s="2" t="n"/>
       <c r="R510" s="3" t="n"/>
+      <c r="T510" s="2" t="n"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="n"/>
@@ -6210,6 +6725,7 @@
       <c r="P511" s="2" t="n"/>
       <c r="Q511" s="2" t="n"/>
       <c r="R511" s="3" t="n"/>
+      <c r="T511" s="2" t="n"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="n"/>
@@ -6221,6 +6737,7 @@
       <c r="P512" s="2" t="n"/>
       <c r="Q512" s="2" t="n"/>
       <c r="R512" s="3" t="n"/>
+      <c r="T512" s="2" t="n"/>
     </row>
     <row r="513">
       <c r="A513" s="2" t="n"/>
@@ -6232,6 +6749,7 @@
       <c r="P513" s="2" t="n"/>
       <c r="Q513" s="2" t="n"/>
       <c r="R513" s="3" t="n"/>
+      <c r="T513" s="2" t="n"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="n"/>
@@ -6243,6 +6761,7 @@
       <c r="P514" s="2" t="n"/>
       <c r="Q514" s="2" t="n"/>
       <c r="R514" s="3" t="n"/>
+      <c r="T514" s="2" t="n"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="n"/>
@@ -6254,6 +6773,7 @@
       <c r="P515" s="2" t="n"/>
       <c r="Q515" s="2" t="n"/>
       <c r="R515" s="3" t="n"/>
+      <c r="T515" s="2" t="n"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="n"/>
@@ -6265,6 +6785,7 @@
       <c r="P516" s="2" t="n"/>
       <c r="Q516" s="2" t="n"/>
       <c r="R516" s="3" t="n"/>
+      <c r="T516" s="2" t="n"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="n"/>
@@ -6276,6 +6797,7 @@
       <c r="P517" s="2" t="n"/>
       <c r="Q517" s="2" t="n"/>
       <c r="R517" s="3" t="n"/>
+      <c r="T517" s="2" t="n"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="n"/>
@@ -6287,6 +6809,7 @@
       <c r="P518" s="2" t="n"/>
       <c r="Q518" s="2" t="n"/>
       <c r="R518" s="3" t="n"/>
+      <c r="T518" s="2" t="n"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="n"/>
@@ -6298,6 +6821,7 @@
       <c r="P519" s="2" t="n"/>
       <c r="Q519" s="2" t="n"/>
       <c r="R519" s="3" t="n"/>
+      <c r="T519" s="2" t="n"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="n"/>
@@ -6309,6 +6833,7 @@
       <c r="P520" s="2" t="n"/>
       <c r="Q520" s="2" t="n"/>
       <c r="R520" s="3" t="n"/>
+      <c r="T520" s="2" t="n"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="n"/>
@@ -6320,6 +6845,7 @@
       <c r="P521" s="2" t="n"/>
       <c r="Q521" s="2" t="n"/>
       <c r="R521" s="3" t="n"/>
+      <c r="T521" s="2" t="n"/>
     </row>
     <row r="522">
       <c r="A522" s="2" t="n"/>
@@ -6331,6 +6857,7 @@
       <c r="P522" s="2" t="n"/>
       <c r="Q522" s="2" t="n"/>
       <c r="R522" s="3" t="n"/>
+      <c r="T522" s="2" t="n"/>
     </row>
     <row r="523">
       <c r="A523" s="2" t="n"/>
@@ -6342,6 +6869,7 @@
       <c r="P523" s="2" t="n"/>
       <c r="Q523" s="2" t="n"/>
       <c r="R523" s="3" t="n"/>
+      <c r="T523" s="2" t="n"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="n"/>
@@ -6353,6 +6881,7 @@
       <c r="P524" s="2" t="n"/>
       <c r="Q524" s="2" t="n"/>
       <c r="R524" s="3" t="n"/>
+      <c r="T524" s="2" t="n"/>
     </row>
     <row r="525">
       <c r="A525" s="2" t="n"/>
@@ -6364,6 +6893,7 @@
       <c r="P525" s="2" t="n"/>
       <c r="Q525" s="2" t="n"/>
       <c r="R525" s="3" t="n"/>
+      <c r="T525" s="2" t="n"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="n"/>
@@ -6375,6 +6905,7 @@
       <c r="P526" s="2" t="n"/>
       <c r="Q526" s="2" t="n"/>
       <c r="R526" s="3" t="n"/>
+      <c r="T526" s="2" t="n"/>
     </row>
     <row r="527">
       <c r="A527" s="2" t="n"/>
@@ -6386,6 +6917,7 @@
       <c r="P527" s="2" t="n"/>
       <c r="Q527" s="2" t="n"/>
       <c r="R527" s="3" t="n"/>
+      <c r="T527" s="2" t="n"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="n"/>
@@ -6397,6 +6929,7 @@
       <c r="P528" s="2" t="n"/>
       <c r="Q528" s="2" t="n"/>
       <c r="R528" s="3" t="n"/>
+      <c r="T528" s="2" t="n"/>
     </row>
     <row r="529">
       <c r="A529" s="2" t="n"/>
@@ -6408,6 +6941,7 @@
       <c r="P529" s="2" t="n"/>
       <c r="Q529" s="2" t="n"/>
       <c r="R529" s="3" t="n"/>
+      <c r="T529" s="2" t="n"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="n"/>
@@ -6419,6 +6953,7 @@
       <c r="P530" s="2" t="n"/>
       <c r="Q530" s="2" t="n"/>
       <c r="R530" s="3" t="n"/>
+      <c r="T530" s="2" t="n"/>
     </row>
     <row r="531">
       <c r="A531" s="2" t="n"/>
@@ -6430,6 +6965,7 @@
       <c r="P531" s="2" t="n"/>
       <c r="Q531" s="2" t="n"/>
       <c r="R531" s="3" t="n"/>
+      <c r="T531" s="2" t="n"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="n"/>
@@ -6441,6 +6977,7 @@
       <c r="P532" s="2" t="n"/>
       <c r="Q532" s="2" t="n"/>
       <c r="R532" s="3" t="n"/>
+      <c r="T532" s="2" t="n"/>
     </row>
     <row r="533">
       <c r="A533" s="2" t="n"/>
@@ -6452,6 +6989,7 @@
       <c r="P533" s="2" t="n"/>
       <c r="Q533" s="2" t="n"/>
       <c r="R533" s="3" t="n"/>
+      <c r="T533" s="2" t="n"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="n"/>
@@ -6463,6 +7001,7 @@
       <c r="P534" s="2" t="n"/>
       <c r="Q534" s="2" t="n"/>
       <c r="R534" s="3" t="n"/>
+      <c r="T534" s="2" t="n"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="n"/>
@@ -6474,6 +7013,7 @@
       <c r="P535" s="2" t="n"/>
       <c r="Q535" s="2" t="n"/>
       <c r="R535" s="3" t="n"/>
+      <c r="T535" s="2" t="n"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="n"/>
@@ -6485,6 +7025,7 @@
       <c r="P536" s="2" t="n"/>
       <c r="Q536" s="2" t="n"/>
       <c r="R536" s="3" t="n"/>
+      <c r="T536" s="2" t="n"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="n"/>
@@ -6496,6 +7037,7 @@
       <c r="P537" s="2" t="n"/>
       <c r="Q537" s="2" t="n"/>
       <c r="R537" s="3" t="n"/>
+      <c r="T537" s="2" t="n"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="n"/>
@@ -6507,6 +7049,7 @@
       <c r="P538" s="2" t="n"/>
       <c r="Q538" s="2" t="n"/>
       <c r="R538" s="3" t="n"/>
+      <c r="T538" s="2" t="n"/>
     </row>
     <row r="539">
       <c r="A539" s="2" t="n"/>
@@ -6518,6 +7061,7 @@
       <c r="P539" s="2" t="n"/>
       <c r="Q539" s="2" t="n"/>
       <c r="R539" s="3" t="n"/>
+      <c r="T539" s="2" t="n"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="n"/>
@@ -6529,6 +7073,7 @@
       <c r="P540" s="2" t="n"/>
       <c r="Q540" s="2" t="n"/>
       <c r="R540" s="3" t="n"/>
+      <c r="T540" s="2" t="n"/>
     </row>
     <row r="541">
       <c r="A541" s="2" t="n"/>
@@ -6540,6 +7085,7 @@
       <c r="P541" s="2" t="n"/>
       <c r="Q541" s="2" t="n"/>
       <c r="R541" s="3" t="n"/>
+      <c r="T541" s="2" t="n"/>
     </row>
     <row r="542">
       <c r="A542" s="2" t="n"/>
@@ -6551,6 +7097,7 @@
       <c r="P542" s="2" t="n"/>
       <c r="Q542" s="2" t="n"/>
       <c r="R542" s="3" t="n"/>
+      <c r="T542" s="2" t="n"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="n"/>
@@ -6562,6 +7109,7 @@
       <c r="P543" s="2" t="n"/>
       <c r="Q543" s="2" t="n"/>
       <c r="R543" s="3" t="n"/>
+      <c r="T543" s="2" t="n"/>
     </row>
     <row r="544">
       <c r="A544" s="2" t="n"/>
@@ -6573,6 +7121,7 @@
       <c r="P544" s="2" t="n"/>
       <c r="Q544" s="2" t="n"/>
       <c r="R544" s="3" t="n"/>
+      <c r="T544" s="2" t="n"/>
     </row>
     <row r="545">
       <c r="A545" s="2" t="n"/>
@@ -6584,6 +7133,7 @@
       <c r="P545" s="2" t="n"/>
       <c r="Q545" s="2" t="n"/>
       <c r="R545" s="3" t="n"/>
+      <c r="T545" s="2" t="n"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="n"/>
@@ -6595,6 +7145,7 @@
       <c r="P546" s="2" t="n"/>
       <c r="Q546" s="2" t="n"/>
       <c r="R546" s="3" t="n"/>
+      <c r="T546" s="2" t="n"/>
     </row>
     <row r="547">
       <c r="A547" s="2" t="n"/>
@@ -6606,6 +7157,7 @@
       <c r="P547" s="2" t="n"/>
       <c r="Q547" s="2" t="n"/>
       <c r="R547" s="3" t="n"/>
+      <c r="T547" s="2" t="n"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="n"/>
@@ -6617,6 +7169,7 @@
       <c r="P548" s="2" t="n"/>
       <c r="Q548" s="2" t="n"/>
       <c r="R548" s="3" t="n"/>
+      <c r="T548" s="2" t="n"/>
     </row>
     <row r="549">
       <c r="A549" s="2" t="n"/>
@@ -6628,6 +7181,7 @@
       <c r="P549" s="2" t="n"/>
       <c r="Q549" s="2" t="n"/>
       <c r="R549" s="3" t="n"/>
+      <c r="T549" s="2" t="n"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="n"/>
@@ -6639,6 +7193,7 @@
       <c r="P550" s="2" t="n"/>
       <c r="Q550" s="2" t="n"/>
       <c r="R550" s="3" t="n"/>
+      <c r="T550" s="2" t="n"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="n"/>
@@ -6650,6 +7205,7 @@
       <c r="P551" s="2" t="n"/>
       <c r="Q551" s="2" t="n"/>
       <c r="R551" s="3" t="n"/>
+      <c r="T551" s="2" t="n"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="n"/>
@@ -6661,6 +7217,7 @@
       <c r="P552" s="2" t="n"/>
       <c r="Q552" s="2" t="n"/>
       <c r="R552" s="3" t="n"/>
+      <c r="T552" s="2" t="n"/>
     </row>
     <row r="553">
       <c r="A553" s="2" t="n"/>
@@ -6672,6 +7229,7 @@
       <c r="P553" s="2" t="n"/>
       <c r="Q553" s="2" t="n"/>
       <c r="R553" s="3" t="n"/>
+      <c r="T553" s="2" t="n"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="n"/>
@@ -6683,6 +7241,7 @@
       <c r="P554" s="2" t="n"/>
       <c r="Q554" s="2" t="n"/>
       <c r="R554" s="3" t="n"/>
+      <c r="T554" s="2" t="n"/>
     </row>
     <row r="555">
       <c r="A555" s="2" t="n"/>
@@ -6694,6 +7253,7 @@
       <c r="P555" s="2" t="n"/>
       <c r="Q555" s="2" t="n"/>
       <c r="R555" s="3" t="n"/>
+      <c r="T555" s="2" t="n"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="n"/>
@@ -6705,6 +7265,7 @@
       <c r="P556" s="2" t="n"/>
       <c r="Q556" s="2" t="n"/>
       <c r="R556" s="3" t="n"/>
+      <c r="T556" s="2" t="n"/>
     </row>
     <row r="557">
       <c r="A557" s="2" t="n"/>
@@ -6716,6 +7277,7 @@
       <c r="P557" s="2" t="n"/>
       <c r="Q557" s="2" t="n"/>
       <c r="R557" s="3" t="n"/>
+      <c r="T557" s="2" t="n"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="n"/>
@@ -6727,6 +7289,7 @@
       <c r="P558" s="2" t="n"/>
       <c r="Q558" s="2" t="n"/>
       <c r="R558" s="3" t="n"/>
+      <c r="T558" s="2" t="n"/>
     </row>
     <row r="559">
       <c r="A559" s="2" t="n"/>
@@ -6738,6 +7301,7 @@
       <c r="P559" s="2" t="n"/>
       <c r="Q559" s="2" t="n"/>
       <c r="R559" s="3" t="n"/>
+      <c r="T559" s="2" t="n"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="n"/>
@@ -6749,6 +7313,7 @@
       <c r="P560" s="2" t="n"/>
       <c r="Q560" s="2" t="n"/>
       <c r="R560" s="3" t="n"/>
+      <c r="T560" s="2" t="n"/>
     </row>
     <row r="561">
       <c r="A561" s="2" t="n"/>
@@ -6760,6 +7325,7 @@
       <c r="P561" s="2" t="n"/>
       <c r="Q561" s="2" t="n"/>
       <c r="R561" s="3" t="n"/>
+      <c r="T561" s="2" t="n"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="n"/>
@@ -6771,6 +7337,7 @@
       <c r="P562" s="2" t="n"/>
       <c r="Q562" s="2" t="n"/>
       <c r="R562" s="3" t="n"/>
+      <c r="T562" s="2" t="n"/>
     </row>
     <row r="563">
       <c r="A563" s="2" t="n"/>
@@ -6782,6 +7349,7 @@
       <c r="P563" s="2" t="n"/>
       <c r="Q563" s="2" t="n"/>
       <c r="R563" s="3" t="n"/>
+      <c r="T563" s="2" t="n"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="n"/>
@@ -6793,6 +7361,7 @@
       <c r="P564" s="2" t="n"/>
       <c r="Q564" s="2" t="n"/>
       <c r="R564" s="3" t="n"/>
+      <c r="T564" s="2" t="n"/>
     </row>
     <row r="565">
       <c r="A565" s="2" t="n"/>
@@ -6804,6 +7373,7 @@
       <c r="P565" s="2" t="n"/>
       <c r="Q565" s="2" t="n"/>
       <c r="R565" s="3" t="n"/>
+      <c r="T565" s="2" t="n"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="n"/>
@@ -6815,6 +7385,7 @@
       <c r="P566" s="2" t="n"/>
       <c r="Q566" s="2" t="n"/>
       <c r="R566" s="3" t="n"/>
+      <c r="T566" s="2" t="n"/>
     </row>
     <row r="567">
       <c r="A567" s="2" t="n"/>
@@ -6826,6 +7397,7 @@
       <c r="P567" s="2" t="n"/>
       <c r="Q567" s="2" t="n"/>
       <c r="R567" s="3" t="n"/>
+      <c r="T567" s="2" t="n"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="n"/>
@@ -6837,6 +7409,7 @@
       <c r="P568" s="2" t="n"/>
       <c r="Q568" s="2" t="n"/>
       <c r="R568" s="3" t="n"/>
+      <c r="T568" s="2" t="n"/>
     </row>
     <row r="569">
       <c r="A569" s="2" t="n"/>
@@ -6848,6 +7421,7 @@
       <c r="P569" s="2" t="n"/>
       <c r="Q569" s="2" t="n"/>
       <c r="R569" s="3" t="n"/>
+      <c r="T569" s="2" t="n"/>
     </row>
     <row r="570">
       <c r="A570" s="2" t="n"/>
@@ -6859,6 +7433,7 @@
       <c r="P570" s="2" t="n"/>
       <c r="Q570" s="2" t="n"/>
       <c r="R570" s="3" t="n"/>
+      <c r="T570" s="2" t="n"/>
     </row>
     <row r="571">
       <c r="A571" s="2" t="n"/>
@@ -6870,6 +7445,7 @@
       <c r="P571" s="2" t="n"/>
       <c r="Q571" s="2" t="n"/>
       <c r="R571" s="3" t="n"/>
+      <c r="T571" s="2" t="n"/>
     </row>
     <row r="572">
       <c r="A572" s="2" t="n"/>
@@ -6881,6 +7457,7 @@
       <c r="P572" s="2" t="n"/>
       <c r="Q572" s="2" t="n"/>
       <c r="R572" s="3" t="n"/>
+      <c r="T572" s="2" t="n"/>
     </row>
     <row r="573">
       <c r="A573" s="2" t="n"/>
@@ -6892,6 +7469,7 @@
       <c r="P573" s="2" t="n"/>
       <c r="Q573" s="2" t="n"/>
       <c r="R573" s="3" t="n"/>
+      <c r="T573" s="2" t="n"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="n"/>
@@ -6903,6 +7481,7 @@
       <c r="P574" s="2" t="n"/>
       <c r="Q574" s="2" t="n"/>
       <c r="R574" s="3" t="n"/>
+      <c r="T574" s="2" t="n"/>
     </row>
     <row r="575">
       <c r="A575" s="2" t="n"/>
@@ -6914,6 +7493,7 @@
       <c r="P575" s="2" t="n"/>
       <c r="Q575" s="2" t="n"/>
       <c r="R575" s="3" t="n"/>
+      <c r="T575" s="2" t="n"/>
     </row>
     <row r="576">
       <c r="A576" s="2" t="n"/>
@@ -6925,6 +7505,7 @@
       <c r="P576" s="2" t="n"/>
       <c r="Q576" s="2" t="n"/>
       <c r="R576" s="3" t="n"/>
+      <c r="T576" s="2" t="n"/>
     </row>
     <row r="577">
       <c r="A577" s="2" t="n"/>
@@ -6936,6 +7517,7 @@
       <c r="P577" s="2" t="n"/>
       <c r="Q577" s="2" t="n"/>
       <c r="R577" s="3" t="n"/>
+      <c r="T577" s="2" t="n"/>
     </row>
     <row r="578">
       <c r="A578" s="2" t="n"/>
@@ -6947,6 +7529,7 @@
       <c r="P578" s="2" t="n"/>
       <c r="Q578" s="2" t="n"/>
       <c r="R578" s="3" t="n"/>
+      <c r="T578" s="2" t="n"/>
     </row>
     <row r="579">
       <c r="A579" s="2" t="n"/>
@@ -6958,6 +7541,7 @@
       <c r="P579" s="2" t="n"/>
       <c r="Q579" s="2" t="n"/>
       <c r="R579" s="3" t="n"/>
+      <c r="T579" s="2" t="n"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="n"/>
@@ -6969,6 +7553,7 @@
       <c r="P580" s="2" t="n"/>
       <c r="Q580" s="2" t="n"/>
       <c r="R580" s="3" t="n"/>
+      <c r="T580" s="2" t="n"/>
     </row>
     <row r="581">
       <c r="A581" s="2" t="n"/>
@@ -6980,6 +7565,7 @@
       <c r="P581" s="2" t="n"/>
       <c r="Q581" s="2" t="n"/>
       <c r="R581" s="3" t="n"/>
+      <c r="T581" s="2" t="n"/>
     </row>
     <row r="582">
       <c r="A582" s="2" t="n"/>
@@ -6991,6 +7577,7 @@
       <c r="P582" s="2" t="n"/>
       <c r="Q582" s="2" t="n"/>
       <c r="R582" s="3" t="n"/>
+      <c r="T582" s="2" t="n"/>
     </row>
     <row r="583">
       <c r="A583" s="2" t="n"/>
@@ -7002,6 +7589,7 @@
       <c r="P583" s="2" t="n"/>
       <c r="Q583" s="2" t="n"/>
       <c r="R583" s="3" t="n"/>
+      <c r="T583" s="2" t="n"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="n"/>
@@ -7013,6 +7601,7 @@
       <c r="P584" s="2" t="n"/>
       <c r="Q584" s="2" t="n"/>
       <c r="R584" s="3" t="n"/>
+      <c r="T584" s="2" t="n"/>
     </row>
     <row r="585">
       <c r="A585" s="2" t="n"/>
@@ -7024,6 +7613,7 @@
       <c r="P585" s="2" t="n"/>
       <c r="Q585" s="2" t="n"/>
       <c r="R585" s="3" t="n"/>
+      <c r="T585" s="2" t="n"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="n"/>
@@ -7035,6 +7625,7 @@
       <c r="P586" s="2" t="n"/>
       <c r="Q586" s="2" t="n"/>
       <c r="R586" s="3" t="n"/>
+      <c r="T586" s="2" t="n"/>
     </row>
     <row r="587">
       <c r="A587" s="2" t="n"/>
@@ -7046,6 +7637,7 @@
       <c r="P587" s="2" t="n"/>
       <c r="Q587" s="2" t="n"/>
       <c r="R587" s="3" t="n"/>
+      <c r="T587" s="2" t="n"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="n"/>
@@ -7057,6 +7649,7 @@
       <c r="P588" s="2" t="n"/>
       <c r="Q588" s="2" t="n"/>
       <c r="R588" s="3" t="n"/>
+      <c r="T588" s="2" t="n"/>
     </row>
     <row r="589">
       <c r="A589" s="2" t="n"/>
@@ -7068,6 +7661,7 @@
       <c r="P589" s="2" t="n"/>
       <c r="Q589" s="2" t="n"/>
       <c r="R589" s="3" t="n"/>
+      <c r="T589" s="2" t="n"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="n"/>
@@ -7079,6 +7673,7 @@
       <c r="P590" s="2" t="n"/>
       <c r="Q590" s="2" t="n"/>
       <c r="R590" s="3" t="n"/>
+      <c r="T590" s="2" t="n"/>
     </row>
     <row r="591">
       <c r="A591" s="2" t="n"/>
@@ -7090,6 +7685,7 @@
       <c r="P591" s="2" t="n"/>
       <c r="Q591" s="2" t="n"/>
       <c r="R591" s="3" t="n"/>
+      <c r="T591" s="2" t="n"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="n"/>
@@ -7101,6 +7697,7 @@
       <c r="P592" s="2" t="n"/>
       <c r="Q592" s="2" t="n"/>
       <c r="R592" s="3" t="n"/>
+      <c r="T592" s="2" t="n"/>
     </row>
     <row r="593">
       <c r="A593" s="2" t="n"/>
@@ -7112,6 +7709,7 @@
       <c r="P593" s="2" t="n"/>
       <c r="Q593" s="2" t="n"/>
       <c r="R593" s="3" t="n"/>
+      <c r="T593" s="2" t="n"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="n"/>
@@ -7123,6 +7721,7 @@
       <c r="P594" s="2" t="n"/>
       <c r="Q594" s="2" t="n"/>
       <c r="R594" s="3" t="n"/>
+      <c r="T594" s="2" t="n"/>
     </row>
     <row r="595">
       <c r="A595" s="2" t="n"/>
@@ -7134,6 +7733,7 @@
       <c r="P595" s="2" t="n"/>
       <c r="Q595" s="2" t="n"/>
       <c r="R595" s="3" t="n"/>
+      <c r="T595" s="2" t="n"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="n"/>
@@ -7145,6 +7745,7 @@
       <c r="P596" s="2" t="n"/>
       <c r="Q596" s="2" t="n"/>
       <c r="R596" s="3" t="n"/>
+      <c r="T596" s="2" t="n"/>
     </row>
     <row r="597">
       <c r="A597" s="2" t="n"/>
@@ -7156,6 +7757,7 @@
       <c r="P597" s="2" t="n"/>
       <c r="Q597" s="2" t="n"/>
       <c r="R597" s="3" t="n"/>
+      <c r="T597" s="2" t="n"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="n"/>
@@ -7167,6 +7769,7 @@
       <c r="P598" s="2" t="n"/>
       <c r="Q598" s="2" t="n"/>
       <c r="R598" s="3" t="n"/>
+      <c r="T598" s="2" t="n"/>
     </row>
     <row r="599">
       <c r="A599" s="2" t="n"/>
@@ -7178,6 +7781,7 @@
       <c r="P599" s="2" t="n"/>
       <c r="Q599" s="2" t="n"/>
       <c r="R599" s="3" t="n"/>
+      <c r="T599" s="2" t="n"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="n"/>
@@ -7189,6 +7793,7 @@
       <c r="P600" s="2" t="n"/>
       <c r="Q600" s="2" t="n"/>
       <c r="R600" s="3" t="n"/>
+      <c r="T600" s="2" t="n"/>
     </row>
     <row r="601">
       <c r="A601" s="2" t="n"/>
@@ -7200,6 +7805,7 @@
       <c r="P601" s="2" t="n"/>
       <c r="Q601" s="2" t="n"/>
       <c r="R601" s="3" t="n"/>
+      <c r="T601" s="2" t="n"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="n"/>
@@ -7211,6 +7817,7 @@
       <c r="P602" s="2" t="n"/>
       <c r="Q602" s="2" t="n"/>
       <c r="R602" s="3" t="n"/>
+      <c r="T602" s="2" t="n"/>
     </row>
     <row r="603">
       <c r="A603" s="2" t="n"/>
@@ -7222,6 +7829,7 @@
       <c r="P603" s="2" t="n"/>
       <c r="Q603" s="2" t="n"/>
       <c r="R603" s="3" t="n"/>
+      <c r="T603" s="2" t="n"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="n"/>
@@ -7233,6 +7841,7 @@
       <c r="P604" s="2" t="n"/>
       <c r="Q604" s="2" t="n"/>
       <c r="R604" s="3" t="n"/>
+      <c r="T604" s="2" t="n"/>
     </row>
     <row r="605">
       <c r="A605" s="2" t="n"/>
@@ -7244,6 +7853,7 @@
       <c r="P605" s="2" t="n"/>
       <c r="Q605" s="2" t="n"/>
       <c r="R605" s="3" t="n"/>
+      <c r="T605" s="2" t="n"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="n"/>
@@ -7255,6 +7865,7 @@
       <c r="P606" s="2" t="n"/>
       <c r="Q606" s="2" t="n"/>
       <c r="R606" s="3" t="n"/>
+      <c r="T606" s="2" t="n"/>
     </row>
     <row r="607">
       <c r="A607" s="2" t="n"/>
@@ -7266,6 +7877,7 @@
       <c r="P607" s="2" t="n"/>
       <c r="Q607" s="2" t="n"/>
       <c r="R607" s="3" t="n"/>
+      <c r="T607" s="2" t="n"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="n"/>
@@ -7277,6 +7889,7 @@
       <c r="P608" s="2" t="n"/>
       <c r="Q608" s="2" t="n"/>
       <c r="R608" s="3" t="n"/>
+      <c r="T608" s="2" t="n"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="n"/>
@@ -7288,6 +7901,7 @@
       <c r="P609" s="2" t="n"/>
       <c r="Q609" s="2" t="n"/>
       <c r="R609" s="3" t="n"/>
+      <c r="T609" s="2" t="n"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="n"/>
@@ -7299,6 +7913,7 @@
       <c r="P610" s="2" t="n"/>
       <c r="Q610" s="2" t="n"/>
       <c r="R610" s="3" t="n"/>
+      <c r="T610" s="2" t="n"/>
     </row>
     <row r="611">
       <c r="A611" s="2" t="n"/>
@@ -7310,6 +7925,7 @@
       <c r="P611" s="2" t="n"/>
       <c r="Q611" s="2" t="n"/>
       <c r="R611" s="3" t="n"/>
+      <c r="T611" s="2" t="n"/>
     </row>
     <row r="612">
       <c r="A612" s="2" t="n"/>
@@ -7321,6 +7937,7 @@
       <c r="P612" s="2" t="n"/>
       <c r="Q612" s="2" t="n"/>
       <c r="R612" s="3" t="n"/>
+      <c r="T612" s="2" t="n"/>
     </row>
     <row r="613">
       <c r="A613" s="2" t="n"/>
@@ -7332,6 +7949,7 @@
       <c r="P613" s="2" t="n"/>
       <c r="Q613" s="2" t="n"/>
       <c r="R613" s="3" t="n"/>
+      <c r="T613" s="2" t="n"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="n"/>
@@ -7343,6 +7961,7 @@
       <c r="P614" s="2" t="n"/>
       <c r="Q614" s="2" t="n"/>
       <c r="R614" s="3" t="n"/>
+      <c r="T614" s="2" t="n"/>
     </row>
     <row r="615">
       <c r="A615" s="2" t="n"/>
@@ -7354,6 +7973,7 @@
       <c r="P615" s="2" t="n"/>
       <c r="Q615" s="2" t="n"/>
       <c r="R615" s="3" t="n"/>
+      <c r="T615" s="2" t="n"/>
     </row>
     <row r="616">
       <c r="A616" s="2" t="n"/>
@@ -7365,6 +7985,7 @@
       <c r="P616" s="2" t="n"/>
       <c r="Q616" s="2" t="n"/>
       <c r="R616" s="3" t="n"/>
+      <c r="T616" s="2" t="n"/>
     </row>
     <row r="617">
       <c r="A617" s="2" t="n"/>
@@ -7376,6 +7997,7 @@
       <c r="P617" s="2" t="n"/>
       <c r="Q617" s="2" t="n"/>
       <c r="R617" s="3" t="n"/>
+      <c r="T617" s="2" t="n"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="n"/>
@@ -7387,6 +8009,7 @@
       <c r="P618" s="2" t="n"/>
       <c r="Q618" s="2" t="n"/>
       <c r="R618" s="3" t="n"/>
+      <c r="T618" s="2" t="n"/>
     </row>
     <row r="619">
       <c r="A619" s="2" t="n"/>
@@ -7398,6 +8021,7 @@
       <c r="P619" s="2" t="n"/>
       <c r="Q619" s="2" t="n"/>
       <c r="R619" s="3" t="n"/>
+      <c r="T619" s="2" t="n"/>
     </row>
     <row r="620">
       <c r="A620" s="2" t="n"/>
@@ -7409,6 +8033,7 @@
       <c r="P620" s="2" t="n"/>
       <c r="Q620" s="2" t="n"/>
       <c r="R620" s="3" t="n"/>
+      <c r="T620" s="2" t="n"/>
     </row>
     <row r="621">
       <c r="A621" s="2" t="n"/>
@@ -7420,6 +8045,7 @@
       <c r="P621" s="2" t="n"/>
       <c r="Q621" s="2" t="n"/>
       <c r="R621" s="3" t="n"/>
+      <c r="T621" s="2" t="n"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="n"/>
@@ -7431,6 +8057,7 @@
       <c r="P622" s="2" t="n"/>
       <c r="Q622" s="2" t="n"/>
       <c r="R622" s="3" t="n"/>
+      <c r="T622" s="2" t="n"/>
     </row>
     <row r="623">
       <c r="A623" s="2" t="n"/>
@@ -7442,6 +8069,7 @@
       <c r="P623" s="2" t="n"/>
       <c r="Q623" s="2" t="n"/>
       <c r="R623" s="3" t="n"/>
+      <c r="T623" s="2" t="n"/>
     </row>
     <row r="624">
       <c r="A624" s="2" t="n"/>
@@ -7453,6 +8081,7 @@
       <c r="P624" s="2" t="n"/>
       <c r="Q624" s="2" t="n"/>
       <c r="R624" s="3" t="n"/>
+      <c r="T624" s="2" t="n"/>
     </row>
     <row r="625">
       <c r="A625" s="2" t="n"/>
@@ -7464,6 +8093,7 @@
       <c r="P625" s="2" t="n"/>
       <c r="Q625" s="2" t="n"/>
       <c r="R625" s="3" t="n"/>
+      <c r="T625" s="2" t="n"/>
     </row>
     <row r="626">
       <c r="A626" s="2" t="n"/>
@@ -7475,6 +8105,7 @@
       <c r="P626" s="2" t="n"/>
       <c r="Q626" s="2" t="n"/>
       <c r="R626" s="3" t="n"/>
+      <c r="T626" s="2" t="n"/>
     </row>
     <row r="627">
       <c r="A627" s="2" t="n"/>
@@ -7486,6 +8117,7 @@
       <c r="P627" s="2" t="n"/>
       <c r="Q627" s="2" t="n"/>
       <c r="R627" s="3" t="n"/>
+      <c r="T627" s="2" t="n"/>
     </row>
     <row r="628">
       <c r="A628" s="2" t="n"/>
@@ -7497,6 +8129,7 @@
       <c r="P628" s="2" t="n"/>
       <c r="Q628" s="2" t="n"/>
       <c r="R628" s="3" t="n"/>
+      <c r="T628" s="2" t="n"/>
     </row>
     <row r="629">
       <c r="A629" s="2" t="n"/>
@@ -7508,6 +8141,7 @@
       <c r="P629" s="2" t="n"/>
       <c r="Q629" s="2" t="n"/>
       <c r="R629" s="3" t="n"/>
+      <c r="T629" s="2" t="n"/>
     </row>
     <row r="630">
       <c r="A630" s="2" t="n"/>
@@ -7519,6 +8153,7 @@
       <c r="P630" s="2" t="n"/>
       <c r="Q630" s="2" t="n"/>
       <c r="R630" s="3" t="n"/>
+      <c r="T630" s="2" t="n"/>
     </row>
     <row r="631">
       <c r="A631" s="2" t="n"/>
@@ -7530,6 +8165,7 @@
       <c r="P631" s="2" t="n"/>
       <c r="Q631" s="2" t="n"/>
       <c r="R631" s="3" t="n"/>
+      <c r="T631" s="2" t="n"/>
     </row>
     <row r="632">
       <c r="A632" s="2" t="n"/>
@@ -7541,6 +8177,7 @@
       <c r="P632" s="2" t="n"/>
       <c r="Q632" s="2" t="n"/>
       <c r="R632" s="3" t="n"/>
+      <c r="T632" s="2" t="n"/>
     </row>
     <row r="633">
       <c r="A633" s="2" t="n"/>
@@ -7552,6 +8189,7 @@
       <c r="P633" s="2" t="n"/>
       <c r="Q633" s="2" t="n"/>
       <c r="R633" s="3" t="n"/>
+      <c r="T633" s="2" t="n"/>
     </row>
     <row r="634">
       <c r="A634" s="2" t="n"/>
@@ -7563,6 +8201,7 @@
       <c r="P634" s="2" t="n"/>
       <c r="Q634" s="2" t="n"/>
       <c r="R634" s="3" t="n"/>
+      <c r="T634" s="2" t="n"/>
     </row>
     <row r="635">
       <c r="A635" s="2" t="n"/>
@@ -7574,6 +8213,7 @@
       <c r="P635" s="2" t="n"/>
       <c r="Q635" s="2" t="n"/>
       <c r="R635" s="3" t="n"/>
+      <c r="T635" s="2" t="n"/>
     </row>
     <row r="636">
       <c r="A636" s="2" t="n"/>
@@ -7585,6 +8225,7 @@
       <c r="P636" s="2" t="n"/>
       <c r="Q636" s="2" t="n"/>
       <c r="R636" s="3" t="n"/>
+      <c r="T636" s="2" t="n"/>
     </row>
     <row r="637">
       <c r="A637" s="2" t="n"/>
@@ -7596,6 +8237,7 @@
       <c r="P637" s="2" t="n"/>
       <c r="Q637" s="2" t="n"/>
       <c r="R637" s="3" t="n"/>
+      <c r="T637" s="2" t="n"/>
     </row>
     <row r="638">
       <c r="A638" s="2" t="n"/>
@@ -7607,6 +8249,7 @@
       <c r="P638" s="2" t="n"/>
       <c r="Q638" s="2" t="n"/>
       <c r="R638" s="3" t="n"/>
+      <c r="T638" s="2" t="n"/>
     </row>
     <row r="639">
       <c r="A639" s="2" t="n"/>
@@ -7618,6 +8261,7 @@
       <c r="P639" s="2" t="n"/>
       <c r="Q639" s="2" t="n"/>
       <c r="R639" s="3" t="n"/>
+      <c r="T639" s="2" t="n"/>
     </row>
     <row r="640">
       <c r="A640" s="2" t="n"/>
@@ -7629,6 +8273,7 @@
       <c r="P640" s="2" t="n"/>
       <c r="Q640" s="2" t="n"/>
       <c r="R640" s="3" t="n"/>
+      <c r="T640" s="2" t="n"/>
     </row>
     <row r="641">
       <c r="A641" s="2" t="n"/>
@@ -7640,6 +8285,7 @@
       <c r="P641" s="2" t="n"/>
       <c r="Q641" s="2" t="n"/>
       <c r="R641" s="3" t="n"/>
+      <c r="T641" s="2" t="n"/>
     </row>
     <row r="642">
       <c r="A642" s="2" t="n"/>
@@ -7651,6 +8297,7 @@
       <c r="P642" s="2" t="n"/>
       <c r="Q642" s="2" t="n"/>
       <c r="R642" s="3" t="n"/>
+      <c r="T642" s="2" t="n"/>
     </row>
     <row r="643">
       <c r="A643" s="2" t="n"/>
@@ -7662,6 +8309,7 @@
       <c r="P643" s="2" t="n"/>
       <c r="Q643" s="2" t="n"/>
       <c r="R643" s="3" t="n"/>
+      <c r="T643" s="2" t="n"/>
     </row>
     <row r="644">
       <c r="A644" s="2" t="n"/>
@@ -7673,6 +8321,7 @@
       <c r="P644" s="2" t="n"/>
       <c r="Q644" s="2" t="n"/>
       <c r="R644" s="3" t="n"/>
+      <c r="T644" s="2" t="n"/>
     </row>
     <row r="645">
       <c r="A645" s="2" t="n"/>
@@ -7684,6 +8333,7 @@
       <c r="P645" s="2" t="n"/>
       <c r="Q645" s="2" t="n"/>
       <c r="R645" s="3" t="n"/>
+      <c r="T645" s="2" t="n"/>
     </row>
     <row r="646">
       <c r="A646" s="2" t="n"/>
@@ -7695,6 +8345,7 @@
       <c r="P646" s="2" t="n"/>
       <c r="Q646" s="2" t="n"/>
       <c r="R646" s="3" t="n"/>
+      <c r="T646" s="2" t="n"/>
     </row>
     <row r="647">
       <c r="A647" s="2" t="n"/>
@@ -7706,6 +8357,7 @@
       <c r="P647" s="2" t="n"/>
       <c r="Q647" s="2" t="n"/>
       <c r="R647" s="3" t="n"/>
+      <c r="T647" s="2" t="n"/>
     </row>
     <row r="648">
       <c r="A648" s="2" t="n"/>
@@ -7717,6 +8369,7 @@
       <c r="P648" s="2" t="n"/>
       <c r="Q648" s="2" t="n"/>
       <c r="R648" s="3" t="n"/>
+      <c r="T648" s="2" t="n"/>
     </row>
     <row r="649">
       <c r="A649" s="2" t="n"/>
@@ -7728,6 +8381,7 @@
       <c r="P649" s="2" t="n"/>
       <c r="Q649" s="2" t="n"/>
       <c r="R649" s="3" t="n"/>
+      <c r="T649" s="2" t="n"/>
     </row>
     <row r="650">
       <c r="A650" s="2" t="n"/>
@@ -7739,6 +8393,7 @@
       <c r="P650" s="2" t="n"/>
       <c r="Q650" s="2" t="n"/>
       <c r="R650" s="3" t="n"/>
+      <c r="T650" s="2" t="n"/>
     </row>
     <row r="651">
       <c r="A651" s="2" t="n"/>
@@ -7750,6 +8405,7 @@
       <c r="P651" s="2" t="n"/>
       <c r="Q651" s="2" t="n"/>
       <c r="R651" s="3" t="n"/>
+      <c r="T651" s="2" t="n"/>
     </row>
     <row r="652">
       <c r="A652" s="2" t="n"/>
@@ -7761,6 +8417,7 @@
       <c r="P652" s="2" t="n"/>
       <c r="Q652" s="2" t="n"/>
       <c r="R652" s="3" t="n"/>
+      <c r="T652" s="2" t="n"/>
     </row>
     <row r="653">
       <c r="A653" s="2" t="n"/>
@@ -7772,6 +8429,7 @@
       <c r="P653" s="2" t="n"/>
       <c r="Q653" s="2" t="n"/>
       <c r="R653" s="3" t="n"/>
+      <c r="T653" s="2" t="n"/>
     </row>
     <row r="654">
       <c r="A654" s="2" t="n"/>
@@ -7783,6 +8441,7 @@
       <c r="P654" s="2" t="n"/>
       <c r="Q654" s="2" t="n"/>
       <c r="R654" s="3" t="n"/>
+      <c r="T654" s="2" t="n"/>
     </row>
     <row r="655">
       <c r="A655" s="2" t="n"/>
@@ -7794,6 +8453,7 @@
       <c r="P655" s="2" t="n"/>
       <c r="Q655" s="2" t="n"/>
       <c r="R655" s="3" t="n"/>
+      <c r="T655" s="2" t="n"/>
     </row>
     <row r="656">
       <c r="A656" s="2" t="n"/>
@@ -7805,6 +8465,7 @@
       <c r="P656" s="2" t="n"/>
       <c r="Q656" s="2" t="n"/>
       <c r="R656" s="3" t="n"/>
+      <c r="T656" s="2" t="n"/>
     </row>
     <row r="657">
       <c r="A657" s="2" t="n"/>
@@ -7816,6 +8477,7 @@
       <c r="P657" s="2" t="n"/>
       <c r="Q657" s="2" t="n"/>
       <c r="R657" s="3" t="n"/>
+      <c r="T657" s="2" t="n"/>
     </row>
     <row r="658">
       <c r="A658" s="2" t="n"/>
@@ -7827,6 +8489,7 @@
       <c r="P658" s="2" t="n"/>
       <c r="Q658" s="2" t="n"/>
       <c r="R658" s="3" t="n"/>
+      <c r="T658" s="2" t="n"/>
     </row>
     <row r="659">
       <c r="A659" s="2" t="n"/>
@@ -7838,6 +8501,7 @@
       <c r="P659" s="2" t="n"/>
       <c r="Q659" s="2" t="n"/>
       <c r="R659" s="3" t="n"/>
+      <c r="T659" s="2" t="n"/>
     </row>
     <row r="660">
       <c r="A660" s="2" t="n"/>
@@ -7849,6 +8513,7 @@
       <c r="P660" s="2" t="n"/>
       <c r="Q660" s="2" t="n"/>
       <c r="R660" s="3" t="n"/>
+      <c r="T660" s="2" t="n"/>
     </row>
     <row r="661">
       <c r="A661" s="2" t="n"/>
@@ -7860,6 +8525,7 @@
       <c r="P661" s="2" t="n"/>
       <c r="Q661" s="2" t="n"/>
       <c r="R661" s="3" t="n"/>
+      <c r="T661" s="2" t="n"/>
     </row>
     <row r="662">
       <c r="A662" s="2" t="n"/>
@@ -7871,6 +8537,7 @@
       <c r="P662" s="2" t="n"/>
       <c r="Q662" s="2" t="n"/>
       <c r="R662" s="3" t="n"/>
+      <c r="T662" s="2" t="n"/>
     </row>
     <row r="663">
       <c r="A663" s="2" t="n"/>
@@ -7882,6 +8549,7 @@
       <c r="P663" s="2" t="n"/>
       <c r="Q663" s="2" t="n"/>
       <c r="R663" s="3" t="n"/>
+      <c r="T663" s="2" t="n"/>
     </row>
     <row r="664">
       <c r="A664" s="2" t="n"/>
@@ -7893,6 +8561,7 @@
       <c r="P664" s="2" t="n"/>
       <c r="Q664" s="2" t="n"/>
       <c r="R664" s="3" t="n"/>
+      <c r="T664" s="2" t="n"/>
     </row>
     <row r="665">
       <c r="A665" s="2" t="n"/>
@@ -7904,6 +8573,7 @@
       <c r="P665" s="2" t="n"/>
       <c r="Q665" s="2" t="n"/>
       <c r="R665" s="3" t="n"/>
+      <c r="T665" s="2" t="n"/>
     </row>
     <row r="666">
       <c r="A666" s="2" t="n"/>
@@ -7915,6 +8585,7 @@
       <c r="P666" s="2" t="n"/>
       <c r="Q666" s="2" t="n"/>
       <c r="R666" s="3" t="n"/>
+      <c r="T666" s="2" t="n"/>
     </row>
     <row r="667">
       <c r="A667" s="2" t="n"/>
@@ -7926,6 +8597,7 @@
       <c r="P667" s="2" t="n"/>
       <c r="Q667" s="2" t="n"/>
       <c r="R667" s="3" t="n"/>
+      <c r="T667" s="2" t="n"/>
     </row>
     <row r="668">
       <c r="A668" s="2" t="n"/>
@@ -7937,6 +8609,7 @@
       <c r="P668" s="2" t="n"/>
       <c r="Q668" s="2" t="n"/>
       <c r="R668" s="3" t="n"/>
+      <c r="T668" s="2" t="n"/>
     </row>
     <row r="669">
       <c r="A669" s="2" t="n"/>
@@ -7948,6 +8621,7 @@
       <c r="P669" s="2" t="n"/>
       <c r="Q669" s="2" t="n"/>
       <c r="R669" s="3" t="n"/>
+      <c r="T669" s="2" t="n"/>
     </row>
     <row r="670">
       <c r="A670" s="2" t="n"/>
@@ -7959,6 +8633,7 @@
       <c r="P670" s="2" t="n"/>
       <c r="Q670" s="2" t="n"/>
       <c r="R670" s="3" t="n"/>
+      <c r="T670" s="2" t="n"/>
     </row>
     <row r="671">
       <c r="A671" s="2" t="n"/>
@@ -7970,6 +8645,7 @@
       <c r="P671" s="2" t="n"/>
       <c r="Q671" s="2" t="n"/>
       <c r="R671" s="3" t="n"/>
+      <c r="T671" s="2" t="n"/>
     </row>
     <row r="672">
       <c r="A672" s="2" t="n"/>
@@ -7981,6 +8657,7 @@
       <c r="P672" s="2" t="n"/>
       <c r="Q672" s="2" t="n"/>
       <c r="R672" s="3" t="n"/>
+      <c r="T672" s="2" t="n"/>
     </row>
     <row r="673">
       <c r="A673" s="2" t="n"/>
@@ -7992,6 +8669,7 @@
       <c r="P673" s="2" t="n"/>
       <c r="Q673" s="2" t="n"/>
       <c r="R673" s="3" t="n"/>
+      <c r="T673" s="2" t="n"/>
     </row>
     <row r="674">
       <c r="A674" s="2" t="n"/>
@@ -8003,6 +8681,7 @@
       <c r="P674" s="2" t="n"/>
       <c r="Q674" s="2" t="n"/>
       <c r="R674" s="3" t="n"/>
+      <c r="T674" s="2" t="n"/>
     </row>
     <row r="675">
       <c r="A675" s="2" t="n"/>
@@ -8014,6 +8693,7 @@
       <c r="P675" s="2" t="n"/>
       <c r="Q675" s="2" t="n"/>
       <c r="R675" s="3" t="n"/>
+      <c r="T675" s="2" t="n"/>
     </row>
     <row r="676">
       <c r="A676" s="2" t="n"/>
@@ -8025,6 +8705,7 @@
       <c r="P676" s="2" t="n"/>
       <c r="Q676" s="2" t="n"/>
       <c r="R676" s="3" t="n"/>
+      <c r="T676" s="2" t="n"/>
     </row>
     <row r="677">
       <c r="A677" s="2" t="n"/>
@@ -8036,6 +8717,7 @@
       <c r="P677" s="2" t="n"/>
       <c r="Q677" s="2" t="n"/>
       <c r="R677" s="3" t="n"/>
+      <c r="T677" s="2" t="n"/>
     </row>
     <row r="678">
       <c r="A678" s="2" t="n"/>
@@ -8047,6 +8729,7 @@
       <c r="P678" s="2" t="n"/>
       <c r="Q678" s="2" t="n"/>
       <c r="R678" s="3" t="n"/>
+      <c r="T678" s="2" t="n"/>
     </row>
     <row r="679">
       <c r="A679" s="2" t="n"/>
@@ -8058,6 +8741,7 @@
       <c r="P679" s="2" t="n"/>
       <c r="Q679" s="2" t="n"/>
       <c r="R679" s="3" t="n"/>
+      <c r="T679" s="2" t="n"/>
     </row>
     <row r="680">
       <c r="A680" s="2" t="n"/>
@@ -8069,6 +8753,7 @@
       <c r="P680" s="2" t="n"/>
       <c r="Q680" s="2" t="n"/>
       <c r="R680" s="3" t="n"/>
+      <c r="T680" s="2" t="n"/>
     </row>
     <row r="681">
       <c r="A681" s="2" t="n"/>
@@ -8080,6 +8765,7 @@
       <c r="P681" s="2" t="n"/>
       <c r="Q681" s="2" t="n"/>
       <c r="R681" s="3" t="n"/>
+      <c r="T681" s="2" t="n"/>
     </row>
     <row r="682">
       <c r="A682" s="2" t="n"/>
@@ -8091,6 +8777,7 @@
       <c r="P682" s="2" t="n"/>
       <c r="Q682" s="2" t="n"/>
       <c r="R682" s="3" t="n"/>
+      <c r="T682" s="2" t="n"/>
     </row>
     <row r="683">
       <c r="A683" s="2" t="n"/>
@@ -8102,6 +8789,7 @@
       <c r="P683" s="2" t="n"/>
       <c r="Q683" s="2" t="n"/>
       <c r="R683" s="3" t="n"/>
+      <c r="T683" s="2" t="n"/>
     </row>
     <row r="684">
       <c r="A684" s="2" t="n"/>
@@ -8113,6 +8801,7 @@
       <c r="P684" s="2" t="n"/>
       <c r="Q684" s="2" t="n"/>
       <c r="R684" s="3" t="n"/>
+      <c r="T684" s="2" t="n"/>
     </row>
     <row r="685">
       <c r="A685" s="2" t="n"/>
@@ -8124,6 +8813,7 @@
       <c r="P685" s="2" t="n"/>
       <c r="Q685" s="2" t="n"/>
       <c r="R685" s="3" t="n"/>
+      <c r="T685" s="2" t="n"/>
     </row>
     <row r="686">
       <c r="A686" s="2" t="n"/>
@@ -8135,6 +8825,7 @@
       <c r="P686" s="2" t="n"/>
       <c r="Q686" s="2" t="n"/>
       <c r="R686" s="3" t="n"/>
+      <c r="T686" s="2" t="n"/>
     </row>
     <row r="687">
       <c r="A687" s="2" t="n"/>
@@ -8146,6 +8837,7 @@
       <c r="P687" s="2" t="n"/>
       <c r="Q687" s="2" t="n"/>
       <c r="R687" s="3" t="n"/>
+      <c r="T687" s="2" t="n"/>
     </row>
     <row r="688">
       <c r="A688" s="2" t="n"/>
@@ -8157,6 +8849,7 @@
       <c r="P688" s="2" t="n"/>
       <c r="Q688" s="2" t="n"/>
       <c r="R688" s="3" t="n"/>
+      <c r="T688" s="2" t="n"/>
     </row>
     <row r="689">
       <c r="A689" s="2" t="n"/>
@@ -8168,6 +8861,7 @@
       <c r="P689" s="2" t="n"/>
       <c r="Q689" s="2" t="n"/>
       <c r="R689" s="3" t="n"/>
+      <c r="T689" s="2" t="n"/>
     </row>
     <row r="690">
       <c r="A690" s="2" t="n"/>
@@ -8179,6 +8873,7 @@
       <c r="P690" s="2" t="n"/>
       <c r="Q690" s="2" t="n"/>
       <c r="R690" s="3" t="n"/>
+      <c r="T690" s="2" t="n"/>
     </row>
     <row r="691">
       <c r="A691" s="2" t="n"/>
@@ -8190,6 +8885,7 @@
       <c r="P691" s="2" t="n"/>
       <c r="Q691" s="2" t="n"/>
       <c r="R691" s="3" t="n"/>
+      <c r="T691" s="2" t="n"/>
     </row>
     <row r="692">
       <c r="A692" s="2" t="n"/>
@@ -8201,6 +8897,7 @@
       <c r="P692" s="2" t="n"/>
       <c r="Q692" s="2" t="n"/>
       <c r="R692" s="3" t="n"/>
+      <c r="T692" s="2" t="n"/>
     </row>
     <row r="693">
       <c r="A693" s="2" t="n"/>
@@ -8212,6 +8909,7 @@
       <c r="P693" s="2" t="n"/>
       <c r="Q693" s="2" t="n"/>
       <c r="R693" s="3" t="n"/>
+      <c r="T693" s="2" t="n"/>
     </row>
     <row r="694">
       <c r="A694" s="2" t="n"/>
@@ -8223,6 +8921,7 @@
       <c r="P694" s="2" t="n"/>
       <c r="Q694" s="2" t="n"/>
       <c r="R694" s="3" t="n"/>
+      <c r="T694" s="2" t="n"/>
     </row>
     <row r="695">
       <c r="A695" s="2" t="n"/>
@@ -8234,6 +8933,7 @@
       <c r="P695" s="2" t="n"/>
       <c r="Q695" s="2" t="n"/>
       <c r="R695" s="3" t="n"/>
+      <c r="T695" s="2" t="n"/>
     </row>
     <row r="696">
       <c r="A696" s="2" t="n"/>
@@ -8245,6 +8945,7 @@
       <c r="P696" s="2" t="n"/>
       <c r="Q696" s="2" t="n"/>
       <c r="R696" s="3" t="n"/>
+      <c r="T696" s="2" t="n"/>
     </row>
     <row r="697">
       <c r="A697" s="2" t="n"/>
@@ -8256,6 +8957,7 @@
       <c r="P697" s="2" t="n"/>
       <c r="Q697" s="2" t="n"/>
       <c r="R697" s="3" t="n"/>
+      <c r="T697" s="2" t="n"/>
     </row>
     <row r="698">
       <c r="A698" s="2" t="n"/>
@@ -8267,6 +8969,7 @@
       <c r="P698" s="2" t="n"/>
       <c r="Q698" s="2" t="n"/>
       <c r="R698" s="3" t="n"/>
+      <c r="T698" s="2" t="n"/>
     </row>
     <row r="699">
       <c r="A699" s="2" t="n"/>
@@ -8278,6 +8981,7 @@
       <c r="P699" s="2" t="n"/>
       <c r="Q699" s="2" t="n"/>
       <c r="R699" s="3" t="n"/>
+      <c r="T699" s="2" t="n"/>
     </row>
     <row r="700">
       <c r="A700" s="2" t="n"/>
@@ -8289,6 +8993,7 @@
       <c r="P700" s="2" t="n"/>
       <c r="Q700" s="2" t="n"/>
       <c r="R700" s="3" t="n"/>
+      <c r="T700" s="2" t="n"/>
     </row>
     <row r="701">
       <c r="A701" s="2" t="n"/>
@@ -8300,6 +9005,7 @@
       <c r="P701" s="2" t="n"/>
       <c r="Q701" s="2" t="n"/>
       <c r="R701" s="3" t="n"/>
+      <c r="T701" s="2" t="n"/>
     </row>
     <row r="702">
       <c r="A702" s="2" t="n"/>
@@ -8311,6 +9017,7 @@
       <c r="P702" s="2" t="n"/>
       <c r="Q702" s="2" t="n"/>
       <c r="R702" s="3" t="n"/>
+      <c r="T702" s="2" t="n"/>
     </row>
     <row r="703">
       <c r="A703" s="2" t="n"/>
@@ -8322,6 +9029,7 @@
       <c r="P703" s="2" t="n"/>
       <c r="Q703" s="2" t="n"/>
       <c r="R703" s="3" t="n"/>
+      <c r="T703" s="2" t="n"/>
     </row>
     <row r="704">
       <c r="A704" s="2" t="n"/>
@@ -8333,6 +9041,7 @@
       <c r="P704" s="2" t="n"/>
       <c r="Q704" s="2" t="n"/>
       <c r="R704" s="3" t="n"/>
+      <c r="T704" s="2" t="n"/>
     </row>
     <row r="705">
       <c r="A705" s="2" t="n"/>
@@ -8344,6 +9053,7 @@
       <c r="P705" s="2" t="n"/>
       <c r="Q705" s="2" t="n"/>
       <c r="R705" s="3" t="n"/>
+      <c r="T705" s="2" t="n"/>
     </row>
     <row r="706">
       <c r="A706" s="2" t="n"/>
@@ -8355,6 +9065,7 @@
       <c r="P706" s="2" t="n"/>
       <c r="Q706" s="2" t="n"/>
       <c r="R706" s="3" t="n"/>
+      <c r="T706" s="2" t="n"/>
     </row>
     <row r="707">
       <c r="A707" s="2" t="n"/>
@@ -8366,6 +9077,7 @@
       <c r="P707" s="2" t="n"/>
       <c r="Q707" s="2" t="n"/>
       <c r="R707" s="3" t="n"/>
+      <c r="T707" s="2" t="n"/>
     </row>
     <row r="708">
       <c r="A708" s="2" t="n"/>
@@ -8377,6 +9089,7 @@
       <c r="P708" s="2" t="n"/>
       <c r="Q708" s="2" t="n"/>
       <c r="R708" s="3" t="n"/>
+      <c r="T708" s="2" t="n"/>
     </row>
     <row r="709">
       <c r="A709" s="2" t="n"/>
@@ -8388,6 +9101,7 @@
       <c r="P709" s="2" t="n"/>
       <c r="Q709" s="2" t="n"/>
       <c r="R709" s="3" t="n"/>
+      <c r="T709" s="2" t="n"/>
     </row>
     <row r="710">
       <c r="A710" s="2" t="n"/>
@@ -8399,6 +9113,7 @@
       <c r="P710" s="2" t="n"/>
       <c r="Q710" s="2" t="n"/>
       <c r="R710" s="3" t="n"/>
+      <c r="T710" s="2" t="n"/>
     </row>
     <row r="711">
       <c r="A711" s="2" t="n"/>
@@ -8410,6 +9125,7 @@
       <c r="P711" s="2" t="n"/>
       <c r="Q711" s="2" t="n"/>
       <c r="R711" s="3" t="n"/>
+      <c r="T711" s="2" t="n"/>
     </row>
     <row r="712">
       <c r="A712" s="2" t="n"/>
@@ -8421,6 +9137,7 @@
       <c r="P712" s="2" t="n"/>
       <c r="Q712" s="2" t="n"/>
       <c r="R712" s="3" t="n"/>
+      <c r="T712" s="2" t="n"/>
     </row>
     <row r="713">
       <c r="A713" s="2" t="n"/>
@@ -8432,6 +9149,7 @@
       <c r="P713" s="2" t="n"/>
       <c r="Q713" s="2" t="n"/>
       <c r="R713" s="3" t="n"/>
+      <c r="T713" s="2" t="n"/>
     </row>
     <row r="714">
       <c r="A714" s="2" t="n"/>
@@ -8443,6 +9161,7 @@
       <c r="P714" s="2" t="n"/>
       <c r="Q714" s="2" t="n"/>
       <c r="R714" s="3" t="n"/>
+      <c r="T714" s="2" t="n"/>
     </row>
     <row r="715">
       <c r="A715" s="2" t="n"/>
@@ -8454,6 +9173,7 @@
       <c r="P715" s="2" t="n"/>
       <c r="Q715" s="2" t="n"/>
       <c r="R715" s="3" t="n"/>
+      <c r="T715" s="2" t="n"/>
     </row>
     <row r="716">
       <c r="A716" s="2" t="n"/>
@@ -8465,6 +9185,7 @@
       <c r="P716" s="2" t="n"/>
       <c r="Q716" s="2" t="n"/>
       <c r="R716" s="3" t="n"/>
+      <c r="T716" s="2" t="n"/>
     </row>
     <row r="717">
       <c r="A717" s="2" t="n"/>
@@ -8476,6 +9197,7 @@
       <c r="P717" s="2" t="n"/>
       <c r="Q717" s="2" t="n"/>
       <c r="R717" s="3" t="n"/>
+      <c r="T717" s="2" t="n"/>
     </row>
     <row r="718">
       <c r="A718" s="2" t="n"/>
@@ -8487,6 +9209,7 @@
       <c r="P718" s="2" t="n"/>
       <c r="Q718" s="2" t="n"/>
       <c r="R718" s="3" t="n"/>
+      <c r="T718" s="2" t="n"/>
     </row>
     <row r="719">
       <c r="A719" s="2" t="n"/>
@@ -8498,6 +9221,7 @@
       <c r="P719" s="2" t="n"/>
       <c r="Q719" s="2" t="n"/>
       <c r="R719" s="3" t="n"/>
+      <c r="T719" s="2" t="n"/>
     </row>
     <row r="720">
       <c r="A720" s="2" t="n"/>
@@ -8509,6 +9233,7 @@
       <c r="P720" s="2" t="n"/>
       <c r="Q720" s="2" t="n"/>
       <c r="R720" s="3" t="n"/>
+      <c r="T720" s="2" t="n"/>
     </row>
     <row r="721">
       <c r="A721" s="2" t="n"/>
@@ -8520,6 +9245,7 @@
       <c r="P721" s="2" t="n"/>
       <c r="Q721" s="2" t="n"/>
       <c r="R721" s="3" t="n"/>
+      <c r="T721" s="2" t="n"/>
     </row>
     <row r="722">
       <c r="A722" s="2" t="n"/>
@@ -8531,6 +9257,7 @@
       <c r="P722" s="2" t="n"/>
       <c r="Q722" s="2" t="n"/>
       <c r="R722" s="3" t="n"/>
+      <c r="T722" s="2" t="n"/>
     </row>
     <row r="723">
       <c r="A723" s="2" t="n"/>
@@ -8542,6 +9269,7 @@
       <c r="P723" s="2" t="n"/>
       <c r="Q723" s="2" t="n"/>
       <c r="R723" s="3" t="n"/>
+      <c r="T723" s="2" t="n"/>
     </row>
     <row r="724">
       <c r="A724" s="2" t="n"/>
@@ -8553,6 +9281,7 @@
       <c r="P724" s="2" t="n"/>
       <c r="Q724" s="2" t="n"/>
       <c r="R724" s="3" t="n"/>
+      <c r="T724" s="2" t="n"/>
     </row>
     <row r="725">
       <c r="A725" s="2" t="n"/>
@@ -8564,6 +9293,7 @@
       <c r="P725" s="2" t="n"/>
       <c r="Q725" s="2" t="n"/>
       <c r="R725" s="3" t="n"/>
+      <c r="T725" s="2" t="n"/>
     </row>
     <row r="726">
       <c r="A726" s="2" t="n"/>
@@ -8575,6 +9305,7 @@
       <c r="P726" s="2" t="n"/>
       <c r="Q726" s="2" t="n"/>
       <c r="R726" s="3" t="n"/>
+      <c r="T726" s="2" t="n"/>
     </row>
     <row r="727">
       <c r="A727" s="2" t="n"/>
@@ -8586,6 +9317,7 @@
       <c r="P727" s="2" t="n"/>
       <c r="Q727" s="2" t="n"/>
       <c r="R727" s="3" t="n"/>
+      <c r="T727" s="2" t="n"/>
     </row>
     <row r="728">
       <c r="A728" s="2" t="n"/>
@@ -8597,6 +9329,7 @@
       <c r="P728" s="2" t="n"/>
       <c r="Q728" s="2" t="n"/>
       <c r="R728" s="3" t="n"/>
+      <c r="T728" s="2" t="n"/>
     </row>
     <row r="729">
       <c r="A729" s="2" t="n"/>
@@ -8608,6 +9341,7 @@
       <c r="P729" s="2" t="n"/>
       <c r="Q729" s="2" t="n"/>
       <c r="R729" s="3" t="n"/>
+      <c r="T729" s="2" t="n"/>
     </row>
     <row r="730">
       <c r="A730" s="2" t="n"/>
@@ -8619,6 +9353,7 @@
       <c r="P730" s="2" t="n"/>
       <c r="Q730" s="2" t="n"/>
       <c r="R730" s="3" t="n"/>
+      <c r="T730" s="2" t="n"/>
     </row>
     <row r="731">
       <c r="A731" s="2" t="n"/>
@@ -8630,6 +9365,7 @@
       <c r="P731" s="2" t="n"/>
       <c r="Q731" s="2" t="n"/>
       <c r="R731" s="3" t="n"/>
+      <c r="T731" s="2" t="n"/>
     </row>
     <row r="732">
       <c r="A732" s="2" t="n"/>
@@ -8641,6 +9377,7 @@
       <c r="P732" s="2" t="n"/>
       <c r="Q732" s="2" t="n"/>
       <c r="R732" s="3" t="n"/>
+      <c r="T732" s="2" t="n"/>
     </row>
     <row r="733">
       <c r="A733" s="2" t="n"/>
@@ -8652,6 +9389,7 @@
       <c r="P733" s="2" t="n"/>
       <c r="Q733" s="2" t="n"/>
       <c r="R733" s="3" t="n"/>
+      <c r="T733" s="2" t="n"/>
     </row>
     <row r="734">
       <c r="A734" s="2" t="n"/>
@@ -8663,6 +9401,7 @@
       <c r="P734" s="2" t="n"/>
       <c r="Q734" s="2" t="n"/>
       <c r="R734" s="3" t="n"/>
+      <c r="T734" s="2" t="n"/>
     </row>
     <row r="735">
       <c r="A735" s="2" t="n"/>
@@ -8674,6 +9413,7 @@
       <c r="P735" s="2" t="n"/>
       <c r="Q735" s="2" t="n"/>
       <c r="R735" s="3" t="n"/>
+      <c r="T735" s="2" t="n"/>
     </row>
     <row r="736">
       <c r="A736" s="2" t="n"/>
@@ -8685,6 +9425,7 @@
       <c r="P736" s="2" t="n"/>
       <c r="Q736" s="2" t="n"/>
       <c r="R736" s="3" t="n"/>
+      <c r="T736" s="2" t="n"/>
     </row>
     <row r="737">
       <c r="A737" s="2" t="n"/>
@@ -8696,6 +9437,7 @@
       <c r="P737" s="2" t="n"/>
       <c r="Q737" s="2" t="n"/>
       <c r="R737" s="3" t="n"/>
+      <c r="T737" s="2" t="n"/>
     </row>
     <row r="738">
       <c r="A738" s="2" t="n"/>
@@ -8707,6 +9449,7 @@
       <c r="P738" s="2" t="n"/>
       <c r="Q738" s="2" t="n"/>
       <c r="R738" s="3" t="n"/>
+      <c r="T738" s="2" t="n"/>
     </row>
     <row r="739">
       <c r="A739" s="2" t="n"/>
@@ -8718,6 +9461,7 @@
       <c r="P739" s="2" t="n"/>
       <c r="Q739" s="2" t="n"/>
       <c r="R739" s="3" t="n"/>
+      <c r="T739" s="2" t="n"/>
     </row>
     <row r="740">
       <c r="A740" s="2" t="n"/>
@@ -8729,6 +9473,7 @@
       <c r="P740" s="2" t="n"/>
       <c r="Q740" s="2" t="n"/>
       <c r="R740" s="3" t="n"/>
+      <c r="T740" s="2" t="n"/>
     </row>
     <row r="741">
       <c r="A741" s="2" t="n"/>
@@ -8740,6 +9485,7 @@
       <c r="P741" s="2" t="n"/>
       <c r="Q741" s="2" t="n"/>
       <c r="R741" s="3" t="n"/>
+      <c r="T741" s="2" t="n"/>
     </row>
     <row r="742">
       <c r="A742" s="2" t="n"/>
@@ -8751,6 +9497,7 @@
       <c r="P742" s="2" t="n"/>
       <c r="Q742" s="2" t="n"/>
       <c r="R742" s="3" t="n"/>
+      <c r="T742" s="2" t="n"/>
     </row>
     <row r="743">
       <c r="A743" s="2" t="n"/>
@@ -8762,6 +9509,7 @@
       <c r="P743" s="2" t="n"/>
       <c r="Q743" s="2" t="n"/>
       <c r="R743" s="3" t="n"/>
+      <c r="T743" s="2" t="n"/>
     </row>
     <row r="744">
       <c r="A744" s="2" t="n"/>
@@ -8773,6 +9521,7 @@
       <c r="P744" s="2" t="n"/>
       <c r="Q744" s="2" t="n"/>
       <c r="R744" s="3" t="n"/>
+      <c r="T744" s="2" t="n"/>
     </row>
     <row r="745">
       <c r="A745" s="2" t="n"/>
@@ -8784,6 +9533,7 @@
       <c r="P745" s="2" t="n"/>
       <c r="Q745" s="2" t="n"/>
       <c r="R745" s="3" t="n"/>
+      <c r="T745" s="2" t="n"/>
     </row>
     <row r="746">
       <c r="A746" s="2" t="n"/>
@@ -8795,6 +9545,7 @@
       <c r="P746" s="2" t="n"/>
       <c r="Q746" s="2" t="n"/>
       <c r="R746" s="3" t="n"/>
+      <c r="T746" s="2" t="n"/>
     </row>
     <row r="747">
       <c r="A747" s="2" t="n"/>
@@ -8806,6 +9557,7 @@
       <c r="P747" s="2" t="n"/>
       <c r="Q747" s="2" t="n"/>
       <c r="R747" s="3" t="n"/>
+      <c r="T747" s="2" t="n"/>
     </row>
     <row r="748">
       <c r="A748" s="2" t="n"/>
@@ -8817,6 +9569,7 @@
       <c r="P748" s="2" t="n"/>
       <c r="Q748" s="2" t="n"/>
       <c r="R748" s="3" t="n"/>
+      <c r="T748" s="2" t="n"/>
     </row>
     <row r="749">
       <c r="A749" s="2" t="n"/>
@@ -8828,6 +9581,7 @@
       <c r="P749" s="2" t="n"/>
       <c r="Q749" s="2" t="n"/>
       <c r="R749" s="3" t="n"/>
+      <c r="T749" s="2" t="n"/>
     </row>
     <row r="750">
       <c r="A750" s="2" t="n"/>
@@ -8839,6 +9593,7 @@
       <c r="P750" s="2" t="n"/>
       <c r="Q750" s="2" t="n"/>
       <c r="R750" s="3" t="n"/>
+      <c r="T750" s="2" t="n"/>
     </row>
     <row r="751">
       <c r="A751" s="2" t="n"/>
@@ -8850,6 +9605,7 @@
       <c r="P751" s="2" t="n"/>
       <c r="Q751" s="2" t="n"/>
       <c r="R751" s="3" t="n"/>
+      <c r="T751" s="2" t="n"/>
     </row>
     <row r="752">
       <c r="A752" s="2" t="n"/>
@@ -8861,6 +9617,7 @@
       <c r="P752" s="2" t="n"/>
       <c r="Q752" s="2" t="n"/>
       <c r="R752" s="3" t="n"/>
+      <c r="T752" s="2" t="n"/>
     </row>
     <row r="753">
       <c r="A753" s="2" t="n"/>
@@ -8872,6 +9629,7 @@
       <c r="P753" s="2" t="n"/>
       <c r="Q753" s="2" t="n"/>
       <c r="R753" s="3" t="n"/>
+      <c r="T753" s="2" t="n"/>
     </row>
     <row r="754">
       <c r="A754" s="2" t="n"/>
@@ -8883,6 +9641,7 @@
       <c r="P754" s="2" t="n"/>
       <c r="Q754" s="2" t="n"/>
       <c r="R754" s="3" t="n"/>
+      <c r="T754" s="2" t="n"/>
     </row>
     <row r="755">
       <c r="A755" s="2" t="n"/>
@@ -8894,6 +9653,7 @@
       <c r="P755" s="2" t="n"/>
       <c r="Q755" s="2" t="n"/>
       <c r="R755" s="3" t="n"/>
+      <c r="T755" s="2" t="n"/>
     </row>
     <row r="756">
       <c r="A756" s="2" t="n"/>
@@ -8905,6 +9665,7 @@
       <c r="P756" s="2" t="n"/>
       <c r="Q756" s="2" t="n"/>
       <c r="R756" s="3" t="n"/>
+      <c r="T756" s="2" t="n"/>
     </row>
     <row r="757">
       <c r="A757" s="2" t="n"/>
@@ -8916,6 +9677,7 @@
       <c r="P757" s="2" t="n"/>
       <c r="Q757" s="2" t="n"/>
       <c r="R757" s="3" t="n"/>
+      <c r="T757" s="2" t="n"/>
     </row>
     <row r="758">
       <c r="A758" s="2" t="n"/>
@@ -8927,6 +9689,7 @@
       <c r="P758" s="2" t="n"/>
       <c r="Q758" s="2" t="n"/>
       <c r="R758" s="3" t="n"/>
+      <c r="T758" s="2" t="n"/>
     </row>
     <row r="759">
       <c r="A759" s="2" t="n"/>
@@ -8938,6 +9701,7 @@
       <c r="P759" s="2" t="n"/>
       <c r="Q759" s="2" t="n"/>
       <c r="R759" s="3" t="n"/>
+      <c r="T759" s="2" t="n"/>
     </row>
     <row r="760">
       <c r="A760" s="2" t="n"/>
@@ -8949,6 +9713,7 @@
       <c r="P760" s="2" t="n"/>
       <c r="Q760" s="2" t="n"/>
       <c r="R760" s="3" t="n"/>
+      <c r="T760" s="2" t="n"/>
     </row>
     <row r="761">
       <c r="A761" s="2" t="n"/>
@@ -8960,6 +9725,7 @@
       <c r="P761" s="2" t="n"/>
       <c r="Q761" s="2" t="n"/>
       <c r="R761" s="3" t="n"/>
+      <c r="T761" s="2" t="n"/>
     </row>
     <row r="762">
       <c r="A762" s="2" t="n"/>
@@ -8971,6 +9737,7 @@
       <c r="P762" s="2" t="n"/>
       <c r="Q762" s="2" t="n"/>
       <c r="R762" s="3" t="n"/>
+      <c r="T762" s="2" t="n"/>
     </row>
     <row r="763">
       <c r="A763" s="2" t="n"/>
@@ -8982,6 +9749,7 @@
       <c r="P763" s="2" t="n"/>
       <c r="Q763" s="2" t="n"/>
       <c r="R763" s="3" t="n"/>
+      <c r="T763" s="2" t="n"/>
     </row>
     <row r="764">
       <c r="A764" s="2" t="n"/>
@@ -8993,6 +9761,7 @@
       <c r="P764" s="2" t="n"/>
       <c r="Q764" s="2" t="n"/>
       <c r="R764" s="3" t="n"/>
+      <c r="T764" s="2" t="n"/>
     </row>
     <row r="765">
       <c r="A765" s="2" t="n"/>
@@ -9004,6 +9773,7 @@
       <c r="P765" s="2" t="n"/>
       <c r="Q765" s="2" t="n"/>
       <c r="R765" s="3" t="n"/>
+      <c r="T765" s="2" t="n"/>
     </row>
     <row r="766">
       <c r="A766" s="2" t="n"/>
@@ -9015,6 +9785,7 @@
       <c r="P766" s="2" t="n"/>
       <c r="Q766" s="2" t="n"/>
       <c r="R766" s="3" t="n"/>
+      <c r="T766" s="2" t="n"/>
     </row>
     <row r="767">
       <c r="A767" s="2" t="n"/>
@@ -9026,6 +9797,7 @@
       <c r="P767" s="2" t="n"/>
       <c r="Q767" s="2" t="n"/>
       <c r="R767" s="3" t="n"/>
+      <c r="T767" s="2" t="n"/>
     </row>
     <row r="768">
       <c r="A768" s="2" t="n"/>
@@ -9037,6 +9809,7 @@
       <c r="P768" s="2" t="n"/>
       <c r="Q768" s="2" t="n"/>
       <c r="R768" s="3" t="n"/>
+      <c r="T768" s="2" t="n"/>
     </row>
     <row r="769">
       <c r="A769" s="2" t="n"/>
@@ -9048,6 +9821,7 @@
       <c r="P769" s="2" t="n"/>
       <c r="Q769" s="2" t="n"/>
       <c r="R769" s="3" t="n"/>
+      <c r="T769" s="2" t="n"/>
     </row>
     <row r="770">
       <c r="A770" s="2" t="n"/>
@@ -9059,6 +9833,7 @@
       <c r="P770" s="2" t="n"/>
       <c r="Q770" s="2" t="n"/>
       <c r="R770" s="3" t="n"/>
+      <c r="T770" s="2" t="n"/>
     </row>
     <row r="771">
       <c r="A771" s="2" t="n"/>
@@ -9070,6 +9845,7 @@
       <c r="P771" s="2" t="n"/>
       <c r="Q771" s="2" t="n"/>
       <c r="R771" s="3" t="n"/>
+      <c r="T771" s="2" t="n"/>
     </row>
     <row r="772">
       <c r="A772" s="2" t="n"/>
@@ -9081,6 +9857,7 @@
       <c r="P772" s="2" t="n"/>
       <c r="Q772" s="2" t="n"/>
       <c r="R772" s="3" t="n"/>
+      <c r="T772" s="2" t="n"/>
     </row>
     <row r="773">
       <c r="A773" s="2" t="n"/>
@@ -9092,6 +9869,7 @@
       <c r="P773" s="2" t="n"/>
       <c r="Q773" s="2" t="n"/>
       <c r="R773" s="3" t="n"/>
+      <c r="T773" s="2" t="n"/>
     </row>
     <row r="774">
       <c r="A774" s="2" t="n"/>
@@ -9103,6 +9881,7 @@
       <c r="P774" s="2" t="n"/>
       <c r="Q774" s="2" t="n"/>
       <c r="R774" s="3" t="n"/>
+      <c r="T774" s="2" t="n"/>
     </row>
     <row r="775">
       <c r="A775" s="2" t="n"/>
@@ -9114,6 +9893,7 @@
       <c r="P775" s="2" t="n"/>
       <c r="Q775" s="2" t="n"/>
       <c r="R775" s="3" t="n"/>
+      <c r="T775" s="2" t="n"/>
     </row>
     <row r="776">
       <c r="A776" s="2" t="n"/>
@@ -9125,6 +9905,7 @@
       <c r="P776" s="2" t="n"/>
       <c r="Q776" s="2" t="n"/>
       <c r="R776" s="3" t="n"/>
+      <c r="T776" s="2" t="n"/>
     </row>
     <row r="777">
       <c r="A777" s="2" t="n"/>
@@ -9136,6 +9917,7 @@
       <c r="P777" s="2" t="n"/>
       <c r="Q777" s="2" t="n"/>
       <c r="R777" s="3" t="n"/>
+      <c r="T777" s="2" t="n"/>
     </row>
     <row r="778">
       <c r="A778" s="2" t="n"/>
@@ -9147,6 +9929,7 @@
       <c r="P778" s="2" t="n"/>
       <c r="Q778" s="2" t="n"/>
       <c r="R778" s="3" t="n"/>
+      <c r="T778" s="2" t="n"/>
     </row>
     <row r="779">
       <c r="A779" s="2" t="n"/>
@@ -9158,6 +9941,7 @@
       <c r="P779" s="2" t="n"/>
       <c r="Q779" s="2" t="n"/>
       <c r="R779" s="3" t="n"/>
+      <c r="T779" s="2" t="n"/>
     </row>
     <row r="780">
       <c r="A780" s="2" t="n"/>
@@ -9169,6 +9953,7 @@
       <c r="P780" s="2" t="n"/>
       <c r="Q780" s="2" t="n"/>
       <c r="R780" s="3" t="n"/>
+      <c r="T780" s="2" t="n"/>
     </row>
     <row r="781">
       <c r="A781" s="2" t="n"/>
@@ -9180,6 +9965,7 @@
       <c r="P781" s="2" t="n"/>
       <c r="Q781" s="2" t="n"/>
       <c r="R781" s="3" t="n"/>
+      <c r="T781" s="2" t="n"/>
     </row>
     <row r="782">
       <c r="A782" s="2" t="n"/>
@@ -9191,6 +9977,7 @@
       <c r="P782" s="2" t="n"/>
       <c r="Q782" s="2" t="n"/>
       <c r="R782" s="3" t="n"/>
+      <c r="T782" s="2" t="n"/>
     </row>
     <row r="783">
       <c r="A783" s="2" t="n"/>
@@ -9202,6 +9989,7 @@
       <c r="P783" s="2" t="n"/>
       <c r="Q783" s="2" t="n"/>
       <c r="R783" s="3" t="n"/>
+      <c r="T783" s="2" t="n"/>
     </row>
     <row r="784">
       <c r="A784" s="2" t="n"/>
@@ -9213,6 +10001,7 @@
       <c r="P784" s="2" t="n"/>
       <c r="Q784" s="2" t="n"/>
       <c r="R784" s="3" t="n"/>
+      <c r="T784" s="2" t="n"/>
     </row>
     <row r="785">
       <c r="A785" s="2" t="n"/>
@@ -9224,6 +10013,7 @@
       <c r="P785" s="2" t="n"/>
       <c r="Q785" s="2" t="n"/>
       <c r="R785" s="3" t="n"/>
+      <c r="T785" s="2" t="n"/>
     </row>
     <row r="786">
       <c r="A786" s="2" t="n"/>
@@ -9235,6 +10025,7 @@
       <c r="P786" s="2" t="n"/>
       <c r="Q786" s="2" t="n"/>
       <c r="R786" s="3" t="n"/>
+      <c r="T786" s="2" t="n"/>
     </row>
     <row r="787">
       <c r="A787" s="2" t="n"/>
@@ -9246,6 +10037,7 @@
       <c r="P787" s="2" t="n"/>
       <c r="Q787" s="2" t="n"/>
       <c r="R787" s="3" t="n"/>
+      <c r="T787" s="2" t="n"/>
     </row>
     <row r="788">
       <c r="A788" s="2" t="n"/>
@@ -9257,6 +10049,7 @@
       <c r="P788" s="2" t="n"/>
       <c r="Q788" s="2" t="n"/>
       <c r="R788" s="3" t="n"/>
+      <c r="T788" s="2" t="n"/>
     </row>
     <row r="789">
       <c r="A789" s="2" t="n"/>
@@ -9268,6 +10061,7 @@
       <c r="P789" s="2" t="n"/>
       <c r="Q789" s="2" t="n"/>
       <c r="R789" s="3" t="n"/>
+      <c r="T789" s="2" t="n"/>
     </row>
     <row r="790">
       <c r="A790" s="2" t="n"/>
@@ -9279,6 +10073,7 @@
       <c r="P790" s="2" t="n"/>
       <c r="Q790" s="2" t="n"/>
       <c r="R790" s="3" t="n"/>
+      <c r="T790" s="2" t="n"/>
     </row>
     <row r="791">
       <c r="A791" s="2" t="n"/>
@@ -9290,6 +10085,7 @@
       <c r="P791" s="2" t="n"/>
       <c r="Q791" s="2" t="n"/>
       <c r="R791" s="3" t="n"/>
+      <c r="T791" s="2" t="n"/>
     </row>
     <row r="792">
       <c r="A792" s="2" t="n"/>
@@ -9301,6 +10097,7 @@
       <c r="P792" s="2" t="n"/>
       <c r="Q792" s="2" t="n"/>
       <c r="R792" s="3" t="n"/>
+      <c r="T792" s="2" t="n"/>
     </row>
     <row r="793">
       <c r="A793" s="2" t="n"/>
@@ -9312,6 +10109,7 @@
       <c r="P793" s="2" t="n"/>
       <c r="Q793" s="2" t="n"/>
       <c r="R793" s="3" t="n"/>
+      <c r="T793" s="2" t="n"/>
     </row>
     <row r="794">
       <c r="A794" s="2" t="n"/>
@@ -9323,6 +10121,7 @@
       <c r="P794" s="2" t="n"/>
       <c r="Q794" s="2" t="n"/>
       <c r="R794" s="3" t="n"/>
+      <c r="T794" s="2" t="n"/>
     </row>
     <row r="795">
       <c r="A795" s="2" t="n"/>
@@ -9334,6 +10133,7 @@
       <c r="P795" s="2" t="n"/>
       <c r="Q795" s="2" t="n"/>
       <c r="R795" s="3" t="n"/>
+      <c r="T795" s="2" t="n"/>
     </row>
     <row r="796">
       <c r="A796" s="2" t="n"/>
@@ -9345,6 +10145,7 @@
       <c r="P796" s="2" t="n"/>
       <c r="Q796" s="2" t="n"/>
       <c r="R796" s="3" t="n"/>
+      <c r="T796" s="2" t="n"/>
     </row>
     <row r="797">
       <c r="A797" s="2" t="n"/>
@@ -9356,6 +10157,7 @@
       <c r="P797" s="2" t="n"/>
       <c r="Q797" s="2" t="n"/>
       <c r="R797" s="3" t="n"/>
+      <c r="T797" s="2" t="n"/>
     </row>
     <row r="798">
       <c r="A798" s="2" t="n"/>
@@ -9367,6 +10169,7 @@
       <c r="P798" s="2" t="n"/>
       <c r="Q798" s="2" t="n"/>
       <c r="R798" s="3" t="n"/>
+      <c r="T798" s="2" t="n"/>
     </row>
     <row r="799">
       <c r="A799" s="2" t="n"/>
@@ -9378,6 +10181,7 @@
       <c r="P799" s="2" t="n"/>
       <c r="Q799" s="2" t="n"/>
       <c r="R799" s="3" t="n"/>
+      <c r="T799" s="2" t="n"/>
     </row>
     <row r="800">
       <c r="A800" s="2" t="n"/>
@@ -9389,6 +10193,7 @@
       <c r="P800" s="2" t="n"/>
       <c r="Q800" s="2" t="n"/>
       <c r="R800" s="3" t="n"/>
+      <c r="T800" s="2" t="n"/>
     </row>
     <row r="801">
       <c r="A801" s="2" t="n"/>
@@ -9400,6 +10205,7 @@
       <c r="P801" s="2" t="n"/>
       <c r="Q801" s="2" t="n"/>
       <c r="R801" s="3" t="n"/>
+      <c r="T801" s="2" t="n"/>
     </row>
     <row r="802">
       <c r="A802" s="2" t="n"/>
@@ -9411,6 +10217,7 @@
       <c r="P802" s="2" t="n"/>
       <c r="Q802" s="2" t="n"/>
       <c r="R802" s="3" t="n"/>
+      <c r="T802" s="2" t="n"/>
     </row>
     <row r="803">
       <c r="A803" s="2" t="n"/>
@@ -9422,6 +10229,7 @@
       <c r="P803" s="2" t="n"/>
       <c r="Q803" s="2" t="n"/>
       <c r="R803" s="3" t="n"/>
+      <c r="T803" s="2" t="n"/>
     </row>
     <row r="804">
       <c r="A804" s="2" t="n"/>
@@ -9433,6 +10241,7 @@
       <c r="P804" s="2" t="n"/>
       <c r="Q804" s="2" t="n"/>
       <c r="R804" s="3" t="n"/>
+      <c r="T804" s="2" t="n"/>
     </row>
     <row r="805">
       <c r="A805" s="2" t="n"/>
@@ -9444,6 +10253,7 @@
       <c r="P805" s="2" t="n"/>
       <c r="Q805" s="2" t="n"/>
       <c r="R805" s="3" t="n"/>
+      <c r="T805" s="2" t="n"/>
     </row>
     <row r="806">
       <c r="A806" s="2" t="n"/>
@@ -9455,6 +10265,7 @@
       <c r="P806" s="2" t="n"/>
       <c r="Q806" s="2" t="n"/>
       <c r="R806" s="3" t="n"/>
+      <c r="T806" s="2" t="n"/>
     </row>
     <row r="807">
       <c r="A807" s="2" t="n"/>
@@ -9466,6 +10277,7 @@
       <c r="P807" s="2" t="n"/>
       <c r="Q807" s="2" t="n"/>
       <c r="R807" s="3" t="n"/>
+      <c r="T807" s="2" t="n"/>
     </row>
     <row r="808">
       <c r="A808" s="2" t="n"/>
@@ -9477,6 +10289,7 @@
       <c r="P808" s="2" t="n"/>
       <c r="Q808" s="2" t="n"/>
       <c r="R808" s="3" t="n"/>
+      <c r="T808" s="2" t="n"/>
     </row>
     <row r="809">
       <c r="A809" s="2" t="n"/>
@@ -9488,6 +10301,7 @@
       <c r="P809" s="2" t="n"/>
       <c r="Q809" s="2" t="n"/>
       <c r="R809" s="3" t="n"/>
+      <c r="T809" s="2" t="n"/>
     </row>
     <row r="810">
       <c r="A810" s="2" t="n"/>
@@ -9499,6 +10313,7 @@
       <c r="P810" s="2" t="n"/>
       <c r="Q810" s="2" t="n"/>
       <c r="R810" s="3" t="n"/>
+      <c r="T810" s="2" t="n"/>
     </row>
     <row r="811">
       <c r="A811" s="2" t="n"/>
@@ -9510,6 +10325,7 @@
       <c r="P811" s="2" t="n"/>
       <c r="Q811" s="2" t="n"/>
       <c r="R811" s="3" t="n"/>
+      <c r="T811" s="2" t="n"/>
     </row>
     <row r="812">
       <c r="A812" s="2" t="n"/>
@@ -9521,6 +10337,7 @@
       <c r="P812" s="2" t="n"/>
       <c r="Q812" s="2" t="n"/>
       <c r="R812" s="3" t="n"/>
+      <c r="T812" s="2" t="n"/>
     </row>
     <row r="813">
       <c r="A813" s="2" t="n"/>
@@ -9532,6 +10349,7 @@
       <c r="P813" s="2" t="n"/>
       <c r="Q813" s="2" t="n"/>
       <c r="R813" s="3" t="n"/>
+      <c r="T813" s="2" t="n"/>
     </row>
     <row r="814">
       <c r="A814" s="2" t="n"/>
@@ -9543,6 +10361,7 @@
       <c r="P814" s="2" t="n"/>
       <c r="Q814" s="2" t="n"/>
       <c r="R814" s="3" t="n"/>
+      <c r="T814" s="2" t="n"/>
     </row>
     <row r="815">
       <c r="A815" s="2" t="n"/>
@@ -9554,6 +10373,7 @@
       <c r="P815" s="2" t="n"/>
       <c r="Q815" s="2" t="n"/>
       <c r="R815" s="3" t="n"/>
+      <c r="T815" s="2" t="n"/>
     </row>
     <row r="816">
       <c r="A816" s="2" t="n"/>
@@ -9565,6 +10385,7 @@
       <c r="P816" s="2" t="n"/>
       <c r="Q816" s="2" t="n"/>
       <c r="R816" s="3" t="n"/>
+      <c r="T816" s="2" t="n"/>
     </row>
     <row r="817">
       <c r="A817" s="2" t="n"/>
@@ -9576,6 +10397,7 @@
       <c r="P817" s="2" t="n"/>
       <c r="Q817" s="2" t="n"/>
       <c r="R817" s="3" t="n"/>
+      <c r="T817" s="2" t="n"/>
     </row>
     <row r="818">
       <c r="A818" s="2" t="n"/>
@@ -9587,6 +10409,7 @@
       <c r="P818" s="2" t="n"/>
       <c r="Q818" s="2" t="n"/>
       <c r="R818" s="3" t="n"/>
+      <c r="T818" s="2" t="n"/>
     </row>
     <row r="819">
       <c r="A819" s="2" t="n"/>
@@ -9598,6 +10421,7 @@
       <c r="P819" s="2" t="n"/>
       <c r="Q819" s="2" t="n"/>
       <c r="R819" s="3" t="n"/>
+      <c r="T819" s="2" t="n"/>
     </row>
     <row r="820">
       <c r="A820" s="2" t="n"/>
@@ -9609,6 +10433,7 @@
       <c r="P820" s="2" t="n"/>
       <c r="Q820" s="2" t="n"/>
       <c r="R820" s="3" t="n"/>
+      <c r="T820" s="2" t="n"/>
     </row>
     <row r="821">
       <c r="A821" s="2" t="n"/>
@@ -9620,6 +10445,7 @@
       <c r="P821" s="2" t="n"/>
       <c r="Q821" s="2" t="n"/>
       <c r="R821" s="3" t="n"/>
+      <c r="T821" s="2" t="n"/>
     </row>
     <row r="822">
       <c r="A822" s="2" t="n"/>
@@ -9631,6 +10457,7 @@
       <c r="P822" s="2" t="n"/>
       <c r="Q822" s="2" t="n"/>
       <c r="R822" s="3" t="n"/>
+      <c r="T822" s="2" t="n"/>
     </row>
     <row r="823">
       <c r="A823" s="2" t="n"/>
@@ -9642,6 +10469,7 @@
       <c r="P823" s="2" t="n"/>
       <c r="Q823" s="2" t="n"/>
       <c r="R823" s="3" t="n"/>
+      <c r="T823" s="2" t="n"/>
     </row>
     <row r="824">
       <c r="A824" s="2" t="n"/>
@@ -9653,6 +10481,7 @@
       <c r="P824" s="2" t="n"/>
       <c r="Q824" s="2" t="n"/>
       <c r="R824" s="3" t="n"/>
+      <c r="T824" s="2" t="n"/>
     </row>
     <row r="825">
       <c r="A825" s="2" t="n"/>
@@ -9664,6 +10493,7 @@
       <c r="P825" s="2" t="n"/>
       <c r="Q825" s="2" t="n"/>
       <c r="R825" s="3" t="n"/>
+      <c r="T825" s="2" t="n"/>
     </row>
     <row r="826">
       <c r="A826" s="2" t="n"/>
@@ -9675,6 +10505,7 @@
       <c r="P826" s="2" t="n"/>
       <c r="Q826" s="2" t="n"/>
       <c r="R826" s="3" t="n"/>
+      <c r="T826" s="2" t="n"/>
     </row>
     <row r="827">
       <c r="A827" s="2" t="n"/>
@@ -9686,6 +10517,7 @@
       <c r="P827" s="2" t="n"/>
       <c r="Q827" s="2" t="n"/>
       <c r="R827" s="3" t="n"/>
+      <c r="T827" s="2" t="n"/>
     </row>
     <row r="828">
       <c r="A828" s="2" t="n"/>
@@ -9697,6 +10529,7 @@
       <c r="P828" s="2" t="n"/>
       <c r="Q828" s="2" t="n"/>
       <c r="R828" s="3" t="n"/>
+      <c r="T828" s="2" t="n"/>
     </row>
     <row r="829">
       <c r="A829" s="2" t="n"/>
@@ -9708,6 +10541,7 @@
       <c r="P829" s="2" t="n"/>
       <c r="Q829" s="2" t="n"/>
       <c r="R829" s="3" t="n"/>
+      <c r="T829" s="2" t="n"/>
     </row>
     <row r="830">
       <c r="A830" s="2" t="n"/>
@@ -9719,6 +10553,7 @@
       <c r="P830" s="2" t="n"/>
       <c r="Q830" s="2" t="n"/>
       <c r="R830" s="3" t="n"/>
+      <c r="T830" s="2" t="n"/>
     </row>
     <row r="831">
       <c r="A831" s="2" t="n"/>
@@ -9730,6 +10565,7 @@
       <c r="P831" s="2" t="n"/>
       <c r="Q831" s="2" t="n"/>
       <c r="R831" s="3" t="n"/>
+      <c r="T831" s="2" t="n"/>
     </row>
     <row r="832">
       <c r="A832" s="2" t="n"/>
@@ -9741,6 +10577,7 @@
       <c r="P832" s="2" t="n"/>
       <c r="Q832" s="2" t="n"/>
       <c r="R832" s="3" t="n"/>
+      <c r="T832" s="2" t="n"/>
     </row>
     <row r="833">
       <c r="A833" s="2" t="n"/>
@@ -9752,6 +10589,7 @@
       <c r="P833" s="2" t="n"/>
       <c r="Q833" s="2" t="n"/>
       <c r="R833" s="3" t="n"/>
+      <c r="T833" s="2" t="n"/>
     </row>
     <row r="834">
       <c r="A834" s="2" t="n"/>
@@ -9763,6 +10601,7 @@
       <c r="P834" s="2" t="n"/>
       <c r="Q834" s="2" t="n"/>
       <c r="R834" s="3" t="n"/>
+      <c r="T834" s="2" t="n"/>
     </row>
     <row r="835">
       <c r="A835" s="2" t="n"/>
@@ -9774,6 +10613,7 @@
       <c r="P835" s="2" t="n"/>
       <c r="Q835" s="2" t="n"/>
       <c r="R835" s="3" t="n"/>
+      <c r="T835" s="2" t="n"/>
     </row>
     <row r="836">
       <c r="A836" s="2" t="n"/>
@@ -9785,6 +10625,7 @@
       <c r="P836" s="2" t="n"/>
       <c r="Q836" s="2" t="n"/>
       <c r="R836" s="3" t="n"/>
+      <c r="T836" s="2" t="n"/>
     </row>
     <row r="837">
       <c r="A837" s="2" t="n"/>
@@ -9796,6 +10637,7 @@
       <c r="P837" s="2" t="n"/>
       <c r="Q837" s="2" t="n"/>
       <c r="R837" s="3" t="n"/>
+      <c r="T837" s="2" t="n"/>
     </row>
     <row r="838">
       <c r="A838" s="2" t="n"/>
@@ -9807,6 +10649,7 @@
       <c r="P838" s="2" t="n"/>
       <c r="Q838" s="2" t="n"/>
       <c r="R838" s="3" t="n"/>
+      <c r="T838" s="2" t="n"/>
     </row>
     <row r="839">
       <c r="A839" s="2" t="n"/>
@@ -9818,6 +10661,7 @@
       <c r="P839" s="2" t="n"/>
       <c r="Q839" s="2" t="n"/>
       <c r="R839" s="3" t="n"/>
+      <c r="T839" s="2" t="n"/>
     </row>
     <row r="840">
       <c r="A840" s="2" t="n"/>
@@ -9829,6 +10673,7 @@
       <c r="P840" s="2" t="n"/>
       <c r="Q840" s="2" t="n"/>
       <c r="R840" s="3" t="n"/>
+      <c r="T840" s="2" t="n"/>
     </row>
     <row r="841">
       <c r="A841" s="2" t="n"/>
@@ -9840,6 +10685,7 @@
       <c r="P841" s="2" t="n"/>
       <c r="Q841" s="2" t="n"/>
       <c r="R841" s="3" t="n"/>
+      <c r="T841" s="2" t="n"/>
     </row>
     <row r="842">
       <c r="A842" s="2" t="n"/>
@@ -9851,6 +10697,7 @@
       <c r="P842" s="2" t="n"/>
       <c r="Q842" s="2" t="n"/>
       <c r="R842" s="3" t="n"/>
+      <c r="T842" s="2" t="n"/>
     </row>
     <row r="843">
       <c r="A843" s="2" t="n"/>
@@ -9862,6 +10709,7 @@
       <c r="P843" s="2" t="n"/>
       <c r="Q843" s="2" t="n"/>
       <c r="R843" s="3" t="n"/>
+      <c r="T843" s="2" t="n"/>
     </row>
     <row r="844">
       <c r="A844" s="2" t="n"/>
@@ -9873,6 +10721,7 @@
       <c r="P844" s="2" t="n"/>
       <c r="Q844" s="2" t="n"/>
       <c r="R844" s="3" t="n"/>
+      <c r="T844" s="2" t="n"/>
     </row>
     <row r="845">
       <c r="A845" s="2" t="n"/>
@@ -9884,6 +10733,7 @@
       <c r="P845" s="2" t="n"/>
       <c r="Q845" s="2" t="n"/>
       <c r="R845" s="3" t="n"/>
+      <c r="T845" s="2" t="n"/>
     </row>
     <row r="846">
       <c r="A846" s="2" t="n"/>
@@ -9895,6 +10745,7 @@
       <c r="P846" s="2" t="n"/>
       <c r="Q846" s="2" t="n"/>
       <c r="R846" s="3" t="n"/>
+      <c r="T846" s="2" t="n"/>
     </row>
     <row r="847">
       <c r="A847" s="2" t="n"/>
@@ -9906,6 +10757,7 @@
       <c r="P847" s="2" t="n"/>
       <c r="Q847" s="2" t="n"/>
       <c r="R847" s="3" t="n"/>
+      <c r="T847" s="2" t="n"/>
     </row>
     <row r="848">
       <c r="A848" s="2" t="n"/>
@@ -9917,6 +10769,7 @@
       <c r="P848" s="2" t="n"/>
       <c r="Q848" s="2" t="n"/>
       <c r="R848" s="3" t="n"/>
+      <c r="T848" s="2" t="n"/>
     </row>
     <row r="849">
       <c r="A849" s="2" t="n"/>
@@ -9928,6 +10781,7 @@
       <c r="P849" s="2" t="n"/>
       <c r="Q849" s="2" t="n"/>
       <c r="R849" s="3" t="n"/>
+      <c r="T849" s="2" t="n"/>
     </row>
     <row r="850">
       <c r="A850" s="2" t="n"/>
@@ -9939,6 +10793,7 @@
       <c r="P850" s="2" t="n"/>
       <c r="Q850" s="2" t="n"/>
       <c r="R850" s="3" t="n"/>
+      <c r="T850" s="2" t="n"/>
     </row>
     <row r="851">
       <c r="A851" s="2" t="n"/>
@@ -9950,6 +10805,7 @@
       <c r="P851" s="2" t="n"/>
       <c r="Q851" s="2" t="n"/>
       <c r="R851" s="3" t="n"/>
+      <c r="T851" s="2" t="n"/>
     </row>
     <row r="852">
       <c r="A852" s="2" t="n"/>
@@ -9961,6 +10817,7 @@
       <c r="P852" s="2" t="n"/>
       <c r="Q852" s="2" t="n"/>
       <c r="R852" s="3" t="n"/>
+      <c r="T852" s="2" t="n"/>
     </row>
     <row r="853">
       <c r="A853" s="2" t="n"/>
@@ -9972,6 +10829,7 @@
       <c r="P853" s="2" t="n"/>
       <c r="Q853" s="2" t="n"/>
       <c r="R853" s="3" t="n"/>
+      <c r="T853" s="2" t="n"/>
     </row>
     <row r="854">
       <c r="A854" s="2" t="n"/>
@@ -9983,6 +10841,7 @@
       <c r="P854" s="2" t="n"/>
       <c r="Q854" s="2" t="n"/>
       <c r="R854" s="3" t="n"/>
+      <c r="T854" s="2" t="n"/>
     </row>
     <row r="855">
       <c r="A855" s="2" t="n"/>
@@ -9994,6 +10853,7 @@
       <c r="P855" s="2" t="n"/>
       <c r="Q855" s="2" t="n"/>
       <c r="R855" s="3" t="n"/>
+      <c r="T855" s="2" t="n"/>
     </row>
     <row r="856">
       <c r="A856" s="2" t="n"/>
@@ -10005,6 +10865,7 @@
       <c r="P856" s="2" t="n"/>
       <c r="Q856" s="2" t="n"/>
       <c r="R856" s="3" t="n"/>
+      <c r="T856" s="2" t="n"/>
     </row>
     <row r="857">
       <c r="A857" s="2" t="n"/>
@@ -10016,6 +10877,7 @@
       <c r="P857" s="2" t="n"/>
       <c r="Q857" s="2" t="n"/>
       <c r="R857" s="3" t="n"/>
+      <c r="T857" s="2" t="n"/>
     </row>
     <row r="858">
       <c r="A858" s="2" t="n"/>
@@ -10027,6 +10889,7 @@
       <c r="P858" s="2" t="n"/>
       <c r="Q858" s="2" t="n"/>
       <c r="R858" s="3" t="n"/>
+      <c r="T858" s="2" t="n"/>
     </row>
     <row r="859">
       <c r="A859" s="2" t="n"/>
@@ -10038,6 +10901,7 @@
       <c r="P859" s="2" t="n"/>
       <c r="Q859" s="2" t="n"/>
       <c r="R859" s="3" t="n"/>
+      <c r="T859" s="2" t="n"/>
     </row>
     <row r="860">
       <c r="A860" s="2" t="n"/>
@@ -10049,6 +10913,7 @@
       <c r="P860" s="2" t="n"/>
       <c r="Q860" s="2" t="n"/>
       <c r="R860" s="3" t="n"/>
+      <c r="T860" s="2" t="n"/>
     </row>
     <row r="861">
       <c r="A861" s="2" t="n"/>
@@ -10060,6 +10925,7 @@
       <c r="P861" s="2" t="n"/>
       <c r="Q861" s="2" t="n"/>
       <c r="R861" s="3" t="n"/>
+      <c r="T861" s="2" t="n"/>
     </row>
     <row r="862">
       <c r="A862" s="2" t="n"/>
@@ -10071,6 +10937,7 @@
       <c r="P862" s="2" t="n"/>
       <c r="Q862" s="2" t="n"/>
       <c r="R862" s="3" t="n"/>
+      <c r="T862" s="2" t="n"/>
     </row>
     <row r="863">
       <c r="A863" s="2" t="n"/>
@@ -10082,6 +10949,7 @@
       <c r="P863" s="2" t="n"/>
       <c r="Q863" s="2" t="n"/>
       <c r="R863" s="3" t="n"/>
+      <c r="T863" s="2" t="n"/>
     </row>
     <row r="864">
       <c r="A864" s="2" t="n"/>
@@ -10093,6 +10961,7 @@
       <c r="P864" s="2" t="n"/>
       <c r="Q864" s="2" t="n"/>
       <c r="R864" s="3" t="n"/>
+      <c r="T864" s="2" t="n"/>
     </row>
     <row r="865">
       <c r="A865" s="2" t="n"/>
@@ -10104,6 +10973,7 @@
       <c r="P865" s="2" t="n"/>
       <c r="Q865" s="2" t="n"/>
       <c r="R865" s="3" t="n"/>
+      <c r="T865" s="2" t="n"/>
     </row>
     <row r="866">
       <c r="A866" s="2" t="n"/>
@@ -10115,6 +10985,7 @@
       <c r="P866" s="2" t="n"/>
       <c r="Q866" s="2" t="n"/>
       <c r="R866" s="3" t="n"/>
+      <c r="T866" s="2" t="n"/>
     </row>
     <row r="867">
       <c r="A867" s="2" t="n"/>
@@ -10126,6 +10997,7 @@
       <c r="P867" s="2" t="n"/>
       <c r="Q867" s="2" t="n"/>
       <c r="R867" s="3" t="n"/>
+      <c r="T867" s="2" t="n"/>
     </row>
     <row r="868">
       <c r="A868" s="2" t="n"/>
@@ -10137,6 +11009,7 @@
       <c r="P868" s="2" t="n"/>
       <c r="Q868" s="2" t="n"/>
       <c r="R868" s="3" t="n"/>
+      <c r="T868" s="2" t="n"/>
     </row>
     <row r="869">
       <c r="A869" s="2" t="n"/>
@@ -10148,6 +11021,7 @@
       <c r="P869" s="2" t="n"/>
       <c r="Q869" s="2" t="n"/>
       <c r="R869" s="3" t="n"/>
+      <c r="T869" s="2" t="n"/>
     </row>
     <row r="870">
       <c r="A870" s="2" t="n"/>
@@ -10159,6 +11033,7 @@
       <c r="P870" s="2" t="n"/>
       <c r="Q870" s="2" t="n"/>
       <c r="R870" s="3" t="n"/>
+      <c r="T870" s="2" t="n"/>
     </row>
     <row r="871">
       <c r="A871" s="2" t="n"/>
@@ -10170,6 +11045,7 @@
       <c r="P871" s="2" t="n"/>
       <c r="Q871" s="2" t="n"/>
       <c r="R871" s="3" t="n"/>
+      <c r="T871" s="2" t="n"/>
     </row>
     <row r="872">
       <c r="A872" s="2" t="n"/>
@@ -10181,6 +11057,7 @@
       <c r="P872" s="2" t="n"/>
       <c r="Q872" s="2" t="n"/>
       <c r="R872" s="3" t="n"/>
+      <c r="T872" s="2" t="n"/>
     </row>
     <row r="873">
       <c r="A873" s="2" t="n"/>
@@ -10192,6 +11069,7 @@
       <c r="P873" s="2" t="n"/>
       <c r="Q873" s="2" t="n"/>
       <c r="R873" s="3" t="n"/>
+      <c r="T873" s="2" t="n"/>
     </row>
     <row r="874">
       <c r="A874" s="2" t="n"/>
@@ -10203,6 +11081,7 @@
       <c r="P874" s="2" t="n"/>
       <c r="Q874" s="2" t="n"/>
       <c r="R874" s="3" t="n"/>
+      <c r="T874" s="2" t="n"/>
     </row>
     <row r="875">
       <c r="A875" s="2" t="n"/>
@@ -10214,6 +11093,7 @@
       <c r="P875" s="2" t="n"/>
       <c r="Q875" s="2" t="n"/>
       <c r="R875" s="3" t="n"/>
+      <c r="T875" s="2" t="n"/>
     </row>
     <row r="876">
       <c r="A876" s="2" t="n"/>
@@ -10225,6 +11105,7 @@
       <c r="P876" s="2" t="n"/>
       <c r="Q876" s="2" t="n"/>
       <c r="R876" s="3" t="n"/>
+      <c r="T876" s="2" t="n"/>
     </row>
     <row r="877">
       <c r="A877" s="2" t="n"/>
@@ -10236,6 +11117,7 @@
       <c r="P877" s="2" t="n"/>
       <c r="Q877" s="2" t="n"/>
       <c r="R877" s="3" t="n"/>
+      <c r="T877" s="2" t="n"/>
     </row>
     <row r="878">
       <c r="A878" s="2" t="n"/>
@@ -10247,6 +11129,7 @@
       <c r="P878" s="2" t="n"/>
       <c r="Q878" s="2" t="n"/>
       <c r="R878" s="3" t="n"/>
+      <c r="T878" s="2" t="n"/>
     </row>
     <row r="879">
       <c r="A879" s="2" t="n"/>
@@ -10258,6 +11141,7 @@
       <c r="P879" s="2" t="n"/>
       <c r="Q879" s="2" t="n"/>
       <c r="R879" s="3" t="n"/>
+      <c r="T879" s="2" t="n"/>
     </row>
     <row r="880">
       <c r="A880" s="2" t="n"/>
@@ -10269,6 +11153,7 @@
       <c r="P880" s="2" t="n"/>
       <c r="Q880" s="2" t="n"/>
       <c r="R880" s="3" t="n"/>
+      <c r="T880" s="2" t="n"/>
     </row>
     <row r="881">
       <c r="A881" s="2" t="n"/>
@@ -10280,6 +11165,7 @@
       <c r="P881" s="2" t="n"/>
       <c r="Q881" s="2" t="n"/>
       <c r="R881" s="3" t="n"/>
+      <c r="T881" s="2" t="n"/>
     </row>
     <row r="882">
       <c r="A882" s="2" t="n"/>
@@ -10291,6 +11177,7 @@
       <c r="P882" s="2" t="n"/>
       <c r="Q882" s="2" t="n"/>
       <c r="R882" s="3" t="n"/>
+      <c r="T882" s="2" t="n"/>
     </row>
     <row r="883">
       <c r="A883" s="2" t="n"/>
@@ -10302,6 +11189,7 @@
       <c r="P883" s="2" t="n"/>
       <c r="Q883" s="2" t="n"/>
       <c r="R883" s="3" t="n"/>
+      <c r="T883" s="2" t="n"/>
     </row>
     <row r="884">
       <c r="A884" s="2" t="n"/>
@@ -10313,6 +11201,7 @@
       <c r="P884" s="2" t="n"/>
       <c r="Q884" s="2" t="n"/>
       <c r="R884" s="3" t="n"/>
+      <c r="T884" s="2" t="n"/>
     </row>
     <row r="885">
       <c r="A885" s="2" t="n"/>
@@ -10324,6 +11213,7 @@
       <c r="P885" s="2" t="n"/>
       <c r="Q885" s="2" t="n"/>
       <c r="R885" s="3" t="n"/>
+      <c r="T885" s="2" t="n"/>
     </row>
     <row r="886">
       <c r="A886" s="2" t="n"/>
@@ -10335,6 +11225,7 @@
       <c r="P886" s="2" t="n"/>
       <c r="Q886" s="2" t="n"/>
       <c r="R886" s="3" t="n"/>
+      <c r="T886" s="2" t="n"/>
     </row>
     <row r="887">
       <c r="A887" s="2" t="n"/>
@@ -10346,6 +11237,7 @@
       <c r="P887" s="2" t="n"/>
       <c r="Q887" s="2" t="n"/>
       <c r="R887" s="3" t="n"/>
+      <c r="T887" s="2" t="n"/>
     </row>
     <row r="888">
       <c r="A888" s="2" t="n"/>
@@ -10357,6 +11249,7 @@
       <c r="P888" s="2" t="n"/>
       <c r="Q888" s="2" t="n"/>
       <c r="R888" s="3" t="n"/>
+      <c r="T888" s="2" t="n"/>
     </row>
     <row r="889">
       <c r="A889" s="2" t="n"/>
@@ -10368,6 +11261,7 @@
       <c r="P889" s="2" t="n"/>
       <c r="Q889" s="2" t="n"/>
       <c r="R889" s="3" t="n"/>
+      <c r="T889" s="2" t="n"/>
     </row>
     <row r="890">
       <c r="A890" s="2" t="n"/>
@@ -10379,6 +11273,7 @@
       <c r="P890" s="2" t="n"/>
       <c r="Q890" s="2" t="n"/>
       <c r="R890" s="3" t="n"/>
+      <c r="T890" s="2" t="n"/>
     </row>
     <row r="891">
       <c r="A891" s="2" t="n"/>
@@ -10390,6 +11285,7 @@
       <c r="P891" s="2" t="n"/>
       <c r="Q891" s="2" t="n"/>
       <c r="R891" s="3" t="n"/>
+      <c r="T891" s="2" t="n"/>
     </row>
     <row r="892">
       <c r="A892" s="2" t="n"/>
@@ -10401,6 +11297,7 @@
       <c r="P892" s="2" t="n"/>
       <c r="Q892" s="2" t="n"/>
       <c r="R892" s="3" t="n"/>
+      <c r="T892" s="2" t="n"/>
     </row>
     <row r="893">
       <c r="A893" s="2" t="n"/>
@@ -10412,6 +11309,7 @@
       <c r="P893" s="2" t="n"/>
       <c r="Q893" s="2" t="n"/>
       <c r="R893" s="3" t="n"/>
+      <c r="T893" s="2" t="n"/>
     </row>
     <row r="894">
       <c r="A894" s="2" t="n"/>
@@ -10423,6 +11321,7 @@
       <c r="P894" s="2" t="n"/>
       <c r="Q894" s="2" t="n"/>
       <c r="R894" s="3" t="n"/>
+      <c r="T894" s="2" t="n"/>
     </row>
     <row r="895">
       <c r="A895" s="2" t="n"/>
@@ -10434,6 +11333,7 @@
       <c r="P895" s="2" t="n"/>
       <c r="Q895" s="2" t="n"/>
       <c r="R895" s="3" t="n"/>
+      <c r="T895" s="2" t="n"/>
     </row>
     <row r="896">
       <c r="A896" s="2" t="n"/>
@@ -10445,6 +11345,7 @@
       <c r="P896" s="2" t="n"/>
       <c r="Q896" s="2" t="n"/>
       <c r="R896" s="3" t="n"/>
+      <c r="T896" s="2" t="n"/>
     </row>
     <row r="897">
       <c r="A897" s="2" t="n"/>
@@ -10456,6 +11357,7 @@
       <c r="P897" s="2" t="n"/>
       <c r="Q897" s="2" t="n"/>
       <c r="R897" s="3" t="n"/>
+      <c r="T897" s="2" t="n"/>
     </row>
     <row r="898">
       <c r="A898" s="2" t="n"/>
@@ -10467,6 +11369,7 @@
       <c r="P898" s="2" t="n"/>
       <c r="Q898" s="2" t="n"/>
       <c r="R898" s="3" t="n"/>
+      <c r="T898" s="2" t="n"/>
     </row>
     <row r="899">
       <c r="A899" s="2" t="n"/>
@@ -10478,6 +11381,7 @@
       <c r="P899" s="2" t="n"/>
       <c r="Q899" s="2" t="n"/>
       <c r="R899" s="3" t="n"/>
+      <c r="T899" s="2" t="n"/>
     </row>
     <row r="900">
       <c r="A900" s="2" t="n"/>
@@ -10489,6 +11393,7 @@
       <c r="P900" s="2" t="n"/>
       <c r="Q900" s="2" t="n"/>
       <c r="R900" s="3" t="n"/>
+      <c r="T900" s="2" t="n"/>
     </row>
     <row r="901">
       <c r="A901" s="2" t="n"/>
@@ -10500,6 +11405,7 @@
       <c r="P901" s="2" t="n"/>
       <c r="Q901" s="2" t="n"/>
       <c r="R901" s="3" t="n"/>
+      <c r="T901" s="2" t="n"/>
     </row>
     <row r="902">
       <c r="A902" s="2" t="n"/>
@@ -10511,6 +11417,7 @@
       <c r="P902" s="2" t="n"/>
       <c r="Q902" s="2" t="n"/>
       <c r="R902" s="3" t="n"/>
+      <c r="T902" s="2" t="n"/>
     </row>
     <row r="903">
       <c r="A903" s="2" t="n"/>
@@ -10522,6 +11429,7 @@
       <c r="P903" s="2" t="n"/>
       <c r="Q903" s="2" t="n"/>
       <c r="R903" s="3" t="n"/>
+      <c r="T903" s="2" t="n"/>
     </row>
     <row r="904">
       <c r="A904" s="2" t="n"/>
@@ -10533,6 +11441,7 @@
       <c r="P904" s="2" t="n"/>
       <c r="Q904" s="2" t="n"/>
       <c r="R904" s="3" t="n"/>
+      <c r="T904" s="2" t="n"/>
     </row>
     <row r="905">
       <c r="A905" s="2" t="n"/>
@@ -10544,6 +11453,7 @@
       <c r="P905" s="2" t="n"/>
       <c r="Q905" s="2" t="n"/>
       <c r="R905" s="3" t="n"/>
+      <c r="T905" s="2" t="n"/>
     </row>
     <row r="906">
       <c r="A906" s="2" t="n"/>
@@ -10555,6 +11465,7 @@
       <c r="P906" s="2" t="n"/>
       <c r="Q906" s="2" t="n"/>
       <c r="R906" s="3" t="n"/>
+      <c r="T906" s="2" t="n"/>
     </row>
     <row r="907">
       <c r="A907" s="2" t="n"/>
@@ -10566,6 +11477,7 @@
       <c r="P907" s="2" t="n"/>
       <c r="Q907" s="2" t="n"/>
       <c r="R907" s="3" t="n"/>
+      <c r="T907" s="2" t="n"/>
     </row>
     <row r="908">
       <c r="A908" s="2" t="n"/>
@@ -10577,6 +11489,7 @@
       <c r="P908" s="2" t="n"/>
       <c r="Q908" s="2" t="n"/>
       <c r="R908" s="3" t="n"/>
+      <c r="T908" s="2" t="n"/>
     </row>
     <row r="909">
       <c r="A909" s="2" t="n"/>
@@ -10588,6 +11501,7 @@
       <c r="P909" s="2" t="n"/>
       <c r="Q909" s="2" t="n"/>
       <c r="R909" s="3" t="n"/>
+      <c r="T909" s="2" t="n"/>
     </row>
     <row r="910">
       <c r="A910" s="2" t="n"/>
@@ -10599,6 +11513,7 @@
       <c r="P910" s="2" t="n"/>
       <c r="Q910" s="2" t="n"/>
       <c r="R910" s="3" t="n"/>
+      <c r="T910" s="2" t="n"/>
     </row>
     <row r="911">
       <c r="A911" s="2" t="n"/>
@@ -10610,6 +11525,7 @@
       <c r="P911" s="2" t="n"/>
       <c r="Q911" s="2" t="n"/>
       <c r="R911" s="3" t="n"/>
+      <c r="T911" s="2" t="n"/>
     </row>
     <row r="912">
       <c r="A912" s="2" t="n"/>
@@ -10621,6 +11537,7 @@
       <c r="P912" s="2" t="n"/>
       <c r="Q912" s="2" t="n"/>
       <c r="R912" s="3" t="n"/>
+      <c r="T912" s="2" t="n"/>
     </row>
     <row r="913">
       <c r="A913" s="2" t="n"/>
@@ -10632,6 +11549,7 @@
       <c r="P913" s="2" t="n"/>
       <c r="Q913" s="2" t="n"/>
       <c r="R913" s="3" t="n"/>
+      <c r="T913" s="2" t="n"/>
     </row>
     <row r="914">
       <c r="A914" s="2" t="n"/>
@@ -10643,6 +11561,7 @@
       <c r="P914" s="2" t="n"/>
       <c r="Q914" s="2" t="n"/>
       <c r="R914" s="3" t="n"/>
+      <c r="T914" s="2" t="n"/>
     </row>
     <row r="915">
       <c r="A915" s="2" t="n"/>
@@ -10654,6 +11573,7 @@
       <c r="P915" s="2" t="n"/>
       <c r="Q915" s="2" t="n"/>
       <c r="R915" s="3" t="n"/>
+      <c r="T915" s="2" t="n"/>
     </row>
     <row r="916">
       <c r="A916" s="2" t="n"/>
@@ -10665,6 +11585,7 @@
       <c r="P916" s="2" t="n"/>
       <c r="Q916" s="2" t="n"/>
       <c r="R916" s="3" t="n"/>
+      <c r="T916" s="2" t="n"/>
     </row>
     <row r="917">
       <c r="A917" s="2" t="n"/>
@@ -10676,6 +11597,7 @@
       <c r="P917" s="2" t="n"/>
       <c r="Q917" s="2" t="n"/>
       <c r="R917" s="3" t="n"/>
+      <c r="T917" s="2" t="n"/>
     </row>
     <row r="918">
       <c r="A918" s="2" t="n"/>
@@ -10687,6 +11609,7 @@
       <c r="P918" s="2" t="n"/>
       <c r="Q918" s="2" t="n"/>
       <c r="R918" s="3" t="n"/>
+      <c r="T918" s="2" t="n"/>
     </row>
     <row r="919">
       <c r="A919" s="2" t="n"/>
@@ -10698,6 +11621,7 @@
       <c r="P919" s="2" t="n"/>
       <c r="Q919" s="2" t="n"/>
       <c r="R919" s="3" t="n"/>
+      <c r="T919" s="2" t="n"/>
     </row>
     <row r="920">
       <c r="A920" s="2" t="n"/>
@@ -10709,6 +11633,7 @@
       <c r="P920" s="2" t="n"/>
       <c r="Q920" s="2" t="n"/>
       <c r="R920" s="3" t="n"/>
+      <c r="T920" s="2" t="n"/>
     </row>
     <row r="921">
       <c r="A921" s="2" t="n"/>
@@ -10720,6 +11645,7 @@
       <c r="P921" s="2" t="n"/>
       <c r="Q921" s="2" t="n"/>
       <c r="R921" s="3" t="n"/>
+      <c r="T921" s="2" t="n"/>
     </row>
     <row r="922">
       <c r="A922" s="2" t="n"/>
@@ -10731,6 +11657,7 @@
       <c r="P922" s="2" t="n"/>
       <c r="Q922" s="2" t="n"/>
       <c r="R922" s="3" t="n"/>
+      <c r="T922" s="2" t="n"/>
     </row>
     <row r="923">
       <c r="A923" s="2" t="n"/>
@@ -10742,6 +11669,7 @@
       <c r="P923" s="2" t="n"/>
       <c r="Q923" s="2" t="n"/>
       <c r="R923" s="3" t="n"/>
+      <c r="T923" s="2" t="n"/>
     </row>
     <row r="924">
       <c r="A924" s="2" t="n"/>
@@ -10753,6 +11681,7 @@
       <c r="P924" s="2" t="n"/>
       <c r="Q924" s="2" t="n"/>
       <c r="R924" s="3" t="n"/>
+      <c r="T924" s="2" t="n"/>
     </row>
     <row r="925">
       <c r="A925" s="2" t="n"/>
@@ -10764,6 +11693,7 @@
       <c r="P925" s="2" t="n"/>
       <c r="Q925" s="2" t="n"/>
       <c r="R925" s="3" t="n"/>
+      <c r="T925" s="2" t="n"/>
     </row>
     <row r="926">
       <c r="A926" s="2" t="n"/>
@@ -10775,6 +11705,7 @@
       <c r="P926" s="2" t="n"/>
       <c r="Q926" s="2" t="n"/>
       <c r="R926" s="3" t="n"/>
+      <c r="T926" s="2" t="n"/>
     </row>
     <row r="927">
       <c r="A927" s="2" t="n"/>
@@ -10786,6 +11717,7 @@
       <c r="P927" s="2" t="n"/>
       <c r="Q927" s="2" t="n"/>
       <c r="R927" s="3" t="n"/>
+      <c r="T927" s="2" t="n"/>
     </row>
     <row r="928">
       <c r="A928" s="2" t="n"/>
@@ -10797,6 +11729,7 @@
       <c r="P928" s="2" t="n"/>
       <c r="Q928" s="2" t="n"/>
       <c r="R928" s="3" t="n"/>
+      <c r="T928" s="2" t="n"/>
     </row>
     <row r="929">
       <c r="A929" s="2" t="n"/>
@@ -10808,6 +11741,7 @@
       <c r="P929" s="2" t="n"/>
       <c r="Q929" s="2" t="n"/>
       <c r="R929" s="3" t="n"/>
+      <c r="T929" s="2" t="n"/>
     </row>
     <row r="930">
       <c r="A930" s="2" t="n"/>
@@ -10819,6 +11753,7 @@
       <c r="P930" s="2" t="n"/>
       <c r="Q930" s="2" t="n"/>
       <c r="R930" s="3" t="n"/>
+      <c r="T930" s="2" t="n"/>
     </row>
     <row r="931">
       <c r="A931" s="2" t="n"/>
@@ -10830,6 +11765,7 @@
       <c r="P931" s="2" t="n"/>
       <c r="Q931" s="2" t="n"/>
       <c r="R931" s="3" t="n"/>
+      <c r="T931" s="2" t="n"/>
     </row>
     <row r="932">
       <c r="A932" s="2" t="n"/>
@@ -10841,6 +11777,7 @@
       <c r="P932" s="2" t="n"/>
       <c r="Q932" s="2" t="n"/>
       <c r="R932" s="3" t="n"/>
+      <c r="T932" s="2" t="n"/>
     </row>
     <row r="933">
       <c r="A933" s="2" t="n"/>
@@ -10852,6 +11789,7 @@
       <c r="P933" s="2" t="n"/>
       <c r="Q933" s="2" t="n"/>
       <c r="R933" s="3" t="n"/>
+      <c r="T933" s="2" t="n"/>
     </row>
     <row r="934">
       <c r="A934" s="2" t="n"/>
@@ -10863,6 +11801,7 @@
       <c r="P934" s="2" t="n"/>
       <c r="Q934" s="2" t="n"/>
       <c r="R934" s="3" t="n"/>
+      <c r="T934" s="2" t="n"/>
     </row>
     <row r="935">
       <c r="A935" s="2" t="n"/>
@@ -10874,6 +11813,7 @@
       <c r="P935" s="2" t="n"/>
       <c r="Q935" s="2" t="n"/>
       <c r="R935" s="3" t="n"/>
+      <c r="T935" s="2" t="n"/>
     </row>
     <row r="936">
       <c r="A936" s="2" t="n"/>
@@ -10885,6 +11825,7 @@
       <c r="P936" s="2" t="n"/>
       <c r="Q936" s="2" t="n"/>
       <c r="R936" s="3" t="n"/>
+      <c r="T936" s="2" t="n"/>
     </row>
     <row r="937">
       <c r="A937" s="2" t="n"/>
@@ -10896,6 +11837,7 @@
       <c r="P937" s="2" t="n"/>
       <c r="Q937" s="2" t="n"/>
       <c r="R937" s="3" t="n"/>
+      <c r="T937" s="2" t="n"/>
     </row>
     <row r="938">
       <c r="A938" s="2" t="n"/>
@@ -10907,6 +11849,7 @@
       <c r="P938" s="2" t="n"/>
       <c r="Q938" s="2" t="n"/>
       <c r="R938" s="3" t="n"/>
+      <c r="T938" s="2" t="n"/>
     </row>
     <row r="939">
       <c r="A939" s="2" t="n"/>
@@ -10918,6 +11861,7 @@
       <c r="P939" s="2" t="n"/>
       <c r="Q939" s="2" t="n"/>
       <c r="R939" s="3" t="n"/>
+      <c r="T939" s="2" t="n"/>
     </row>
     <row r="940">
       <c r="A940" s="2" t="n"/>
@@ -10929,6 +11873,7 @@
       <c r="P940" s="2" t="n"/>
       <c r="Q940" s="2" t="n"/>
       <c r="R940" s="3" t="n"/>
+      <c r="T940" s="2" t="n"/>
     </row>
     <row r="941">
       <c r="A941" s="2" t="n"/>
@@ -10940,6 +11885,7 @@
       <c r="P941" s="2" t="n"/>
       <c r="Q941" s="2" t="n"/>
       <c r="R941" s="3" t="n"/>
+      <c r="T941" s="2" t="n"/>
     </row>
     <row r="942">
       <c r="A942" s="2" t="n"/>
@@ -10951,6 +11897,7 @@
       <c r="P942" s="2" t="n"/>
       <c r="Q942" s="2" t="n"/>
       <c r="R942" s="3" t="n"/>
+      <c r="T942" s="2" t="n"/>
     </row>
     <row r="943">
       <c r="A943" s="2" t="n"/>
@@ -10962,6 +11909,7 @@
       <c r="P943" s="2" t="n"/>
       <c r="Q943" s="2" t="n"/>
       <c r="R943" s="3" t="n"/>
+      <c r="T943" s="2" t="n"/>
     </row>
     <row r="944">
       <c r="A944" s="2" t="n"/>
@@ -10973,6 +11921,7 @@
       <c r="P944" s="2" t="n"/>
       <c r="Q944" s="2" t="n"/>
       <c r="R944" s="3" t="n"/>
+      <c r="T944" s="2" t="n"/>
     </row>
     <row r="945">
       <c r="A945" s="2" t="n"/>
@@ -10984,6 +11933,7 @@
       <c r="P945" s="2" t="n"/>
       <c r="Q945" s="2" t="n"/>
       <c r="R945" s="3" t="n"/>
+      <c r="T945" s="2" t="n"/>
     </row>
     <row r="946">
       <c r="A946" s="2" t="n"/>
@@ -10995,6 +11945,7 @@
       <c r="P946" s="2" t="n"/>
       <c r="Q946" s="2" t="n"/>
       <c r="R946" s="3" t="n"/>
+      <c r="T946" s="2" t="n"/>
     </row>
     <row r="947">
       <c r="A947" s="2" t="n"/>
@@ -11006,6 +11957,7 @@
       <c r="P947" s="2" t="n"/>
       <c r="Q947" s="2" t="n"/>
       <c r="R947" s="3" t="n"/>
+      <c r="T947" s="2" t="n"/>
     </row>
     <row r="948">
       <c r="A948" s="2" t="n"/>
@@ -11017,6 +11969,7 @@
       <c r="P948" s="2" t="n"/>
       <c r="Q948" s="2" t="n"/>
       <c r="R948" s="3" t="n"/>
+      <c r="T948" s="2" t="n"/>
     </row>
     <row r="949">
       <c r="A949" s="2" t="n"/>
@@ -11028,6 +11981,7 @@
       <c r="P949" s="2" t="n"/>
       <c r="Q949" s="2" t="n"/>
       <c r="R949" s="3" t="n"/>
+      <c r="T949" s="2" t="n"/>
     </row>
     <row r="950">
       <c r="A950" s="2" t="n"/>
@@ -11039,6 +11993,7 @@
       <c r="P950" s="2" t="n"/>
       <c r="Q950" s="2" t="n"/>
       <c r="R950" s="3" t="n"/>
+      <c r="T950" s="2" t="n"/>
     </row>
     <row r="951">
       <c r="A951" s="2" t="n"/>
@@ -11050,6 +12005,7 @@
       <c r="P951" s="2" t="n"/>
       <c r="Q951" s="2" t="n"/>
       <c r="R951" s="3" t="n"/>
+      <c r="T951" s="2" t="n"/>
     </row>
     <row r="952">
       <c r="A952" s="2" t="n"/>
@@ -11061,6 +12017,7 @@
       <c r="P952" s="2" t="n"/>
       <c r="Q952" s="2" t="n"/>
       <c r="R952" s="3" t="n"/>
+      <c r="T952" s="2" t="n"/>
     </row>
     <row r="953">
       <c r="A953" s="2" t="n"/>
@@ -11072,6 +12029,7 @@
       <c r="P953" s="2" t="n"/>
       <c r="Q953" s="2" t="n"/>
       <c r="R953" s="3" t="n"/>
+      <c r="T953" s="2" t="n"/>
     </row>
     <row r="954">
       <c r="A954" s="2" t="n"/>
@@ -11083,6 +12041,7 @@
       <c r="P954" s="2" t="n"/>
       <c r="Q954" s="2" t="n"/>
       <c r="R954" s="3" t="n"/>
+      <c r="T954" s="2" t="n"/>
     </row>
     <row r="955">
       <c r="A955" s="2" t="n"/>
@@ -11094,6 +12053,7 @@
       <c r="P955" s="2" t="n"/>
       <c r="Q955" s="2" t="n"/>
       <c r="R955" s="3" t="n"/>
+      <c r="T955" s="2" t="n"/>
     </row>
     <row r="956">
       <c r="A956" s="2" t="n"/>
@@ -11105,6 +12065,7 @@
       <c r="P956" s="2" t="n"/>
       <c r="Q956" s="2" t="n"/>
       <c r="R956" s="3" t="n"/>
+      <c r="T956" s="2" t="n"/>
     </row>
     <row r="957">
       <c r="A957" s="2" t="n"/>
@@ -11116,6 +12077,7 @@
       <c r="P957" s="2" t="n"/>
       <c r="Q957" s="2" t="n"/>
       <c r="R957" s="3" t="n"/>
+      <c r="T957" s="2" t="n"/>
     </row>
     <row r="958">
       <c r="A958" s="2" t="n"/>
@@ -11127,6 +12089,7 @@
       <c r="P958" s="2" t="n"/>
       <c r="Q958" s="2" t="n"/>
       <c r="R958" s="3" t="n"/>
+      <c r="T958" s="2" t="n"/>
     </row>
     <row r="959">
       <c r="A959" s="2" t="n"/>
@@ -11138,6 +12101,7 @@
       <c r="P959" s="2" t="n"/>
       <c r="Q959" s="2" t="n"/>
       <c r="R959" s="3" t="n"/>
+      <c r="T959" s="2" t="n"/>
     </row>
     <row r="960">
       <c r="A960" s="2" t="n"/>
@@ -11149,6 +12113,7 @@
       <c r="P960" s="2" t="n"/>
       <c r="Q960" s="2" t="n"/>
       <c r="R960" s="3" t="n"/>
+      <c r="T960" s="2" t="n"/>
     </row>
     <row r="961">
       <c r="A961" s="2" t="n"/>
@@ -11160,6 +12125,7 @@
       <c r="P961" s="2" t="n"/>
       <c r="Q961" s="2" t="n"/>
       <c r="R961" s="3" t="n"/>
+      <c r="T961" s="2" t="n"/>
     </row>
     <row r="962">
       <c r="A962" s="2" t="n"/>
@@ -11171,6 +12137,7 @@
       <c r="P962" s="2" t="n"/>
       <c r="Q962" s="2" t="n"/>
       <c r="R962" s="3" t="n"/>
+      <c r="T962" s="2" t="n"/>
     </row>
     <row r="963">
       <c r="A963" s="2" t="n"/>
@@ -11182,6 +12149,7 @@
       <c r="P963" s="2" t="n"/>
       <c r="Q963" s="2" t="n"/>
       <c r="R963" s="3" t="n"/>
+      <c r="T963" s="2" t="n"/>
     </row>
     <row r="964">
       <c r="A964" s="2" t="n"/>
@@ -11193,6 +12161,7 @@
       <c r="P964" s="2" t="n"/>
       <c r="Q964" s="2" t="n"/>
       <c r="R964" s="3" t="n"/>
+      <c r="T964" s="2" t="n"/>
     </row>
     <row r="965">
       <c r="A965" s="2" t="n"/>
@@ -11204,6 +12173,7 @@
       <c r="P965" s="2" t="n"/>
       <c r="Q965" s="2" t="n"/>
       <c r="R965" s="3" t="n"/>
+      <c r="T965" s="2" t="n"/>
     </row>
     <row r="966">
       <c r="A966" s="2" t="n"/>
@@ -11215,6 +12185,7 @@
       <c r="P966" s="2" t="n"/>
       <c r="Q966" s="2" t="n"/>
       <c r="R966" s="3" t="n"/>
+      <c r="T966" s="2" t="n"/>
     </row>
     <row r="967">
       <c r="A967" s="2" t="n"/>
@@ -11226,6 +12197,7 @@
       <c r="P967" s="2" t="n"/>
       <c r="Q967" s="2" t="n"/>
       <c r="R967" s="3" t="n"/>
+      <c r="T967" s="2" t="n"/>
     </row>
     <row r="968">
       <c r="A968" s="2" t="n"/>
@@ -11237,6 +12209,7 @@
       <c r="P968" s="2" t="n"/>
       <c r="Q968" s="2" t="n"/>
       <c r="R968" s="3" t="n"/>
+      <c r="T968" s="2" t="n"/>
     </row>
     <row r="969">
       <c r="A969" s="2" t="n"/>
@@ -11248,6 +12221,7 @@
       <c r="P969" s="2" t="n"/>
       <c r="Q969" s="2" t="n"/>
       <c r="R969" s="3" t="n"/>
+      <c r="T969" s="2" t="n"/>
     </row>
     <row r="970">
       <c r="A970" s="2" t="n"/>
@@ -11259,6 +12233,7 @@
       <c r="P970" s="2" t="n"/>
       <c r="Q970" s="2" t="n"/>
       <c r="R970" s="3" t="n"/>
+      <c r="T970" s="2" t="n"/>
     </row>
     <row r="971">
       <c r="A971" s="2" t="n"/>
@@ -11270,6 +12245,7 @@
       <c r="P971" s="2" t="n"/>
       <c r="Q971" s="2" t="n"/>
       <c r="R971" s="3" t="n"/>
+      <c r="T971" s="2" t="n"/>
     </row>
     <row r="972">
       <c r="A972" s="2" t="n"/>
@@ -11281,6 +12257,7 @@
       <c r="P972" s="2" t="n"/>
       <c r="Q972" s="2" t="n"/>
       <c r="R972" s="3" t="n"/>
+      <c r="T972" s="2" t="n"/>
     </row>
     <row r="973">
       <c r="A973" s="2" t="n"/>
@@ -11292,6 +12269,7 @@
       <c r="P973" s="2" t="n"/>
       <c r="Q973" s="2" t="n"/>
       <c r="R973" s="3" t="n"/>
+      <c r="T973" s="2" t="n"/>
     </row>
     <row r="974">
       <c r="A974" s="2" t="n"/>
@@ -11303,6 +12281,7 @@
       <c r="P974" s="2" t="n"/>
       <c r="Q974" s="2" t="n"/>
       <c r="R974" s="3" t="n"/>
+      <c r="T974" s="2" t="n"/>
     </row>
     <row r="975">
       <c r="A975" s="2" t="n"/>
@@ -11314,6 +12293,7 @@
       <c r="P975" s="2" t="n"/>
       <c r="Q975" s="2" t="n"/>
       <c r="R975" s="3" t="n"/>
+      <c r="T975" s="2" t="n"/>
     </row>
     <row r="976">
       <c r="A976" s="2" t="n"/>
@@ -11325,6 +12305,7 @@
       <c r="P976" s="2" t="n"/>
       <c r="Q976" s="2" t="n"/>
       <c r="R976" s="3" t="n"/>
+      <c r="T976" s="2" t="n"/>
     </row>
     <row r="977">
       <c r="A977" s="2" t="n"/>
@@ -11336,6 +12317,7 @@
       <c r="P977" s="2" t="n"/>
       <c r="Q977" s="2" t="n"/>
       <c r="R977" s="3" t="n"/>
+      <c r="T977" s="2" t="n"/>
     </row>
     <row r="978">
       <c r="A978" s="2" t="n"/>
@@ -11347,6 +12329,7 @@
       <c r="P978" s="2" t="n"/>
       <c r="Q978" s="2" t="n"/>
       <c r="R978" s="3" t="n"/>
+      <c r="T978" s="2" t="n"/>
     </row>
     <row r="979">
       <c r="A979" s="2" t="n"/>
@@ -11358,6 +12341,7 @@
       <c r="P979" s="2" t="n"/>
       <c r="Q979" s="2" t="n"/>
       <c r="R979" s="3" t="n"/>
+      <c r="T979" s="2" t="n"/>
     </row>
     <row r="980">
       <c r="A980" s="2" t="n"/>
@@ -11369,6 +12353,7 @@
       <c r="P980" s="2" t="n"/>
       <c r="Q980" s="2" t="n"/>
       <c r="R980" s="3" t="n"/>
+      <c r="T980" s="2" t="n"/>
     </row>
     <row r="981">
       <c r="A981" s="2" t="n"/>
@@ -11380,6 +12365,7 @@
       <c r="P981" s="2" t="n"/>
       <c r="Q981" s="2" t="n"/>
       <c r="R981" s="3" t="n"/>
+      <c r="T981" s="2" t="n"/>
     </row>
     <row r="982">
       <c r="A982" s="2" t="n"/>
@@ -11391,6 +12377,7 @@
       <c r="P982" s="2" t="n"/>
       <c r="Q982" s="2" t="n"/>
       <c r="R982" s="3" t="n"/>
+      <c r="T982" s="2" t="n"/>
     </row>
     <row r="983">
       <c r="A983" s="2" t="n"/>
@@ -11402,6 +12389,7 @@
       <c r="P983" s="2" t="n"/>
       <c r="Q983" s="2" t="n"/>
       <c r="R983" s="3" t="n"/>
+      <c r="T983" s="2" t="n"/>
     </row>
     <row r="984">
       <c r="A984" s="2" t="n"/>
@@ -11413,6 +12401,7 @@
       <c r="P984" s="2" t="n"/>
       <c r="Q984" s="2" t="n"/>
       <c r="R984" s="3" t="n"/>
+      <c r="T984" s="2" t="n"/>
     </row>
     <row r="985">
       <c r="A985" s="2" t="n"/>
@@ -11424,6 +12413,7 @@
       <c r="P985" s="2" t="n"/>
       <c r="Q985" s="2" t="n"/>
       <c r="R985" s="3" t="n"/>
+      <c r="T985" s="2" t="n"/>
     </row>
     <row r="986">
       <c r="A986" s="2" t="n"/>
@@ -11435,6 +12425,7 @@
       <c r="P986" s="2" t="n"/>
       <c r="Q986" s="2" t="n"/>
       <c r="R986" s="3" t="n"/>
+      <c r="T986" s="2" t="n"/>
     </row>
     <row r="987">
       <c r="A987" s="2" t="n"/>
@@ -11446,6 +12437,7 @@
       <c r="P987" s="2" t="n"/>
       <c r="Q987" s="2" t="n"/>
       <c r="R987" s="3" t="n"/>
+      <c r="T987" s="2" t="n"/>
     </row>
     <row r="988">
       <c r="A988" s="2" t="n"/>
@@ -11457,6 +12449,7 @@
       <c r="P988" s="2" t="n"/>
       <c r="Q988" s="2" t="n"/>
       <c r="R988" s="3" t="n"/>
+      <c r="T988" s="2" t="n"/>
     </row>
     <row r="989">
       <c r="A989" s="2" t="n"/>
@@ -11468,6 +12461,7 @@
       <c r="P989" s="2" t="n"/>
       <c r="Q989" s="2" t="n"/>
       <c r="R989" s="3" t="n"/>
+      <c r="T989" s="2" t="n"/>
     </row>
     <row r="990">
       <c r="A990" s="2" t="n"/>
@@ -11479,6 +12473,7 @@
       <c r="P990" s="2" t="n"/>
       <c r="Q990" s="2" t="n"/>
       <c r="R990" s="3" t="n"/>
+      <c r="T990" s="2" t="n"/>
     </row>
     <row r="991">
       <c r="A991" s="2" t="n"/>
@@ -11490,6 +12485,7 @@
       <c r="P991" s="2" t="n"/>
       <c r="Q991" s="2" t="n"/>
       <c r="R991" s="3" t="n"/>
+      <c r="T991" s="2" t="n"/>
     </row>
     <row r="992">
       <c r="A992" s="2" t="n"/>
@@ -11501,6 +12497,7 @@
       <c r="P992" s="2" t="n"/>
       <c r="Q992" s="2" t="n"/>
       <c r="R992" s="3" t="n"/>
+      <c r="T992" s="2" t="n"/>
     </row>
     <row r="993">
       <c r="A993" s="2" t="n"/>
@@ -11512,6 +12509,7 @@
       <c r="P993" s="2" t="n"/>
       <c r="Q993" s="2" t="n"/>
       <c r="R993" s="3" t="n"/>
+      <c r="T993" s="2" t="n"/>
     </row>
     <row r="994">
       <c r="A994" s="2" t="n"/>
@@ -11523,6 +12521,7 @@
       <c r="P994" s="2" t="n"/>
       <c r="Q994" s="2" t="n"/>
       <c r="R994" s="3" t="n"/>
+      <c r="T994" s="2" t="n"/>
     </row>
     <row r="995">
       <c r="A995" s="2" t="n"/>
@@ -11534,6 +12533,7 @@
       <c r="P995" s="2" t="n"/>
       <c r="Q995" s="2" t="n"/>
       <c r="R995" s="3" t="n"/>
+      <c r="T995" s="2" t="n"/>
     </row>
     <row r="996">
       <c r="A996" s="2" t="n"/>
@@ -11545,6 +12545,7 @@
       <c r="P996" s="2" t="n"/>
       <c r="Q996" s="2" t="n"/>
       <c r="R996" s="3" t="n"/>
+      <c r="T996" s="2" t="n"/>
     </row>
     <row r="997">
       <c r="A997" s="2" t="n"/>
@@ -11556,6 +12557,7 @@
       <c r="P997" s="2" t="n"/>
       <c r="Q997" s="2" t="n"/>
       <c r="R997" s="3" t="n"/>
+      <c r="T997" s="2" t="n"/>
     </row>
     <row r="998">
       <c r="A998" s="2" t="n"/>
@@ -11567,6 +12569,7 @@
       <c r="P998" s="2" t="n"/>
       <c r="Q998" s="2" t="n"/>
       <c r="R998" s="3" t="n"/>
+      <c r="T998" s="2" t="n"/>
     </row>
     <row r="999">
       <c r="A999" s="2" t="n"/>
@@ -11578,6 +12581,7 @@
       <c r="P999" s="2" t="n"/>
       <c r="Q999" s="2" t="n"/>
       <c r="R999" s="3" t="n"/>
+      <c r="T999" s="2" t="n"/>
     </row>
     <row r="1000">
       <c r="A1000" s="2" t="n"/>
@@ -11589,6 +12593,7 @@
       <c r="P1000" s="2" t="n"/>
       <c r="Q1000" s="2" t="n"/>
       <c r="R1000" s="3" t="n"/>
+      <c r="T1000" s="2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -11606,7 +12611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11900,6 +12905,19 @@
       <c r="C19" t="inlineStr">
         <is>
           <t>Yes = write the headline on the image (Cloudinary)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Approver Email</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Who gets the approval emails (separate several with commas). Empty = approve in this sheet only.</t>
         </is>
       </c>
     </row>
@@ -12080,7 +13098,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3. Set Status to APPROVED (or REGENERATE / REJECTED).</t>
+          <t>3. Set Status to APPROVED (or REGENERATE / REJECTED) - or click the buttons in the approval email.</t>
         </is>
       </c>
     </row>
